--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$396</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$437</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD396"/>
+  <dimension ref="A1:AD437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48972,8 +48972,5174 @@
       <c r="AC396" s="2" t="inlineStr"/>
       <c r="AD396" s="2" t="inlineStr"/>
     </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>translationjob27</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:21.034</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:21.060</t>
+        </is>
+      </c>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:21.323</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:24.819</t>
+        </is>
+      </c>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:24.880</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>11:27:24.937</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="n">
+        <v>3785</v>
+      </c>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U397" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V397" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="n">
+        <v>3903</v>
+      </c>
+      <c r="Y397" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z397" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA397" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB397" s="2" t="inlineStr"/>
+      <c r="AC397" s="2" t="inlineStr"/>
+      <c r="AD397" s="2" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>translationjob28</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:25.251</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:25.280</t>
+        </is>
+      </c>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:25.733</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:28.549</t>
+        </is>
+      </c>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:28.610</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>11:27:28.671</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="n">
+        <v>3298</v>
+      </c>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U398" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V398" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W398" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X398" s="2" t="n">
+        <v>3420</v>
+      </c>
+      <c r="Y398" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z398" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA398" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB398" s="2" t="inlineStr"/>
+      <c r="AC398" s="2" t="inlineStr"/>
+      <c r="AD398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>translationjob29</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:28.964</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:28.994</t>
+        </is>
+      </c>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:29.201</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:31.511</t>
+        </is>
+      </c>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:31.554</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr">
+        <is>
+          <t>11:27:31.621</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="n">
+        <v>2547</v>
+      </c>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U399" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V399" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="n">
+        <v>2657</v>
+      </c>
+      <c r="Y399" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z399" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA399" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB399" s="2" t="inlineStr"/>
+      <c r="AC399" s="2" t="inlineStr"/>
+      <c r="AD399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>translationjob30</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:31.896</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:31.925</t>
+        </is>
+      </c>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:32.125</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:35.510</t>
+        </is>
+      </c>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:35.557</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr">
+        <is>
+          <t>11:27:35.628</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="n">
+        <v>3614</v>
+      </c>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U400" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V400" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="n">
+        <v>3732</v>
+      </c>
+      <c r="Y400" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z400" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA400" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB400" s="2" t="inlineStr"/>
+      <c r="AC400" s="2" t="inlineStr"/>
+      <c r="AD400" s="2" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>translationjob31</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:35.924</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:35.949</t>
+        </is>
+      </c>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:36.144</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:39.135</t>
+        </is>
+      </c>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:39.185</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>11:27:39.236</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="n">
+        <v>3211</v>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U401" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V401" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="n">
+        <v>3312</v>
+      </c>
+      <c r="Y401" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z401" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA401" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB401" s="2" t="inlineStr"/>
+      <c r="AC401" s="2" t="inlineStr"/>
+      <c r="AD401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>translationjob32</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:39.698</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:39.724</t>
+        </is>
+      </c>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:40.105</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:43.410</t>
+        </is>
+      </c>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:43.462</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>11:27:43.559</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="n">
+        <v>3712</v>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U402" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V402" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="n">
+        <v>3861</v>
+      </c>
+      <c r="Y402" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z402" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA402" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB402" s="2" t="inlineStr"/>
+      <c r="AC402" s="2" t="inlineStr"/>
+      <c r="AD402" s="2" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>translationjob33</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:30.382</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:30.408</t>
+        </is>
+      </c>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:30.588</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:33.854</t>
+        </is>
+      </c>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:34.021</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>11:31:34.089</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="n">
+        <v>3472</v>
+      </c>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="U403" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V403" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="n">
+        <v>3707</v>
+      </c>
+      <c r="Y403" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z403" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA403" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB403" s="2" t="inlineStr"/>
+      <c r="AC403" s="2" t="inlineStr"/>
+      <c r="AD403" s="2" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>translationjob34</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:34.333</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:34.357</t>
+        </is>
+      </c>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:34.551</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:37.631</t>
+        </is>
+      </c>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:37.721</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>11:31:37.920</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="n">
+        <v>3298</v>
+      </c>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="U404" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V404" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="W404" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X404" s="2" t="n">
+        <v>3587</v>
+      </c>
+      <c r="Y404" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z404" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB404" s="2" t="inlineStr"/>
+      <c r="AC404" s="2" t="inlineStr"/>
+      <c r="AD404" s="2" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>translationjob35</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:38.029</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:38.053</t>
+        </is>
+      </c>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:38.236</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.969</t>
+        </is>
+      </c>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:41.022</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>11:31:41.094</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="n">
+        <v>2940</v>
+      </c>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U405" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V405" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="n">
+        <v>3065</v>
+      </c>
+      <c r="Y405" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z405" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB405" s="2" t="inlineStr"/>
+      <c r="AC405" s="2" t="inlineStr"/>
+      <c r="AD405" s="2" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>translationjob36</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:39.529</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:39.556</t>
+        </is>
+      </c>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:39.741</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.121</t>
+        </is>
+      </c>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.171</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.240</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="n">
+        <v>3592</v>
+      </c>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U406" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V406" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="n">
+        <v>3711</v>
+      </c>
+      <c r="Y406" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z406" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA406" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB406" s="2" t="inlineStr"/>
+      <c r="AC406" s="2" t="inlineStr"/>
+      <c r="AD406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>translationjob37</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:41.375</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:41.401</t>
+        </is>
+      </c>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:41.605</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:45.588</t>
+        </is>
+      </c>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:45.643</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr">
+        <is>
+          <t>11:31:45.695</t>
+        </is>
+      </c>
+      <c r="P407" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="n">
+        <v>4213</v>
+      </c>
+      <c r="S407" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T407" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U407" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V407" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W407" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X407" s="2" t="n">
+        <v>4320</v>
+      </c>
+      <c r="Y407" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="Z407" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA407" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB407" s="2" t="inlineStr"/>
+      <c r="AC407" s="2" t="inlineStr"/>
+      <c r="AD407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>translationjob38</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.603</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.628</t>
+        </is>
+      </c>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:43.815</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:49.671</t>
+        </is>
+      </c>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:49.731</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>11:31:49.791</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="n">
+        <v>6068</v>
+      </c>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U408" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V408" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W408" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X408" s="2" t="n">
+        <v>6188</v>
+      </c>
+      <c r="Y408" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z408" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA408" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB408" s="2" t="inlineStr"/>
+      <c r="AC408" s="2" t="inlineStr"/>
+      <c r="AD408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>translationjob39</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:46.010</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:46.027</t>
+        </is>
+      </c>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:46.221</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.016</t>
+        </is>
+      </c>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.052</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.145</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="n">
+        <v>5006</v>
+      </c>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U409" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V409" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="W409" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X409" s="2" t="n">
+        <v>5135</v>
+      </c>
+      <c r="Y409" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z409" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA409" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB409" s="2" t="inlineStr"/>
+      <c r="AC409" s="2" t="inlineStr"/>
+      <c r="AD409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>translationjob40</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.364</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.383</t>
+        </is>
+      </c>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:51.735</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.441</t>
+        </is>
+      </c>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.490</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.534</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="n">
+        <v>4077</v>
+      </c>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U410" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V410" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W410" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X410" s="2" t="n">
+        <v>4170</v>
+      </c>
+      <c r="Y410" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z410" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA410" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB410" s="2" t="inlineStr"/>
+      <c r="AC410" s="2" t="inlineStr"/>
+      <c r="AD410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>translationjob41</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:52.170</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:52.185</t>
+        </is>
+      </c>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:52.343</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.293</t>
+        </is>
+      </c>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.335</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.376</t>
+        </is>
+      </c>
+      <c r="P411" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="n">
+        <v>3123</v>
+      </c>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U411" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V411" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="n">
+        <v>3206</v>
+      </c>
+      <c r="Y411" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z411" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA411" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB411" s="2" t="inlineStr"/>
+      <c r="AC411" s="2" t="inlineStr"/>
+      <c r="AD411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>translationjob42</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.532</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.787</t>
+        </is>
+      </c>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>12:35:55.896</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.077</t>
+        </is>
+      </c>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.117</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.177</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>4545</v>
+      </c>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U412" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V412" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="n">
+        <v>4645</v>
+      </c>
+      <c r="Y412" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z412" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA412" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB412" s="2" t="inlineStr"/>
+      <c r="AC412" s="2" t="inlineStr"/>
+      <c r="AD412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>12:35:56.865</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr">
+        <is>
+          <t>12:35:56.883</t>
+        </is>
+      </c>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>12:35:57.049</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.593</t>
+        </is>
+      </c>
+      <c r="N413" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.641</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.704</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>3728</v>
+      </c>
+      <c r="S413" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U413" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V413" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W413" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X413" s="2" t="n">
+        <v>3839</v>
+      </c>
+      <c r="Y413" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z413" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB413" s="2" t="inlineStr"/>
+      <c r="AC413" s="2" t="inlineStr"/>
+      <c r="AD413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.363</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.904</t>
+        </is>
+      </c>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:00.963</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:04.927</t>
+        </is>
+      </c>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:04.974</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>12:36:05.017</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="n">
+        <v>4564</v>
+      </c>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V414" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W414" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X414" s="2" t="n">
+        <v>4654</v>
+      </c>
+      <c r="Y414" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z414" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA414" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB414" s="2" t="inlineStr"/>
+      <c r="AC414" s="2" t="inlineStr"/>
+      <c r="AD414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:08.865</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:08.884</t>
+        </is>
+      </c>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:09.220</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:13.981</t>
+        </is>
+      </c>
+      <c r="N415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:14.026</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>13:07:14.102</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>5116</v>
+      </c>
+      <c r="S415" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W415" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X415" s="2" t="n">
+        <v>5237</v>
+      </c>
+      <c r="Y415" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z415" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB415" s="2" t="inlineStr"/>
+      <c r="AC415" s="2" t="inlineStr"/>
+      <c r="AD415" s="2" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:14.246</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:14.314</t>
+        </is>
+      </c>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:14.484</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:18.858</t>
+        </is>
+      </c>
+      <c r="N416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:18.902</t>
+        </is>
+      </c>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>13:07:19.003</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R416" s="2" t="n">
+        <v>4612</v>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U416" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V416" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="W416" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X416" s="2" t="n">
+        <v>4757</v>
+      </c>
+      <c r="Y416" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z416" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA416" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB416" s="2" t="inlineStr"/>
+      <c r="AC416" s="2" t="inlineStr"/>
+      <c r="AD416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>translationjob33</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:19.139</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:19.154</t>
+        </is>
+      </c>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:19.342</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:23.888</t>
+        </is>
+      </c>
+      <c r="N417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:23.930</t>
+        </is>
+      </c>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>13:07:23.987</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="n">
+        <v>4749</v>
+      </c>
+      <c r="S417" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T417" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U417" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V417" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W417" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>4848</v>
+      </c>
+      <c r="Y417" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z417" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB417" s="2" t="inlineStr"/>
+      <c r="AC417" s="2" t="inlineStr"/>
+      <c r="AD417" s="2" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>translationjob34</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:24.118</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:24.133</t>
+        </is>
+      </c>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:24.457</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:28.793</t>
+        </is>
+      </c>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:28.839</t>
+        </is>
+      </c>
+      <c r="O418" s="2" t="inlineStr">
+        <is>
+          <t>13:07:28.894</t>
+        </is>
+      </c>
+      <c r="P418" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R418" s="2" t="n">
+        <v>4675</v>
+      </c>
+      <c r="S418" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T418" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U418" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W418" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X418" s="2" t="n">
+        <v>4776</v>
+      </c>
+      <c r="Y418" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z418" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA418" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB418" s="2" t="inlineStr"/>
+      <c r="AC418" s="2" t="inlineStr"/>
+      <c r="AD418" s="2" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>translationjob35</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:28.949</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:28.964</t>
+        </is>
+      </c>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:29.211</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:34.009</t>
+        </is>
+      </c>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:34.050</t>
+        </is>
+      </c>
+      <c r="O419" s="2" t="inlineStr">
+        <is>
+          <t>13:07:34.095</t>
+        </is>
+      </c>
+      <c r="P419" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="n">
+        <v>5060</v>
+      </c>
+      <c r="S419" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U419" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V419" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W419" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X419" s="2" t="n">
+        <v>5146</v>
+      </c>
+      <c r="Y419" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z419" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB419" s="2" t="inlineStr"/>
+      <c r="AC419" s="2" t="inlineStr"/>
+      <c r="AD419" s="2" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>translationjob36</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:56.709</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:56.739</t>
+        </is>
+      </c>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:57.077</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:58.972</t>
+        </is>
+      </c>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:59.038</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr">
+        <is>
+          <t>13:54:59.119</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="n">
+        <v>2263</v>
+      </c>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U420" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V420" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W420" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X420" s="2" t="n">
+        <v>2410</v>
+      </c>
+      <c r="Y420" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z420" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB420" s="2" t="inlineStr"/>
+      <c r="AC420" s="2" t="inlineStr"/>
+      <c r="AD420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>translationjob37</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>13:54:59.297</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="inlineStr">
+        <is>
+          <t>13:54:59.318</t>
+        </is>
+      </c>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>13:54:59.579</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="inlineStr">
+        <is>
+          <t>13:55:01.699</t>
+        </is>
+      </c>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>13:55:01.757</t>
+        </is>
+      </c>
+      <c r="O421" s="2" t="inlineStr">
+        <is>
+          <t>13:55:01.847</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>2402</v>
+      </c>
+      <c r="S421" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U421" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V421" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="W421" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X421" s="2" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Y421" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z421" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB421" s="2" t="inlineStr"/>
+      <c r="AC421" s="2" t="inlineStr"/>
+      <c r="AD421" s="2" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>translationjob38</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:02.017</t>
+        </is>
+      </c>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:02.035</t>
+        </is>
+      </c>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:02.291</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.282</t>
+        </is>
+      </c>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.445</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.513</t>
+        </is>
+      </c>
+      <c r="P422" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R422" s="2" t="n">
+        <v>2265</v>
+      </c>
+      <c r="S422" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="U422" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W422" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X422" s="2" t="n">
+        <v>2496</v>
+      </c>
+      <c r="Y422" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z422" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA422" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB422" s="2" t="inlineStr"/>
+      <c r="AC422" s="2" t="inlineStr"/>
+      <c r="AD422" s="2" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>translationjob39</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.683</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.700</t>
+        </is>
+      </c>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:04.932</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:06.570</t>
+        </is>
+      </c>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:06.625</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr">
+        <is>
+          <t>13:55:06.689</t>
+        </is>
+      </c>
+      <c r="P423" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>1887</v>
+      </c>
+      <c r="S423" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U423" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W423" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X423" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="Y423" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="Z423" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB423" s="2" t="inlineStr"/>
+      <c r="AC423" s="2" t="inlineStr"/>
+      <c r="AD423" s="2" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>translationjob40</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:06.752</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:06.770</t>
+        </is>
+      </c>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:07.020</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:08.616</t>
+        </is>
+      </c>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:08.673</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr">
+        <is>
+          <t>13:55:08.849</t>
+        </is>
+      </c>
+      <c r="P424" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>1864</v>
+      </c>
+      <c r="S424" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="T424" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U424" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="W424" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X424" s="2" t="n">
+        <v>2097</v>
+      </c>
+      <c r="Y424" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="Z424" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB424" s="2" t="inlineStr"/>
+      <c r="AC424" s="2" t="inlineStr"/>
+      <c r="AD424" s="2" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>translationjob41</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:09.040</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:09.062</t>
+        </is>
+      </c>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:09.343</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:11.000</t>
+        </is>
+      </c>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:11.067</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr">
+        <is>
+          <t>13:55:11.122</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="S425" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U425" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W425" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="Y425" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="Z425" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA425" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB425" s="2" t="inlineStr"/>
+      <c r="AC425" s="2" t="inlineStr"/>
+      <c r="AD425" s="2" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:24.868</t>
+        </is>
+      </c>
+      <c r="K426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:24.885</t>
+        </is>
+      </c>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:25.088</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.170</t>
+        </is>
+      </c>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.222</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.280</t>
+        </is>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R426" s="2" t="n">
+        <v>5302</v>
+      </c>
+      <c r="S426" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U426" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V426" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W426" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X426" s="2" t="n">
+        <v>5412</v>
+      </c>
+      <c r="Y426" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z426" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB426" s="2" t="inlineStr"/>
+      <c r="AC426" s="2" t="inlineStr"/>
+      <c r="AD426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.408</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.426</t>
+        </is>
+      </c>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:30.623</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.030</t>
+        </is>
+      </c>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.084</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.144</t>
+        </is>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>4622</v>
+      </c>
+      <c r="S427" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U427" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V427" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W427" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>4736</v>
+      </c>
+      <c r="Y427" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z427" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB427" s="2" t="inlineStr"/>
+      <c r="AC427" s="2" t="inlineStr"/>
+      <c r="AD427" s="2" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>translationjob48</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:32.382</t>
+        </is>
+      </c>
+      <c r="K428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:32.398</t>
+        </is>
+      </c>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:32.575</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.109</t>
+        </is>
+      </c>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.156</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.206</t>
+        </is>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="n">
+        <v>4727</v>
+      </c>
+      <c r="S428" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U428" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W428" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X428" s="2" t="n">
+        <v>4824</v>
+      </c>
+      <c r="Y428" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z428" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB428" s="2" t="inlineStr"/>
+      <c r="AC428" s="2" t="inlineStr"/>
+      <c r="AD428" s="2" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>translationjob49</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.307</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.323</t>
+        </is>
+      </c>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:35.490</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.531</t>
+        </is>
+      </c>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.575</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.695</t>
+        </is>
+      </c>
+      <c r="P429" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>5224</v>
+      </c>
+      <c r="S429" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="T429" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U429" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="W429" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>5388</v>
+      </c>
+      <c r="Y429" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z429" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB429" s="2" t="inlineStr"/>
+      <c r="AC429" s="2" t="inlineStr"/>
+      <c r="AD429" s="2" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>translationjob50</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.324</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.340</t>
+        </is>
+      </c>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:37.501</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:43.324</t>
+        </is>
+      </c>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:43.373</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr">
+        <is>
+          <t>15:20:43.421</t>
+        </is>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S430" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U430" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W430" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>6097</v>
+      </c>
+      <c r="Y430" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z430" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB430" s="2" t="inlineStr"/>
+      <c r="AC430" s="2" t="inlineStr"/>
+      <c r="AD430" s="2" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>translationjob51</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.817</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.832</t>
+        </is>
+      </c>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:40.996</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:48.424</t>
+        </is>
+      </c>
+      <c r="N431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:48.470</t>
+        </is>
+      </c>
+      <c r="O431" s="2" t="inlineStr">
+        <is>
+          <t>15:20:48.519</t>
+        </is>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>7607</v>
+      </c>
+      <c r="S431" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U431" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V431" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W431" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>7702</v>
+      </c>
+      <c r="Y431" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z431" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA431" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB431" s="2" t="inlineStr"/>
+      <c r="AC431" s="2" t="inlineStr"/>
+      <c r="AD431" s="2" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>translationjob52</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:03.636</t>
+        </is>
+      </c>
+      <c r="K432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:03.665</t>
+        </is>
+      </c>
+      <c r="L432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:04.061</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.119</t>
+        </is>
+      </c>
+      <c r="N432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.200</t>
+        </is>
+      </c>
+      <c r="O432" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.281</t>
+        </is>
+      </c>
+      <c r="P432" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q432" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>4483</v>
+      </c>
+      <c r="S432" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="U432" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V432" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W432" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>4645</v>
+      </c>
+      <c r="Y432" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z432" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB432" s="2" t="inlineStr"/>
+      <c r="AC432" s="2" t="inlineStr"/>
+      <c r="AD432" s="2" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>translationjob53</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.441</t>
+        </is>
+      </c>
+      <c r="K433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.457</t>
+        </is>
+      </c>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:08.685</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:11.728</t>
+        </is>
+      </c>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:11.845</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr">
+        <is>
+          <t>18:02:11.941</t>
+        </is>
+      </c>
+      <c r="P433" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q433" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>3287</v>
+      </c>
+      <c r="S433" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="U433" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="W433" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="Y433" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="Z433" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB433" s="2" t="inlineStr"/>
+      <c r="AC433" s="2" t="inlineStr"/>
+      <c r="AD433" s="2" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>translationjob54</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:12.109</t>
+        </is>
+      </c>
+      <c r="K434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:12.128</t>
+        </is>
+      </c>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:12.364</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:15.793</t>
+        </is>
+      </c>
+      <c r="N434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:15.858</t>
+        </is>
+      </c>
+      <c r="O434" s="2" t="inlineStr">
+        <is>
+          <t>18:02:15.933</t>
+        </is>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>3684</v>
+      </c>
+      <c r="S434" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U434" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V434" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W434" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>3824</v>
+      </c>
+      <c r="Y434" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z434" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB434" s="2" t="inlineStr"/>
+      <c r="AC434" s="2" t="inlineStr"/>
+      <c r="AD434" s="2" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>translationjob55</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:16.309</t>
+        </is>
+      </c>
+      <c r="K435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:16.329</t>
+        </is>
+      </c>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:16.697</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:21.819</t>
+        </is>
+      </c>
+      <c r="N435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:21.878</t>
+        </is>
+      </c>
+      <c r="O435" s="2" t="inlineStr">
+        <is>
+          <t>18:02:21.933</t>
+        </is>
+      </c>
+      <c r="P435" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="Q435" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>5510</v>
+      </c>
+      <c r="S435" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T435" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U435" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W435" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>5624</v>
+      </c>
+      <c r="Y435" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z435" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA435" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB435" s="2" t="inlineStr"/>
+      <c r="AC435" s="2" t="inlineStr"/>
+      <c r="AD435" s="2" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>translationjob56</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:22.174</t>
+        </is>
+      </c>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:22.190</t>
+        </is>
+      </c>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:22.474</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:27.566</t>
+        </is>
+      </c>
+      <c r="N436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:27.642</t>
+        </is>
+      </c>
+      <c r="O436" s="2" t="inlineStr">
+        <is>
+          <t>18:02:27.713</t>
+        </is>
+      </c>
+      <c r="P436" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q436" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R436" s="2" t="n">
+        <v>5392</v>
+      </c>
+      <c r="S436" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U436" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V436" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W436" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>5539</v>
+      </c>
+      <c r="Y436" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z436" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB436" s="2" t="inlineStr"/>
+      <c r="AC436" s="2" t="inlineStr"/>
+      <c r="AD436" s="2" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>translationjob57</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:25.786</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:25.808</t>
+        </is>
+      </c>
+      <c r="L437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:26.059</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:30.458</t>
+        </is>
+      </c>
+      <c r="N437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:30.526</t>
+        </is>
+      </c>
+      <c r="O437" s="2" t="inlineStr">
+        <is>
+          <t>18:02:30.590</t>
+        </is>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q437" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>4672</v>
+      </c>
+      <c r="S437" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U437" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W437" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X437" s="2" t="n">
+        <v>4804</v>
+      </c>
+      <c r="Y437" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z437" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB437" s="2" t="inlineStr"/>
+      <c r="AC437" s="2" t="inlineStr"/>
+      <c r="AD437" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD396"/>
+  <autoFilter ref="A1:AD437"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48984,7 +54150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -49251,6 +54417,46 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49262,7 +54468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -49271,6 +54477,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49302,6 +54509,11 @@
       <c r="F1" s="5" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
@@ -49318,6 +54530,9 @@
       <c r="F2" s="7" t="n">
         <v>662</v>
       </c>
+      <c r="G2" s="6" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -49332,6 +54547,9 @@
       <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -49346,6 +54564,7 @@
       <c r="F4" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -49360,6 +54579,9 @@
       <c r="F5" s="7" t="n">
         <v>558</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -49374,6 +54596,9 @@
       <c r="F6" s="6" t="n">
         <v>32</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -49388,6 +54613,9 @@
       <c r="F7" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -49402,6 +54630,9 @@
       <c r="F8" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -49416,6 +54647,9 @@
       <c r="F9" s="7" t="n">
         <v>45485</v>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>44689</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -49430,6 +54664,9 @@
       <c r="F10" s="7" t="n">
         <v>227</v>
       </c>
+      <c r="G10" s="7" t="n">
+        <v>22332</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -49444,6 +54681,9 @@
       <c r="F11" s="7" t="n">
         <v>3900</v>
       </c>
+      <c r="G11" s="7" t="n">
+        <v>3646</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -49458,6 +54698,9 @@
       <c r="F12" s="7" t="n">
         <v>808</v>
       </c>
+      <c r="G12" s="7" t="n">
+        <v>308</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -49472,6 +54715,9 @@
       <c r="F13" s="7" t="n">
         <v>578</v>
       </c>
+      <c r="G13" s="7" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -49485,6 +54731,9 @@
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="n">
         <v>10</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -49498,7 +54747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49672,6 +54921,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Translation Jobs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors by Date" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Translation Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Errors by Date" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD244"/>
+  <dimension ref="A1:AD250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30602,8 +30602,764 @@
       <c r="AC244" s="2" t="inlineStr"/>
       <c r="AD244" s="2" t="inlineStr"/>
     </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>translationjob42</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:16.617</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:16.637</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:17.068</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.260</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.338</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.414</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>5643</v>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U245" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V245" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="n">
+        <v>5797</v>
+      </c>
+      <c r="Y245" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z245" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA245" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.589</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.609</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:22.940</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:26.629</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:26.688</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>18:28:26.753</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="n">
+        <v>4040</v>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U246" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V246" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W246" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X246" s="2" t="n">
+        <v>4164</v>
+      </c>
+      <c r="Y246" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z246" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB246" s="2" t="inlineStr"/>
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:26.915</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:26.932</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:27.228</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:32.377</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:32.443</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>18:28:32.506</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="n">
+        <v>5462</v>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U247" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V247" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W247" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X247" s="2" t="n">
+        <v>5591</v>
+      </c>
+      <c r="Y247" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z247" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB247" s="2" t="inlineStr"/>
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:32.712</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:32.782</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:33.018</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:36.608</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:36.654</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>18:28:36.717</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="n">
+        <v>3896</v>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U248" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V248" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W248" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X248" s="2" t="n">
+        <v>4005</v>
+      </c>
+      <c r="Y248" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="Z248" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA248" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB248" s="2" t="inlineStr"/>
+      <c r="AC248" s="2" t="inlineStr"/>
+      <c r="AD248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:36.935</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:36.953</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:37.273</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.188</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.258</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.313</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="n">
+        <v>3253</v>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U249" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V249" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W249" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X249" s="2" t="n">
+        <v>3378</v>
+      </c>
+      <c r="Y249" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z249" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB249" s="2" t="inlineStr"/>
+      <c r="AC249" s="2" t="inlineStr"/>
+      <c r="AD249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>translationjob47</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.493</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.512</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:40.704</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:45.261</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:45.314</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>18:28:45.398</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="n">
+        <v>4768</v>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U250" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V250" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="W250" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X250" s="2" t="n">
+        <v>4905</v>
+      </c>
+      <c r="Y250" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z250" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA250" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB250" s="2" t="inlineStr"/>
+      <c r="AC250" s="2" t="inlineStr"/>
+      <c r="AD250" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD244"/>
+  <autoFilter ref="A1:AD250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30768,10 +31524,10 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0</v>
@@ -30854,7 +31610,7 @@
         <v>662</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -30950,7 +31706,7 @@
         <v>45485</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>44689</v>
+        <v>44773</v>
       </c>
     </row>
     <row r="10">
@@ -30964,7 +31720,7 @@
         <v>227</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>22332</v>
+        <v>22408</v>
       </c>
     </row>
     <row r="11">
@@ -30992,7 +31748,7 @@
         <v>808</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>308</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -31006,7 +31762,7 @@
         <v>578</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
@@ -31140,16 +31896,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0</v>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +54,20 @@
         <bgColor rgb="002E3345"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,16 +75,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -621,8 +654,764 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>translationjob142</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:07.803</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:07.818</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:24.456</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.003</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.041</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.219</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>16638</v>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16.6s</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>37200</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>37.2s</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>37416</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>37.4s</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>translationjob143</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>01:35:55.782</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>01:35:55.793</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>01:36:12.977</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.213</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.251</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.424</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>17184</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>17.2s</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>38431</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>38.4s</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>38642</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>38.6s</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>translationjob144</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>01:36:47.251</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>01:36:47.264</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>01:37:44.967</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>01:38:06.891</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>01:38:06.950</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>01:38:07.195</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>57703</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>57.7s</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>79640</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1m 19.6s</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>79944</v>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>1m 19.9s</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>translationjob145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>01:38:24.864</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>01:38:24.877</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>01:38:40.797</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>01:38:59.982</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>01:39:00.021</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>01:39:00.187</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>15920</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>15.9s</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>35118</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>35.1s</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>35323</v>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>35.3s</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>translationjob146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:11.457</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:11.470</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:27.446</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.430</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.473</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.632</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>15976</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>16.0s</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>41973</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>42.0s</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>42175</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>42.2s</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>translationjob147</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:04.332</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:04.345</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:22.123</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.786</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.820</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.991</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>17778</v>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>17.8s</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>42454</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>42.5s</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>42659</v>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>42.7s</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD1"/>
+  <autoFilter ref="A1:AD7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -633,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -649,54 +1438,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Stuck</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Retried</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Avg Duration</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Min Duration</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Max Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>46.0s</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>35.3s</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>1m 19.9s</t>
         </is>
       </c>
     </row>
@@ -711,17 +1540,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Error Category</t>
         </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Language copy not found</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>95728</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TicketAssemblyTranslationServiceImpl</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ReplicationSquadListener</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>30119</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ResourceUtils commit</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>LockUtil contention</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TranslateHrefAttributes</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Error executing workflow</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -748,40 +1653,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Total Entries</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Obtained</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Expires</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Token Size Entries</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1410,8 +1410,764 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>translationjob142</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:07.803</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:07.818</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:24.456</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.003</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.041</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>01:35:45.219</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>16638</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>16.6s</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>37200</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>37.2s</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>37416</v>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>37.4s</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>translationjob143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>01:35:55.782</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>01:35:55.793</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>01:36:12.977</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.213</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.251</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>01:36:34.424</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>17184</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>17.2s</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>38431</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>38.4s</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>38642</v>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>38.6s</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>translationjob144</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>01:36:47.251</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>01:36:47.264</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>01:37:44.967</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>01:38:06.891</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>01:38:06.950</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>01:38:07.195</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>57703</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>57.7s</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>79640</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1m 19.6s</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>79944</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>1m 19.9s</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>translationjob145</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>01:38:24.864</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>01:38:24.877</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>01:38:40.797</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>01:38:59.982</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>01:39:00.021</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>01:39:00.187</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>15920</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>15.9s</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>35118</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>35.1s</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>35323</v>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>35.3s</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>translationjob146</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:11.457</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:11.470</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:27.446</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.430</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.473</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>01:39:53.632</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>15976</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>16.0s</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>41973</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>42.0s</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>42175</v>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>42.2s</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>translationjob147</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:04.332</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:04.345</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:22.123</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.786</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.820</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>01:40:46.991</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>17778</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>17.8s</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>42454</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>42.5s</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>42659</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>42.7s</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD7"/>
+  <autoFilter ref="A1:AD13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1422,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1529,6 +2285,46 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>46.0s</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>35.3s</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>1m 19.9s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1540,11 +2336,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1558,6 +2355,11 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1568,6 +2370,9 @@
       <c r="B2" s="5" t="n">
         <v>95728</v>
       </c>
+      <c r="C2" s="5" t="n">
+        <v>129524</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1578,6 +2383,9 @@
       <c r="B3" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="C3" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1588,6 +2396,9 @@
       <c r="B4" s="5" t="n">
         <v>30119</v>
       </c>
+      <c r="C4" s="5" t="n">
+        <v>48161</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1598,6 +2409,9 @@
       <c r="B5" s="5" t="n">
         <v>1360</v>
       </c>
+      <c r="C5" s="5" t="n">
+        <v>2532</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1608,6 +2422,9 @@
       <c r="B6" s="5" t="n">
         <v>136</v>
       </c>
+      <c r="C6" s="5" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1618,6 +2435,9 @@
       <c r="B7" s="4" t="n">
         <v>95</v>
       </c>
+      <c r="C7" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1627,6 +2447,20 @@
       </c>
       <c r="B8" s="4" t="n">
         <v>21</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ThumbnailServlet</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="n">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +2474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1714,6 +2548,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1410,764 +1410,8 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>translationjob142</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>DE-DE</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:07.803</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:07.818</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:24.456</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:45.003</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:45.041</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>01:35:45.219</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>16638</v>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>16.6s</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>37200</v>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>37.2s</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0.0s</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>37416</v>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>37.4s</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>translationjob143</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>PT-PT</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>01:35:55.782</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>01:35:55.793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>01:36:12.977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>01:36:34.213</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>01:36:34.251</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>01:36:34.424</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>17184</v>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>17.2s</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>38431</v>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>38.4s</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0.0s</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>38642</v>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>38.6s</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr"/>
-      <c r="AD9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>translationjob144</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>EN-US</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>01:36:47.251</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>01:36:47.264</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>01:37:44.967</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>01:38:06.891</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>01:38:06.950</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>01:38:07.195</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>57703</v>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>57.7s</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>79640</v>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1m 19.6s</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0.1s</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>79944</v>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>1m 19.9s</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
-      <c r="AD10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>translationjob145</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>AR-AE</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>01:38:24.864</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>01:38:24.877</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>01:38:40.797</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>01:38:59.982</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>01:39:00.021</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>01:39:00.187</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>15920</v>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>15.9s</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>35118</v>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>35.1s</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0.0s</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>35323</v>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>35.3s</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr"/>
-      <c r="AD11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>translationjob146</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>FR-FR</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:11.457</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:11.470</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:27.446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:53.430</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:53.473</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>01:39:53.632</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>15976</v>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>16.0s</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>41973</v>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>42.0s</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0.0s</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>42175</v>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>42.2s</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr"/>
-      <c r="AD12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>translationjob147</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Ignacio Ai Translation Project</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>JA-JP</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>es_es</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>rmcf-ai-translatorion-connector</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>MACHINE_TRANSLATION</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:04.332</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:04.345</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:22.123</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:46.786</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:46.820</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>01:40:46.991</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>17778</v>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>17.8s</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>42454</v>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>42.5s</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0.0s</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>0.2s</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>42659</v>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>42.7s</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr"/>
-      <c r="AD13" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AD13"/>
+  <autoFilter ref="A1:AD7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2178,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2285,46 +1529,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>46.0s</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>35.3s</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>1m 19.9s</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2336,12 +1540,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2355,11 +1558,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2368,99 +1566,77 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>95728</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>129524</v>
+        <v>143349</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TicketAssemblyTranslationServiceImpl</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>8</v>
+          <t>ThumbnailServlet</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ReplicationSquadListener</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>30119</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>48161</v>
+          <t>TicketAssemblyTranslationServiceImpl</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ResourceUtils commit</t>
+          <t>ReplicationSquadListener</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1360</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2532</v>
+        <v>51234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>LockUtil contention</t>
+          <t>ResourceUtils commit</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>136</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TranslateHrefAttributes</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>95</v>
+          <t>LockUtil contention</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Error executing workflow</t>
+          <t>TranslateHrefAttributes</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ThumbnailServlet</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="5" t="n">
-        <v>134</v>
+          <t>Error executing workflow</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2474,7 +1650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2548,31 +1724,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
         <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,15 +99,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -657,7 +664,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -783,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -909,7 +916,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1035,7 +1042,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1161,7 +1168,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1287,7 +1294,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1410,8 +1417,6366 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>translationjob59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:16.760</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:16.775</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:17.152</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:24.542</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:24.578</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>12:34:24.651</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>7782</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>7891</v>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>translationjob60</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:24.811</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:24.825</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:25.150</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.137</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.185</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.280</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>7326</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>translationjob61</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.403</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.416</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:32.742</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:39.060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:39.098</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>12:34:39.184</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>6657</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>6781</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>translationjob62</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>12:34:39.296</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>12:34:39.307</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>12:34:39.597</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>translationjob64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>12:34:54.900</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12:34:54.911</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12:34:55.229</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12:35:04.720</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>12:35:04.754</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>12:35:04.840</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>9820</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>9940</v>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>translationjob140</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:18.359</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:18.376</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:19.020</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:25.872</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:25.926</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>14:37:26.036</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>7513</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>7677</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>translationjob141</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:23.602</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:23.626</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:24.101</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:26.459</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:26.539</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>14:37:27.825</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>2857</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>1286</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>4223</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>translationjob142</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:26.519</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:28.427</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:28.670</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:33.249</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:33.312</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>14:37:33.425</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>6730</v>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>6906</v>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>translationjob143</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:29.115</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:29.130</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:29.751</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:35.264</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:35.318</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>14:37:35.427</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>6149</v>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>6312</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>translationjob144</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>14:37:33.840</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>14:37:33.856</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>14:37:33.974</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr"/>
+      <c r="V17" s="3" t="inlineStr"/>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr"/>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>translationjob145</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:36.035</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:36.054</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:36.437</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:43.071</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:43.130</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>14:37:43.235</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>7036</v>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>translationjob146</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:41.610</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:41.627</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:41.802</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.157</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.348</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.418</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>2547</v>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>2808</v>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>translationjob147</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:43.600</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:43.623</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.167</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.775</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.835</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.975</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>8175</v>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>8375</v>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>translationjob148</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.880</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:44.903</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:45.086</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:46.972</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:47.023</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>14:37:47.072</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>2092</v>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>2192</v>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>translationjob149</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:47.430</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:47.448</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:47.926</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:49.609</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:49.657</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>14:37:49.712</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>478</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>2179</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>2282</v>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>translationjob150</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:49.842</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:50.141</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:50.711</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.674</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.724</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.775</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>1832</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>1933</v>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>translationjob151</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.062</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.080</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:51.247</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:53.515</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:53.712</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>14:37:53.760</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>2453</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>2698</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>translationjob152</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>14:37:52.404</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>14:37:52.406</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>14:37:53.171</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>14:38:05.813</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14:38:05.868</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>14:38:06.015</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>765</v>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>13409</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>13611</v>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>translationjob149</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.756</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.778</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.947</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:56.605</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:56.663</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>16:16:56.726</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>5849</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>5970</v>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>translationjob150</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>16:16:57.186</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>16:16:57.208</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>16:16:57.403</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>16:17:02.680</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>16:17:02.734</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>16:17:02.813</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>5494</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>5627</v>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>translationjob151</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:03.170</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:03.185</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:03.520</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:13.036</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:13.115</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>16:17:13.197</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>9866</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>10027</v>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>translationjob152</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:13.585</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:13.600</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:14.145</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:21.015</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:21.095</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>16:17:21.195</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>7430</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>7610</v>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>translationjob153</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:21.794</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:21.809</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:22.127</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:31.236</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:31.298</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>16:17:31.380</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>9442</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>9586</v>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>translationjob154</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>16:20:24.934</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>16:20:24.950</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>16:20:32.119</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>16:21:12.166</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>16:21:12.215</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>16:21:13.507</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>7169</v>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>47232</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>47.2s</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>1292</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>48573</v>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>48.6s</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>translationjob155</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:06.666</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:06.681</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:06.852</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:22.079</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:22.119</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>16:21:22.175</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>15413</v>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>15.4s</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>15509</v>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>15.5s</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>translationjob156</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>16:21:18.126</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>16:21:22.500</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>16:21:24.863</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>16:22:00.402</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>2363</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>42276</v>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>42.3s</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>translationjob158</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:00.917</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:00.936</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:01.092</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:11.781</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:11.826</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>16:22:11.922</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>10864</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10.9s</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>11005</v>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>translationjob159</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>16:22:12.391</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>16:22:12.413</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>16:22:18.654</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>16:23:10.507</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="n">
+        <v>6241</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>58116</v>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>58.1s</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>translationjob160</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>16:22:21.431</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>16:22:21.463</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>16:22:28.597</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>16:23:06.722</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>16:23:06.776</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>16:23:07.785</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>7134</v>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>45.3s</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>46354</v>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>46.4s</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>translationjob161</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:11.021</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:11.038</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:11.231</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:26.384</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:26.557</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>16:23:26.613</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>15363</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>15.4s</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>15592</v>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>15.6s</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>translationjob162</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>16:23:13.192</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>16:23:13.207</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>16:23:21.301</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>16:24:02.754</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>16:24:02.804</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>16:24:03.879</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>8094</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>49562</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>49.6s</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>50687</v>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>50.7s</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>translationjob163</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:27.153</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:27.173</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:27.557</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:53.892</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:53.940</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>16:23:53.986</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>26739</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>26.7s</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>26833</v>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>26.8s</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>translationjob164</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:36.989</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:37.021</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:37.357</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:39.580</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:39.694</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>18:04:39.777</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>2591</v>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>2788</v>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>translationjob165</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:40.262</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:40.281</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:40.550</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:42.548</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:42.607</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>18:04:42.680</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>2286</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>2418</v>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>translationjob166</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:43.303</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:43.330</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:43.654</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:45.802</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:45.903</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>18:04:45.967</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>2499</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>2664</v>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>translationjob167</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:46.476</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:46.503</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:46.880</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:48.831</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:48.914</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>18:04:48.978</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>2355</v>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>2502</v>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>translationjob168</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>18:04:49.455</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>18:04:49.477</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>18:04:49.711</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AC44" s="3" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>translationjob169</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:53.061</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:53.087</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:53.494</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:55.641</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:55.722</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>18:04:55.782</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>2580</v>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>2721</v>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>translationjob170</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>22:00:17.734</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>22:00:17.760</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>22:00:18.015</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>translationjob171</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.577</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.604</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.859</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:26.718</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:26.788</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>22:00:26.850</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>4141</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>4273</v>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>translationjob172</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:27.387</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:27.413</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:27.675</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:30.834</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:30.937</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>22:00:31.013</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>3447</v>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>3626</v>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>translationjob173</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:31.528</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:31.549</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:31.780</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:35.794</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:35.879</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>22:00:35.945</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>4266</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>4417</v>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>translationjob174</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:36.527</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:36.557</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:36.808</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.062</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.126</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.193</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>5535</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>5666</v>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>translationjob175</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.673</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.693</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:42.921</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:48.362</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:48.421</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>22:00:48.490</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>5689</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>5817</v>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>translationjob176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:19.666</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:19.683</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:20.542</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:27.277</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:27.331</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>23:01:27.572</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>7611</v>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>7906</v>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>translationjob177</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:28.027</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:28.042</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:28.700</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:34.399</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:34.445</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>23:01:34.643</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>6372</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>6616</v>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>translationjob178</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:35.057</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:35.077</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:36.527</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:41.977</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:42.017</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>23:01:44.290</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>6920</v>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>2273</v>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>9233</v>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>translationjob179</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:44.736</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:44.753</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:45.214</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:51.615</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:51.661</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>23:01:51.894</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>6879</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="n">
+        <v>7158</v>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>translationjob180</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:52.298</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:52.314</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:52.790</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:58.742</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:58.936</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>23:01:59.138</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>6444</v>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="n">
+        <v>6840</v>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>translationjob181</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>23:01:59.565</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>23:01:59.585</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>23:02:00.155</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr"/>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="3" t="inlineStr"/>
+      <c r="AC57" s="3" t="inlineStr"/>
+      <c r="AD57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>translationjob63</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>12:34:46.014</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>12:34:54.689</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>12:34:54.727</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:34:54.816</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>translationjob148</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.226</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.275</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:16:50.336</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>translationjob157</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>16:21:38.618</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>16:22:04.037</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>16:22:04.090</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:22:05.416</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>1326</v>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD7"/>
+  <autoFilter ref="A1:AD60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1438,92 +7803,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Stuck</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Retried</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Avg Duration</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Min Duration</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Max Duration</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>46.0s</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>35.3s</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>14.3s</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>1m 19.9s</t>
         </is>
@@ -1540,7 +7905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1548,95 +7913,145 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Error Category</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Language copy not found</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
-        <v>143349</v>
+      <c r="B2" s="6" t="n">
+        <v>380300</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ThumbnailServlet</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Failed to start translation</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TicketAssemblyTranslationServiceImpl</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Error processing Translation project</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ReplicationSquadListener</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>TranslationCleanupJobConsumer</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>51234</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ResourceUtils commit</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>5694</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ThumbnailServlet</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>492</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>LockUtil contention</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TicketAssemblyTranslationServiceImpl</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TranslateHrefAttributes</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>95</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>GCCScriptProcessor</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ReplicationSquadListener</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>220470</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ReplicationNewsAssemblyListener</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>23122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ResourceUtils commit</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>26165</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>LockUtil contention</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TranslateHrefAttributes</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Error executing workflow</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>320</v>
+      <c r="B14" s="6" t="n">
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -1663,64 +8078,64 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Entries</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Obtained</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Expires</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Token Size Entries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>896</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7775,8 +7775,7034 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>translationjob106</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:57.301</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:57.317</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:57.607</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:59.659</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:59.723</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>11:34:59.824</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>2358</v>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="n">
+        <v>2523</v>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>translationjob107</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:00.048</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:00.067</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:00.272</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:02.461</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:02.526</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>11:35:02.610</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>2413</v>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>2562</v>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>translationjob108</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:02.835</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:02.852</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:03.071</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:05.797</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:05.846</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>11:35:05.951</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>2962</v>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>3116</v>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>translationjob109</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:06.228</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:06.246</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:06.464</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:08.961</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:09.013</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>11:35:09.117</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>2733</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>2889</v>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>translationjob110</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:09.513</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:09.535</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:09.779</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:12.056</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:12.121</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>11:35:12.186</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>2543</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="n">
+        <v>2673</v>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>translationjob182</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:35.006</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:35.032</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:35.459</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:46.839</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:46.918</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.086</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>11833</v>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>11.8s</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="n">
+        <v>12080</v>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>12.1s</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>translationjob183</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.394</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.414</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.827</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.266</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.359</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.515</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>5872</v>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>6121</v>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>translationjob184</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.848</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.869</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>12:15:54.301</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>12:16:00.185</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:16:00.248</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>12:16:00.417</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>6337</v>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="n">
+        <v>6569</v>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>translationjob185</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:00.727</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:00.750</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:01.460</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:09.911</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:10.064</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>12:16:10.218</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>9184</v>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="n">
+        <v>9491</v>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>9.5s</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>translationjob186</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:10.537</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:10.559</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:11.004</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:16.336</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:16.400</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>12:16:16.543</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>5799</v>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="n">
+        <v>6006</v>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>translationjob187</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:16.996</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:17.028</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:17.662</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:26.691</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:26.779</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>12:16:26.947</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>9695</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="n">
+        <v>9951</v>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>translationjob111</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:15.455</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:15.475</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:15.898</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:24.167</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:24.264</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:27:24.548</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>8712</v>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="n">
+        <v>9093</v>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>translationjob112</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:24.799</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:24.819</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:25.286</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:32.318</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:32.390</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:27:32.552</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>7519</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>translationjob113</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:32.776</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:32.809</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:33.276</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:40.357</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:40.483</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>14:27:40.693</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>7581</v>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="n">
+        <v>7917</v>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>translationjob114</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:40.900</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:40.931</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:41.323</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:51.420</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:51.486</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>14:27:51.701</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>10520</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>10.5s</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="n">
+        <v>10801</v>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>10.8s</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>translationjob115</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>14:27:51.973</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>14:27:51.994</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>14:27:52.454</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>14:28:00.955</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>14:28:01.033</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>14:28:01.224</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>8982</v>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="n">
+        <v>9251</v>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>translationjob116</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:01.426</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:01.452</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:02.062</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:14.029</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:14.094</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>14:28:14.309</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>12603</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="n">
+        <v>12883</v>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>12.9s</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>translationjob188</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:34.605</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:34.621</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:34.946</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:41.373</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:41.422</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>15:39:41.574</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="n">
+        <v>6969</v>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>translationjob189</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:41.921</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:41.939</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:42.231</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:47.965</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:48.031</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>15:39:48.160</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>6044</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="n">
+        <v>6239</v>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>translationjob190</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>15:39:48.400</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>15:39:48.418</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>15:39:48.702</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr"/>
+      <c r="S80" s="3" t="inlineStr"/>
+      <c r="T80" s="3" t="inlineStr"/>
+      <c r="U80" s="3" t="inlineStr"/>
+      <c r="V80" s="3" t="inlineStr"/>
+      <c r="W80" s="3" t="inlineStr"/>
+      <c r="X80" s="3" t="inlineStr"/>
+      <c r="Y80" s="3" t="inlineStr"/>
+      <c r="Z80" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB80" s="3" t="inlineStr"/>
+      <c r="AC80" s="3" t="inlineStr"/>
+      <c r="AD80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>translationjob192</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:00.726</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:00.744</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:01.061</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:07.995</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:08.051</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>15:40:08.171</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>7269</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="n">
+        <v>7445</v>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>translationjob193</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:08.443</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:08.459</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:08.932</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:17.090</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:17.143</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>15:40:17.343</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>8647</v>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>translationjob154</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.420</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.431</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.570</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:47.672</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:47.726</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:43:47.770</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>2252</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="n">
+        <v>2350</v>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>translationjob155</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:47.938</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:47.950</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:48.086</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:51.993</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:52.032</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:43:52.074</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>4055</v>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="n">
+        <v>4136</v>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>translationjob156</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:50.222</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:50.238</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:50.436</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.256</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.295</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.340</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>3034</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="n">
+        <v>3118</v>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>translationjob157</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:52.247</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:52.262</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:52.403</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:56.512</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:56.548</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:43:56.587</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>4265</v>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="n">
+        <v>4340</v>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>translationjob158</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.517</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.530</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:53.678</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:57.572</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:57.618</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>19:43:57.665</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>4055</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="n">
+        <v>4148</v>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>translationjob159</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:44.080</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:44.092</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:44.218</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:46.881</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:46.913</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:44:46.959</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>2801</v>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="n">
+        <v>2879</v>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>translationjob160</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:47.211</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:47.227</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:47.352</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:50.077</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:50.111</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:44:50.154</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>2866</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="n">
+        <v>2943</v>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>translationjob161</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>19:44:50.301</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>19:44:50.316</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>19:44:50.452</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr"/>
+      <c r="S90" s="3" t="inlineStr"/>
+      <c r="T90" s="3" t="inlineStr"/>
+      <c r="U90" s="3" t="inlineStr"/>
+      <c r="V90" s="3" t="inlineStr"/>
+      <c r="W90" s="3" t="inlineStr"/>
+      <c r="X90" s="3" t="inlineStr"/>
+      <c r="Y90" s="3" t="inlineStr"/>
+      <c r="Z90" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" s="3" t="inlineStr"/>
+      <c r="AC90" s="3" t="inlineStr"/>
+      <c r="AD90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>translationjob162</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>19:44:51.363</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>19:44:51.379</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>19:44:51.526</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr"/>
+      <c r="S91" s="3" t="inlineStr"/>
+      <c r="T91" s="3" t="inlineStr"/>
+      <c r="U91" s="3" t="inlineStr"/>
+      <c r="V91" s="3" t="inlineStr"/>
+      <c r="W91" s="3" t="inlineStr"/>
+      <c r="X91" s="3" t="inlineStr"/>
+      <c r="Y91" s="3" t="inlineStr"/>
+      <c r="Z91" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB91" s="3" t="inlineStr"/>
+      <c r="AC91" s="3" t="inlineStr"/>
+      <c r="AD91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>translationjob165</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:19.110</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:19.124</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:19.496</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:28.913</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:28.993</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:47:29.124</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>9803</v>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="n">
+        <v>10014</v>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>translationjob168</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>19:47:29.314</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>19:47:29.331</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>19:47:29.670</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>19:47:29.890</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>576</v>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="T93" s="3" t="inlineStr"/>
+      <c r="U93" s="3" t="inlineStr"/>
+      <c r="V93" s="3" t="inlineStr"/>
+      <c r="W93" s="3" t="inlineStr"/>
+      <c r="X93" s="3" t="inlineStr"/>
+      <c r="Y93" s="3" t="inlineStr"/>
+      <c r="Z93" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" s="3" t="inlineStr"/>
+      <c r="AC93" s="3" t="inlineStr"/>
+      <c r="AD93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>translationjob169</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:30.085</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:30.099</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:30.401</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:39.568</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:39.603</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:47:39.729</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>9483</v>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>9.5s</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="n">
+        <v>9644</v>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>translationjob170</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:34.100</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:34.113</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:34.344</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.337</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.379</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.473</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>10237</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="n">
+        <v>10373</v>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>translationjob171</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:39.916</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:39.930</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:40.233</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:48.641</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:48.683</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:47:48.777</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="n">
+        <v>8861</v>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>translationjob172</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.655</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.667</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:44.921</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:55.212</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:55.256</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:47:55.359</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>10557</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="n">
+        <v>10704</v>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>translationjob173</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>19:47:48.965</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>19:47:48.978</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>19:47:49.295</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>19:47:49.486</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr"/>
+      <c r="O98" s="3" t="inlineStr"/>
+      <c r="P98" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="S98" s="3" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="T98" s="3" t="inlineStr"/>
+      <c r="U98" s="3" t="inlineStr"/>
+      <c r="V98" s="3" t="inlineStr"/>
+      <c r="W98" s="3" t="inlineStr"/>
+      <c r="X98" s="3" t="inlineStr"/>
+      <c r="Y98" s="3" t="inlineStr"/>
+      <c r="Z98" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="3" t="inlineStr"/>
+      <c r="AC98" s="3" t="inlineStr"/>
+      <c r="AD98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>translationjob174</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>22:51:44.602</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>22:51:44.618</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>22:51:44.793</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr"/>
+      <c r="S99" s="3" t="inlineStr"/>
+      <c r="T99" s="3" t="inlineStr"/>
+      <c r="U99" s="3" t="inlineStr"/>
+      <c r="V99" s="3" t="inlineStr"/>
+      <c r="W99" s="3" t="inlineStr"/>
+      <c r="X99" s="3" t="inlineStr"/>
+      <c r="Y99" s="3" t="inlineStr"/>
+      <c r="Z99" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="3" t="inlineStr"/>
+      <c r="AC99" s="3" t="inlineStr"/>
+      <c r="AD99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>translationjob176</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:52.221</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:52.233</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:52.372</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:58.652</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:58.696</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>22:51:58.735</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>6431</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>translationjob177</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.720</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.731</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.914</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.012</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.077</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.116</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>3292</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="n">
+        <v>3396</v>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>translationjob178</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.282</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.295</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>22:51:57.421</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>22:52:04.312</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>22:52:04.344</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>22:52:04.381</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>7030</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="n">
+        <v>7099</v>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>translationjob179</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>22:51:58.894</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>22:51:58.907</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>22:51:59.049</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>22:52:03.319</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>22:52:03.360</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>22:52:03.405</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>4425</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="n">
+        <v>4511</v>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>translationjob180</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:00.688</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:00.704</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:01.025</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:09.689</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:09.730</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>23:00:09.842</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>9001</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="n">
+        <v>9154</v>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>translationjob181</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>23:00:06.590</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>23:00:06.604</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>23:00:07.042</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>23:00:07.249</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr"/>
+      <c r="P105" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R105" s="3" t="n">
+        <v>659</v>
+      </c>
+      <c r="S105" s="3" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="T105" s="3" t="inlineStr"/>
+      <c r="U105" s="3" t="inlineStr"/>
+      <c r="V105" s="3" t="inlineStr"/>
+      <c r="W105" s="3" t="inlineStr"/>
+      <c r="X105" s="3" t="inlineStr"/>
+      <c r="Y105" s="3" t="inlineStr"/>
+      <c r="Z105" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="3" t="inlineStr"/>
+      <c r="AC105" s="3" t="inlineStr"/>
+      <c r="AD105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>translationjob182</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:07.535</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:07.550</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:07.851</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.578</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.623</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.741</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>19043</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>19.0s</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="n">
+        <v>19206</v>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>19.2s</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>translationjob183</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>23:00:10.016</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>23:00:10.031</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>23:00:10.360</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>23:00:10.583</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr"/>
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R107" s="3" t="n">
+        <v>567</v>
+      </c>
+      <c r="S107" s="3" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="T107" s="3" t="inlineStr"/>
+      <c r="U107" s="3" t="inlineStr"/>
+      <c r="V107" s="3" t="inlineStr"/>
+      <c r="W107" s="3" t="inlineStr"/>
+      <c r="X107" s="3" t="inlineStr"/>
+      <c r="Y107" s="3" t="inlineStr"/>
+      <c r="Z107" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="3" t="inlineStr"/>
+      <c r="AC107" s="3" t="inlineStr"/>
+      <c r="AD107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>translationjob184</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:10.777</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:10.791</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:11.100</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.001</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.043</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.171</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>8224</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="n">
+        <v>8394</v>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>translationjob185</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.333</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.347</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.637</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:32.420</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:32.549</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>23:00:32.671</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>13087</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>13.1s</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="n">
+        <v>13338</v>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>translationjob186</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.979</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.995</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>23:00:35.846</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>23:00:35.887</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>23:00:36.005</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="n">
+        <v>8867</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="n">
+        <v>9026</v>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>translationjob187</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>23:00:32.852</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>23:00:32.869</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>23:00:33.334</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>23:00:33.579</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="3" t="n">
+        <v>465</v>
+      </c>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R111" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="T111" s="3" t="inlineStr"/>
+      <c r="U111" s="3" t="inlineStr"/>
+      <c r="V111" s="3" t="inlineStr"/>
+      <c r="W111" s="3" t="inlineStr"/>
+      <c r="X111" s="3" t="inlineStr"/>
+      <c r="Y111" s="3" t="inlineStr"/>
+      <c r="Z111" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" s="3" t="inlineStr"/>
+      <c r="AC111" s="3" t="inlineStr"/>
+      <c r="AD111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>translationjob188</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:33.882</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:33.898</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:34.187</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:47.756</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:47.929</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>23:00:48.094</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>13874</v>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>13.9s</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>14.2s</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>translationjob189</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>23:00:36.163</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>23:00:36.177</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>23:00:36.517</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>23:00:36.783</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr"/>
+      <c r="P113" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R113" s="3" t="n">
+        <v>620</v>
+      </c>
+      <c r="S113" s="3" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="T113" s="3" t="inlineStr"/>
+      <c r="U113" s="3" t="inlineStr"/>
+      <c r="V113" s="3" t="inlineStr"/>
+      <c r="W113" s="3" t="inlineStr"/>
+      <c r="X113" s="3" t="inlineStr"/>
+      <c r="Y113" s="3" t="inlineStr"/>
+      <c r="Z113" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" s="3" t="inlineStr"/>
+      <c r="AC113" s="3" t="inlineStr"/>
+      <c r="AD113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>translationjob105</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>11:34:56.823</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>11:34:56.887</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>11:34:56.952</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr"/>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>translationjob191</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>15:40:00.151</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>15:40:00.199</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>15:40:00.359</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr"/>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>translationjob153</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.172</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.214</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>19:43:45.263</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr"/>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>translationjob163</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>19:44:58.383</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>19:44:58.427</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>19:44:58.487</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V117" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr"/>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>translationjob164</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>19:44:59.442</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>19:44:59.478</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>19:44:59.517</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr"/>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>translationjob167</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>19:47:33.705</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>19:47:33.748</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>19:47:33.858</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V119" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr"/>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>translationjob175</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.435</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.481</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>22:51:53.524</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr"/>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD60"/>
+  <autoFilter ref="A1:AD120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7787,7 +14813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7894,6 +14920,46 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>19.2s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7905,11 +14971,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7923,6 +14990,11 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -7933,6 +15005,9 @@
       <c r="B2" s="6" t="n">
         <v>380300</v>
       </c>
+      <c r="C2" s="6" t="n">
+        <v>289168</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -7943,6 +15018,9 @@
       <c r="B3" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -7953,6 +15031,9 @@
       <c r="B4" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="C4" s="5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -7963,6 +15044,9 @@
       <c r="B5" s="5" t="n">
         <v>17</v>
       </c>
+      <c r="C5" s="6" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -7973,6 +15057,9 @@
       <c r="B6" s="6" t="n">
         <v>492</v>
       </c>
+      <c r="C6" s="6" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7983,6 +15070,9 @@
       <c r="B7" s="5" t="n">
         <v>70</v>
       </c>
+      <c r="C7" s="5" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7993,6 +15083,9 @@
       <c r="B8" s="5" t="n">
         <v>32</v>
       </c>
+      <c r="C8" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8003,6 +15096,9 @@
       <c r="B9" s="6" t="n">
         <v>220470</v>
       </c>
+      <c r="C9" s="6" t="n">
+        <v>167143</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8013,6 +15109,9 @@
       <c r="B10" s="6" t="n">
         <v>23122</v>
       </c>
+      <c r="C10" s="6" t="n">
+        <v>13518</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8023,6 +15122,9 @@
       <c r="B11" s="6" t="n">
         <v>26165</v>
       </c>
+      <c r="C11" s="6" t="n">
+        <v>18348</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -8033,6 +15135,9 @@
       <c r="B12" s="6" t="n">
         <v>2285</v>
       </c>
+      <c r="C12" s="6" t="n">
+        <v>1168</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -8043,6 +15148,9 @@
       <c r="B13" s="6" t="n">
         <v>1118</v>
       </c>
+      <c r="C13" s="6" t="n">
+        <v>822</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -8052,6 +15160,9 @@
       </c>
       <c r="B14" s="6" t="n">
         <v>1163</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -8065,7 +15176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8139,6 +15250,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AD183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14801,8 +14801,7810 @@
       <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:24.481</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:24.500</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:24.689</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:26.487</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:26.550</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>10:12:26.643</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="n">
+        <v>2162</v>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:26.977</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:26.996</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:27.178</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:29.642</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:29.695</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>10:12:29.741</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>2665</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="n">
+        <v>2764</v>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:30.004</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:30.029</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:30.226</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:32.565</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:32.700</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>10:12:32.763</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>2561</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="n">
+        <v>2759</v>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:33.013</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:33.035</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:33.234</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.209</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.348</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.401</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>2196</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="n">
+        <v>2388</v>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.646</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.664</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:35.839</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:37.910</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:37.972</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>10:12:38.040</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>2264</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="n">
+        <v>2394</v>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:41.850</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:41.868</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:42.064</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:45.989</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.022</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.065</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>4139</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="n">
+        <v>4215</v>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.268</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.283</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.411</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.122</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.161</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.202</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>2854</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="n">
+        <v>2934</v>
+      </c>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z127" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.406</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.418</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:49.554</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.631</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.662</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.706</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>3225</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.912</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.923</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:53.050</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:55.677</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:55.712</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>10:33:55.747</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>2765</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="n">
+        <v>2835</v>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:55.925</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:55.937</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:56.065</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.873</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.906</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.943</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>2948</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="n">
+        <v>3018</v>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>10:33:59.140</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>10:33:59.153</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>10:33:59.281</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>10:34:02.843</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>10:34:02.885</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>10:34:02.922</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>3703</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="n">
+        <v>3782</v>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:17.408</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:17.422</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:17.755</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.675</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.716</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.770</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>2267</v>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="n">
+        <v>2362</v>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.842</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.854</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:19.982</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.398</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.435</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.474</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>1556</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.628</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.640</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:21.760</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:23.810</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:23.846</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>10:45:23.880</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>2182</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="n">
+        <v>2252</v>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="Z134" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:24.031</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:24.042</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:24.218</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:26.201</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:26.231</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>10:45:26.264</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>2170</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="n">
+        <v>2233</v>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:01.062</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:01.075</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:01.227</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:05.963</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:06.006</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>11:08:06.046</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>4901</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="n">
+        <v>4984</v>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:07.839</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:07.861</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:08.251</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:15.657</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:15.705</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>12:13:15.811</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>7818</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="n">
+        <v>7972</v>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:16.068</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:16.085</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:16.468</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:22.097</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:22.143</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>12:13:22.265</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>6029</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="n">
+        <v>6197</v>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:22.551</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:22.566</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:23.095</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:28.315</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:28.362</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>12:13:28.461</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>5764</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="n">
+        <v>5910</v>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:28.738</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:28.753</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:29.136</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:35.308</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:35.357</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>12:13:35.456</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>6570</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="n">
+        <v>6718</v>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:35.693</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:35.711</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:36.044</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.184</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.254</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.354</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>5491</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="n">
+        <v>5661</v>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.608</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.623</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:41.985</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:49.199</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:49.295</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>12:13:49.376</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>7591</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>7768</v>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>15:20:58.404</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>15:20:58.421</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>15:20:58.755</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>15:21:01.313</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>15:21:01.370</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>15:21:01.423</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>2909</v>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="n">
+        <v>3019</v>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>translationjob23</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>15:21:01.660</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>15:21:01.673</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>15:21:01.866</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr"/>
+      <c r="N144" s="3" t="inlineStr"/>
+      <c r="O144" s="3" t="inlineStr"/>
+      <c r="P144" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R144" s="3" t="inlineStr"/>
+      <c r="S144" s="3" t="inlineStr"/>
+      <c r="T144" s="3" t="inlineStr"/>
+      <c r="U144" s="3" t="inlineStr"/>
+      <c r="V144" s="3" t="inlineStr"/>
+      <c r="W144" s="3" t="inlineStr"/>
+      <c r="X144" s="3" t="inlineStr"/>
+      <c r="Y144" s="3" t="inlineStr"/>
+      <c r="Z144" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="3" t="inlineStr"/>
+      <c r="AC144" s="3" t="inlineStr"/>
+      <c r="AD144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>translationjob25</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.417</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.438</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.598</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.020</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.125</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.171</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>2603</v>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="n">
+        <v>2754</v>
+      </c>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z145" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>translationjob26</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.423</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.437</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:10.576</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:12.870</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:12.919</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>15:21:12.973</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>2447</v>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z146" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>translationjob27</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:13.091</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:13.110</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:13.252</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:15.461</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:15.503</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>15:21:15.557</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>2370</v>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="Y147" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z147" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>translationjob28</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:39.079</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:39.096</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:39.256</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.136</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.193</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.268</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>2189</v>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>translationjob29</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.486</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.503</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:41.645</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.108</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.154</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.220</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>1622</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="n">
+        <v>1734</v>
+      </c>
+      <c r="Y149" s="2" t="inlineStr">
+        <is>
+          <t>1.7s</t>
+        </is>
+      </c>
+      <c r="Z149" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>translationjob30</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.473</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.495</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:43.659</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.054</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.113</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.160</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>2581</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>2687</v>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z150" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>translationjob31</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.387</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.407</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:46.548</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:48.488</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:48.576</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>15:32:48.630</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>2101</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="n">
+        <v>2243</v>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>translationjob32</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:48.862</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:48.882</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:49.031</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:50.658</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:50.705</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>15:32:50.762</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>translationjob33</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:51.009</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:51.033</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:51.172</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:52.797</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:52.854</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>15:32:52.896</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>1788</v>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>1887</v>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="Z153" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>21:21:38.610</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>21:21:38.646</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>21:22:20.222</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>21:23:03.563</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>21:23:03.633</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>21:23:08.765</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>41576</v>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>41.6s</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>84953</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>1m 25.0s</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>5132</v>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>90155</v>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>1m 30.2s</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>21:23:34.851</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>21:23:34.887</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>21:23:50.337</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>21:24:00.943</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>21:24:01.032</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>21:24:02.406</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>15450</v>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>15.4s</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>26092</v>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>26.1s</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>1374</v>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="n">
+        <v>27555</v>
+      </c>
+      <c r="Y155" s="2" t="inlineStr">
+        <is>
+          <t>27.6s</t>
+        </is>
+      </c>
+      <c r="Z155" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>21:24:16.814</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>21:24:16.850</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>21:25:07.876</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>21:26:00.766</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>51026</v>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>51.0s</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="n">
+        <v>103952</v>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>1m 44.0s</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>21:26:31.914</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>21:26:31.943</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>21:27:37.446</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>21:28:14.881</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>21:28:14.978</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>21:28:21.020</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>65503</v>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>1m 5.5s</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="n">
+        <v>102967</v>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>1m 43.0s</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>6042</v>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="n">
+        <v>109106</v>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>1m 49.1s</t>
+        </is>
+      </c>
+      <c r="Z157" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>21:28:49.239</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>21:28:49.267</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>21:30:33.510</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>21:30:33.591</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>21:30:40.000</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="n">
+        <v>104271</v>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>1m 44.3s</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>6409</v>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="n">
+        <v>110761</v>
+      </c>
+      <c r="Y158" s="2" t="inlineStr">
+        <is>
+          <t>1m 50.8s</t>
+        </is>
+      </c>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.662</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.692</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.955</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:45.227</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:45.292</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>21:44:45.383</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="n">
+        <v>5565</v>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="n">
+        <v>5721</v>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:45.773</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:45.802</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:46.098</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:56.499</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:56.557</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>21:44:56.643</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>10726</v>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="n">
+        <v>10870</v>
+      </c>
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>10.9s</t>
+        </is>
+      </c>
+      <c r="Z160" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>21:44:57.064</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>21:44:57.106</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>21:44:57.343</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>21:45:05.532</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>21:45:05.594</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>21:45:05.675</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>8468</v>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="n">
+        <v>8611</v>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:06.079</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:06.106</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:06.333</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:11.972</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:12.205</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>21:45:12.292</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>5893</v>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="n">
+        <v>6213</v>
+      </c>
+      <c r="Y162" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z162" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:12.655</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:12.686</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:12.965</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:22.211</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:22.288</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>21:45:22.352</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>9556</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="n">
+        <v>9697</v>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="Z163" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:48.931</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:48.958</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:49.590</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:56.415</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:56.475</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>23:06:56.653</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>7484</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="n">
+        <v>7722</v>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>23:06:57.086</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>23:06:57.119</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>23:06:57.689</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>23:07:02.050</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>23:07:02.108</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>23:07:02.291</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>4964</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>5205</v>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:02.725</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:02.750</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:03.426</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:07.726</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:07.799</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>23:07:08.000</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>5001</v>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="n">
+        <v>5275</v>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:08.328</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:08.354</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:08.710</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:14.943</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:15.018</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>23:07:15.178</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>6615</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="n">
+        <v>6850</v>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:15.537</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:15.563</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:15.904</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:21.398</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:21.458</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>23:07:21.605</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="n">
+        <v>5861</v>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>6068</v>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:22.014</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:22.040</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:22.457</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:28.456</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:28.513</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>23:07:29.079</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>6442</v>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>7065</v>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:06.480</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:06.504</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:06.704</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.110</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.170</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.255</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>2630</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="n">
+        <v>2775</v>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.659</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.681</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:09.861</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:12.680</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:12.732</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>23:10:12.786</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>3021</v>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="n">
+        <v>3127</v>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:13.269</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:13.292</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:13.487</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:16.429</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:16.483</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>23:10:16.541</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="n">
+        <v>3160</v>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="n">
+        <v>3272</v>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z172" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:16.944</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:16.967</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:17.143</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.125</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.175</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.241</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>3181</v>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="n">
+        <v>3297</v>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.583</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.607</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:20.797</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:23.477</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:23.532</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>23:10:23.595</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>2894</v>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="n">
+        <v>3012</v>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:23.962</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:23.986</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:24.321</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:27.835</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:27.883</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>23:10:27.953</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>3873</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="n">
+        <v>3991</v>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>translationjob23</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:05.775</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:05.799</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:06.146</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:10.851</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:10.915</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>23:14:11.061</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>5076</v>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="n">
+        <v>5286</v>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>translationjob24</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:11.446</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:11.474</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:11.819</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:16.102</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:16.157</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>23:14:16.469</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>4656</v>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="n">
+        <v>5023</v>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>translationjob25</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:16.801</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:16.825</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:17.205</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:22.078</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:22.152</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>23:14:22.313</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>5277</v>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="n">
+        <v>5512</v>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>translationjob26</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:22.646</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:22.672</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:23.243</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:28.646</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:28.698</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>23:14:28.867</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="n">
+        <v>6221</v>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>translationjob27</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:29.274</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:29.300</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:29.672</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:34.095</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:34.165</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>23:14:34.327</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>4821</v>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="n">
+        <v>5053</v>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>translationjob28</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:34.633</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:34.657</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:35.014</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:41.598</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:41.695</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>23:14:41.914</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>6965</v>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>translationjob24</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.047</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.089</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>15:21:07.132</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="inlineStr"/>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA182" s="2" t="inlineStr"/>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.018</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.103</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>21:44:39.181</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr"/>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr"/>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD120"/>
+  <autoFilter ref="A1:AD183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14813,7 +22615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14960,6 +22762,46 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>11.4s</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>1m 50.8s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14971,12 +22813,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14995,6 +22838,11 @@
           <t>2026-03-19</t>
         </is>
       </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -15008,6 +22856,9 @@
       <c r="C2" s="6" t="n">
         <v>289168</v>
       </c>
+      <c r="D2" s="6" t="n">
+        <v>20497</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -15021,6 +22872,7 @@
       <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -15034,6 +22886,7 @@
       <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -15047,6 +22900,9 @@
       <c r="C5" s="6" t="n">
         <v>788</v>
       </c>
+      <c r="D5" s="6" t="n">
+        <v>792</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -15060,6 +22916,9 @@
       <c r="C6" s="6" t="n">
         <v>444</v>
       </c>
+      <c r="D6" s="6" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -15073,6 +22932,9 @@
       <c r="C7" s="5" t="n">
         <v>62</v>
       </c>
+      <c r="D7" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -15086,6 +22948,9 @@
       <c r="C8" s="5" t="n">
         <v>12</v>
       </c>
+      <c r="D8" s="5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -15099,6 +22964,9 @@
       <c r="C9" s="6" t="n">
         <v>167143</v>
       </c>
+      <c r="D9" s="6" t="n">
+        <v>122671</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -15112,6 +22980,9 @@
       <c r="C10" s="6" t="n">
         <v>13518</v>
       </c>
+      <c r="D10" s="6" t="n">
+        <v>16899</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -15125,6 +22996,9 @@
       <c r="C11" s="6" t="n">
         <v>18348</v>
       </c>
+      <c r="D11" s="6" t="n">
+        <v>12262</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -15138,6 +23012,9 @@
       <c r="C12" s="6" t="n">
         <v>1168</v>
       </c>
+      <c r="D12" s="6" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -15151,6 +23028,9 @@
       <c r="C13" s="6" t="n">
         <v>822</v>
       </c>
+      <c r="D13" s="6" t="n">
+        <v>846</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -15163,6 +23043,21 @@
       </c>
       <c r="C14" s="6" t="n">
         <v>714</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Content LC unknown state</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -15176,7 +23071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15275,6 +23170,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>418</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD270"/>
+  <dimension ref="A1:AD335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33436,8 +33436,8078 @@
       <c r="AC270" s="2" t="inlineStr"/>
       <c r="AD270" s="2" t="inlineStr"/>
     </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>translationjob47</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:04.290</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:04.311</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:04.615</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:12.947</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:13.030</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>09:32:13.095</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="n">
+        <v>8657</v>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="U271" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="n">
+        <v>8805</v>
+      </c>
+      <c r="Y271" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB271" s="2" t="inlineStr"/>
+      <c r="AC271" s="2" t="inlineStr"/>
+      <c r="AD271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>translationjob48</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:13.274</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:13.294</t>
+        </is>
+      </c>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:13.587</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:18.590</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:18.654</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>09:32:18.741</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="n">
+        <v>5316</v>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V272" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="n">
+        <v>5467</v>
+      </c>
+      <c r="Y272" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z272" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB272" s="2" t="inlineStr"/>
+      <c r="AC272" s="2" t="inlineStr"/>
+      <c r="AD272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>translationjob49</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:18.896</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:18.916</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:19.124</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.287</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.348</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.477</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="n">
+        <v>13391</v>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U273" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="n">
+        <v>13581</v>
+      </c>
+      <c r="Y273" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="Z273" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB273" s="2" t="inlineStr"/>
+      <c r="AC273" s="2" t="inlineStr"/>
+      <c r="AD273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>translationjob50</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.641</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.661</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:32.870</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.271</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.336</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.396</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="n">
+        <v>8630</v>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U274" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V274" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="n">
+        <v>8755</v>
+      </c>
+      <c r="Y274" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB274" s="2" t="inlineStr"/>
+      <c r="AC274" s="2" t="inlineStr"/>
+      <c r="AD274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>translationjob51</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.632</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.648</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:41.856</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:46.968</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:47.026</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>09:32:47.082</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="n">
+        <v>5336</v>
+      </c>
+      <c r="S275" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U275" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V275" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="n">
+        <v>5450</v>
+      </c>
+      <c r="Y275" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z275" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB275" s="2" t="inlineStr"/>
+      <c r="AC275" s="2" t="inlineStr"/>
+      <c r="AD275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>translationjob52</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:47.317</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:47.333</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:47.594</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:54.583</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:54.642</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>09:32:54.704</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="n">
+        <v>7266</v>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V276" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X276" s="2" t="n">
+        <v>7387</v>
+      </c>
+      <c r="Y276" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z276" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB276" s="2" t="inlineStr"/>
+      <c r="AC276" s="2" t="inlineStr"/>
+      <c r="AD276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>translationjob53</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:37.503</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:37.524</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:38.202</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:55.718</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:55.783</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>14:47:56.007</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="n">
+        <v>18215</v>
+      </c>
+      <c r="S277" s="2" t="inlineStr">
+        <is>
+          <t>18.2s</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U277" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V277" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="n">
+        <v>18504</v>
+      </c>
+      <c r="Y277" s="2" t="inlineStr">
+        <is>
+          <t>18.5s</t>
+        </is>
+      </c>
+      <c r="Z277" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB277" s="2" t="inlineStr"/>
+      <c r="AC277" s="2" t="inlineStr"/>
+      <c r="AD277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>translationjob54</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>14:47:56.393</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>14:47:56.414</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>14:47:57.067</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>14:48:10.152</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>14:48:10.230</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>14:48:10.439</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="n">
+        <v>13759</v>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U278" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V278" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="n">
+        <v>14046</v>
+      </c>
+      <c r="Y278" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA278" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB278" s="2" t="inlineStr"/>
+      <c r="AC278" s="2" t="inlineStr"/>
+      <c r="AD278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>translationjob55</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>14:48:10.732</t>
+        </is>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>14:48:10.759</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>14:48:11.192</t>
+        </is>
+      </c>
+      <c r="M279" s="4" t="inlineStr">
+        <is>
+          <t>14:49:12.515</t>
+        </is>
+      </c>
+      <c r="N279" s="4" t="inlineStr"/>
+      <c r="O279" s="4" t="inlineStr"/>
+      <c r="P279" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q279" s="4" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R279" s="4" t="n">
+        <v>61783</v>
+      </c>
+      <c r="S279" s="4" t="inlineStr">
+        <is>
+          <t>1m 1.8s</t>
+        </is>
+      </c>
+      <c r="T279" s="4" t="inlineStr"/>
+      <c r="U279" s="4" t="inlineStr"/>
+      <c r="V279" s="4" t="inlineStr"/>
+      <c r="W279" s="4" t="inlineStr"/>
+      <c r="X279" s="4" t="inlineStr"/>
+      <c r="Y279" s="4" t="inlineStr"/>
+      <c r="Z279" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA279" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB279" s="4" t="inlineStr"/>
+      <c r="AC279" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD279" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>translationjob56</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:12.834</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:12.854</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:13.227</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:31.460</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:31.536</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>14:49:31.770</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="n">
+        <v>18626</v>
+      </c>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>18.6s</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U280" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V280" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="n">
+        <v>18936</v>
+      </c>
+      <c r="Y280" s="2" t="inlineStr">
+        <is>
+          <t>18.9s</t>
+        </is>
+      </c>
+      <c r="Z280" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB280" s="2" t="inlineStr"/>
+      <c r="AC280" s="2" t="inlineStr"/>
+      <c r="AD280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>translationjob57</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:32.024</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:32.058</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:32.876</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:49.076</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:49.134</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>14:49:49.325</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="n">
+        <v>17052</v>
+      </c>
+      <c r="S281" s="2" t="inlineStr">
+        <is>
+          <t>17.1s</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U281" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V281" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="n">
+        <v>17301</v>
+      </c>
+      <c r="Y281" s="2" t="inlineStr">
+        <is>
+          <t>17.3s</t>
+        </is>
+      </c>
+      <c r="Z281" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB281" s="2" t="inlineStr"/>
+      <c r="AC281" s="2" t="inlineStr"/>
+      <c r="AD281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>translationjob58</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>14:49:49.700</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>14:49:49.905</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>14:49:50.303</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>14:50:15.731</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>14:50:15.795</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>14:50:15.968</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="n">
+        <v>26031</v>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
+          <t>26.0s</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U282" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V282" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X282" s="2" t="n">
+        <v>26268</v>
+      </c>
+      <c r="Y282" s="2" t="inlineStr">
+        <is>
+          <t>26.3s</t>
+        </is>
+      </c>
+      <c r="Z282" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB282" s="2" t="inlineStr"/>
+      <c r="AC282" s="2" t="inlineStr"/>
+      <c r="AD282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>translationjob59</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>15:03:54.984</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>15:03:55.005</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>15:03:55.253</t>
+        </is>
+      </c>
+      <c r="M283" s="4" t="inlineStr">
+        <is>
+          <t>15:04:56.816</t>
+        </is>
+      </c>
+      <c r="N283" s="4" t="inlineStr"/>
+      <c r="O283" s="4" t="inlineStr"/>
+      <c r="P283" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q283" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R283" s="4" t="n">
+        <v>61832</v>
+      </c>
+      <c r="S283" s="4" t="inlineStr">
+        <is>
+          <t>1m 1.8s</t>
+        </is>
+      </c>
+      <c r="T283" s="4" t="inlineStr"/>
+      <c r="U283" s="4" t="inlineStr"/>
+      <c r="V283" s="4" t="inlineStr"/>
+      <c r="W283" s="4" t="inlineStr"/>
+      <c r="X283" s="4" t="inlineStr"/>
+      <c r="Y283" s="4" t="inlineStr"/>
+      <c r="Z283" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA283" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB283" s="4" t="inlineStr"/>
+      <c r="AC283" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD283" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>translationjob60</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G284" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I284" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>15:08:54.740</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>15:08:54.760</t>
+        </is>
+      </c>
+      <c r="L284" s="4" t="inlineStr">
+        <is>
+          <t>15:08:54.973</t>
+        </is>
+      </c>
+      <c r="M284" s="4" t="inlineStr">
+        <is>
+          <t>15:09:56.042</t>
+        </is>
+      </c>
+      <c r="N284" s="4" t="inlineStr"/>
+      <c r="O284" s="4" t="inlineStr"/>
+      <c r="P284" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q284" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R284" s="4" t="n">
+        <v>61302</v>
+      </c>
+      <c r="S284" s="4" t="inlineStr">
+        <is>
+          <t>1m 1.3s</t>
+        </is>
+      </c>
+      <c r="T284" s="4" t="inlineStr"/>
+      <c r="U284" s="4" t="inlineStr"/>
+      <c r="V284" s="4" t="inlineStr"/>
+      <c r="W284" s="4" t="inlineStr"/>
+      <c r="X284" s="4" t="inlineStr"/>
+      <c r="Y284" s="4" t="inlineStr"/>
+      <c r="Z284" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA284" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB284" s="4" t="inlineStr"/>
+      <c r="AC284" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD284" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>translationjob61</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H285" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>15:14:27.084</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>15:14:27.105</t>
+        </is>
+      </c>
+      <c r="L285" s="4" t="inlineStr">
+        <is>
+          <t>15:14:27.312</t>
+        </is>
+      </c>
+      <c r="M285" s="4" t="inlineStr">
+        <is>
+          <t>15:15:28.413</t>
+        </is>
+      </c>
+      <c r="N285" s="4" t="inlineStr"/>
+      <c r="O285" s="4" t="inlineStr"/>
+      <c r="P285" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q285" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R285" s="4" t="n">
+        <v>61329</v>
+      </c>
+      <c r="S285" s="4" t="inlineStr">
+        <is>
+          <t>1m 1.3s</t>
+        </is>
+      </c>
+      <c r="T285" s="4" t="inlineStr"/>
+      <c r="U285" s="4" t="inlineStr"/>
+      <c r="V285" s="4" t="inlineStr"/>
+      <c r="W285" s="4" t="inlineStr"/>
+      <c r="X285" s="4" t="inlineStr"/>
+      <c r="Y285" s="4" t="inlineStr"/>
+      <c r="Z285" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA285" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB285" s="4" t="inlineStr"/>
+      <c r="AC285" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD285" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>translationjob62</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:04.473</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:04.493</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:04.692</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:28.419</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:28.477</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>15:17:28.546</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="n">
+        <v>23946</v>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>23.9s</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U286" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V286" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W286" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X286" s="2" t="n">
+        <v>24073</v>
+      </c>
+      <c r="Y286" s="2" t="inlineStr">
+        <is>
+          <t>24.1s</t>
+        </is>
+      </c>
+      <c r="Z286" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA286" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB286" s="2" t="inlineStr"/>
+      <c r="AC286" s="2" t="inlineStr"/>
+      <c r="AD286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>translationjob211</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:36.893</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:36.912</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:37.273</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:45.577</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:45.625</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>17:13:45.730</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="n">
+        <v>8684</v>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U287" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V287" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="W287" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X287" s="2" t="n">
+        <v>8837</v>
+      </c>
+      <c r="Y287" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z287" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA287" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB287" s="2" t="inlineStr"/>
+      <c r="AC287" s="2" t="inlineStr"/>
+      <c r="AD287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>translationjob212</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:46.014</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:46.031</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:46.513</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:51.444</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:51.492</t>
+        </is>
+      </c>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>17:13:51.619</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="n">
+        <v>482</v>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="n">
+        <v>5430</v>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V288" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="W288" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X288" s="2" t="n">
+        <v>5605</v>
+      </c>
+      <c r="Y288" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z288" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA288" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB288" s="2" t="inlineStr"/>
+      <c r="AC288" s="2" t="inlineStr"/>
+      <c r="AD288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>translationjob213</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>17:13:51.856</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>17:13:51.870</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>17:13:52.274</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>17:14:06.663</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>17:14:06.707</t>
+        </is>
+      </c>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>17:14:06.809</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="n">
+        <v>14807</v>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>14.8s</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U289" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V289" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="W289" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X289" s="2" t="n">
+        <v>14953</v>
+      </c>
+      <c r="Y289" s="2" t="inlineStr">
+        <is>
+          <t>15.0s</t>
+        </is>
+      </c>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB289" s="2" t="inlineStr"/>
+      <c r="AC289" s="2" t="inlineStr"/>
+      <c r="AD289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>translationjob214</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:07.077</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:07.099</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:07.396</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:13.471</t>
+        </is>
+      </c>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:13.522</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>17:14:13.637</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="n">
+        <v>6394</v>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V290" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="W290" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X290" s="2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="Y290" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA290" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB290" s="2" t="inlineStr"/>
+      <c r="AC290" s="2" t="inlineStr"/>
+      <c r="AD290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>translationjob215</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:13.958</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:13.991</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:14.477</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:19.261</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:19.420</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>17:14:19.513</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="n">
+        <v>5303</v>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V291" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="W291" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X291" s="2" t="n">
+        <v>5555</v>
+      </c>
+      <c r="Y291" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z291" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB291" s="2" t="inlineStr"/>
+      <c r="AC291" s="2" t="inlineStr"/>
+      <c r="AD291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>translationjob216</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:19.769</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:19.783</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:20.208</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:28.350</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:28.443</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>17:14:28.533</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="n">
+        <v>8581</v>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V292" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="n">
+        <v>8764</v>
+      </c>
+      <c r="Y292" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z292" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB292" s="2" t="inlineStr"/>
+      <c r="AC292" s="2" t="inlineStr"/>
+      <c r="AD292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>translationjob217</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:26.447</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:26.459</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:26.722</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.213</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.251</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.327</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="n">
+        <v>9766</v>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V293" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="n">
+        <v>9880</v>
+      </c>
+      <c r="Y293" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="Z293" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB293" s="2" t="inlineStr"/>
+      <c r="AC293" s="2" t="inlineStr"/>
+      <c r="AD293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>translationjob218</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.557</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.571</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:36.846</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:42.647</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:42.685</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>19:18:42.768</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="n">
+        <v>6090</v>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U294" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V294" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="n">
+        <v>6211</v>
+      </c>
+      <c r="Y294" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA294" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB294" s="2" t="inlineStr"/>
+      <c r="AC294" s="2" t="inlineStr"/>
+      <c r="AD294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>translationjob219</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:42.991</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:43.003</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:43.252</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.300</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.337</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.414</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="n">
+        <v>13309</v>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U295" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V295" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="n">
+        <v>13423</v>
+      </c>
+      <c r="Y295" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA295" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB295" s="2" t="inlineStr"/>
+      <c r="AC295" s="2" t="inlineStr"/>
+      <c r="AD295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>translationjob220</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.614</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.625</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>19:18:56.918</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>19:19:03.482</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>19:19:03.516</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>19:19:03.589</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="n">
+        <v>6868</v>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V296" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="n">
+        <v>6975</v>
+      </c>
+      <c r="Y296" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB296" s="2" t="inlineStr"/>
+      <c r="AC296" s="2" t="inlineStr"/>
+      <c r="AD296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>translationjob221</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:03.803</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:03.815</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:04.136</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.353</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.396</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.472</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="n">
+        <v>5550</v>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V297" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="n">
+        <v>5669</v>
+      </c>
+      <c r="Y297" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z297" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA297" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB297" s="2" t="inlineStr"/>
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>translationjob222</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.680</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.693</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:09.908</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:18.878</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:18.993</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>19:19:19.097</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="n">
+        <v>9198</v>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V298" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="n">
+        <v>9417</v>
+      </c>
+      <c r="Y298" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="Z298" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA298" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB298" s="2" t="inlineStr"/>
+      <c r="AC298" s="2" t="inlineStr"/>
+      <c r="AD298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:22.279</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:22.298</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:22.530</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:36.969</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:37.017</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>20:14:37.087</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="n">
+        <v>14690</v>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>14.7s</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V299" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="n">
+        <v>14808</v>
+      </c>
+      <c r="Y299" s="2" t="inlineStr">
+        <is>
+          <t>14.8s</t>
+        </is>
+      </c>
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB299" s="2" t="inlineStr"/>
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:28.890</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:28.904</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:29.102</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:59.656</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:59.710</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>20:14:59.777</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="n">
+        <v>30766</v>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>30.8s</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V300" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W300" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X300" s="2" t="n">
+        <v>30887</v>
+      </c>
+      <c r="Y300" s="2" t="inlineStr">
+        <is>
+          <t>30.9s</t>
+        </is>
+      </c>
+      <c r="Z300" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB300" s="2" t="inlineStr"/>
+      <c r="AC300" s="2" t="inlineStr"/>
+      <c r="AD300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>20:14:37.230</t>
+        </is>
+      </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>20:14:37.244</t>
+        </is>
+      </c>
+      <c r="L301" s="4" t="inlineStr">
+        <is>
+          <t>20:14:37.395</t>
+        </is>
+      </c>
+      <c r="M301" s="4" t="inlineStr">
+        <is>
+          <t>20:15:38.359</t>
+        </is>
+      </c>
+      <c r="N301" s="4" t="inlineStr"/>
+      <c r="O301" s="4" t="inlineStr"/>
+      <c r="P301" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q301" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R301" s="4" t="n">
+        <v>61129</v>
+      </c>
+      <c r="S301" s="4" t="inlineStr">
+        <is>
+          <t>1m 1.1s</t>
+        </is>
+      </c>
+      <c r="T301" s="4" t="inlineStr"/>
+      <c r="U301" s="4" t="inlineStr"/>
+      <c r="V301" s="4" t="inlineStr"/>
+      <c r="W301" s="4" t="inlineStr"/>
+      <c r="X301" s="4" t="inlineStr"/>
+      <c r="Y301" s="4" t="inlineStr"/>
+      <c r="Z301" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB301" s="4" t="inlineStr"/>
+      <c r="AC301" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD301" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>20:14:59.983</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>20:15:00.001</t>
+        </is>
+      </c>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>20:15:00.258</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.512</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.553</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.608</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="n">
+        <v>10529</v>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>10.5s</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U302" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V302" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="Y302" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="Z302" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA302" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB302" s="2" t="inlineStr"/>
+      <c r="AC302" s="2" t="inlineStr"/>
+      <c r="AD302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.709</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.722</t>
+        </is>
+      </c>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:10.975</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:27.432</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:27.474</t>
+        </is>
+      </c>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>20:15:27.516</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="n">
+        <v>16723</v>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>16.7s</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U303" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V303" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="W303" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X303" s="2" t="n">
+        <v>16807</v>
+      </c>
+      <c r="Y303" s="2" t="inlineStr">
+        <is>
+          <t>16.8s</t>
+        </is>
+      </c>
+      <c r="Z303" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA303" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB303" s="2" t="inlineStr"/>
+      <c r="AC303" s="2" t="inlineStr"/>
+      <c r="AD303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:38.604</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:38.622</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:38.850</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:55.225</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:55.267</t>
+        </is>
+      </c>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>20:15:55.319</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="n">
+        <v>16621</v>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>16.6s</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U304" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V304" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W304" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X304" s="2" t="n">
+        <v>16715</v>
+      </c>
+      <c r="Y304" s="2" t="inlineStr">
+        <is>
+          <t>16.7s</t>
+        </is>
+      </c>
+      <c r="Z304" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA304" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB304" s="2" t="inlineStr"/>
+      <c r="AC304" s="2" t="inlineStr"/>
+      <c r="AD304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>translationjob223</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:42.062</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:42.085</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:42.432</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:50.165</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:50.210</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>21:59:50.346</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="n">
+        <v>8103</v>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U305" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V305" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="W305" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X305" s="2" t="n">
+        <v>8284</v>
+      </c>
+      <c r="Y305" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA305" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB305" s="2" t="inlineStr"/>
+      <c r="AC305" s="2" t="inlineStr"/>
+      <c r="AD305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>translationjob224</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:50.610</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:50.626</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:51.013</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:55.398</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:55.471</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>21:59:55.600</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="n">
+        <v>4788</v>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="U306" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V306" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="W306" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X306" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="Y306" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB306" s="2" t="inlineStr"/>
+      <c r="AC306" s="2" t="inlineStr"/>
+      <c r="AD306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>translationjob225</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>21:59:55.841</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t>21:59:55.859</t>
+        </is>
+      </c>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>21:59:56.242</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.253</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.377</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.585</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="n">
+        <v>12412</v>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>12.4s</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="U307" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V307" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="n">
+        <v>12744</v>
+      </c>
+      <c r="Y307" s="2" t="inlineStr">
+        <is>
+          <t>12.7s</t>
+        </is>
+      </c>
+      <c r="Z307" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA307" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB307" s="2" t="inlineStr"/>
+      <c r="AC307" s="2" t="inlineStr"/>
+      <c r="AD307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>translationjob226</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:09.000</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:09.024</t>
+        </is>
+      </c>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:09.632</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:15.998</t>
+        </is>
+      </c>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.054</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.247</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>608</v>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="n">
+        <v>6998</v>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U308" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V308" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="n">
+        <v>7247</v>
+      </c>
+      <c r="Y308" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="Z308" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA308" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB308" s="2" t="inlineStr"/>
+      <c r="AC308" s="2" t="inlineStr"/>
+      <c r="AD308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>translationjob227</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.605</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.621</t>
+        </is>
+      </c>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:17.027</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.655</t>
+        </is>
+      </c>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.717</t>
+        </is>
+      </c>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>22:00:22.889</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="n">
+        <v>6050</v>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U309" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V309" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="W309" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X309" s="2" t="n">
+        <v>6284</v>
+      </c>
+      <c r="Y309" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z309" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA309" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB309" s="2" t="inlineStr"/>
+      <c r="AC309" s="2" t="inlineStr"/>
+      <c r="AD309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>translationjob228</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:23.286</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:23.301</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:24.102</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:30.433</t>
+        </is>
+      </c>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:30.503</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>22:00:30.702</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="n">
+        <v>7147</v>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U310" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V310" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="n">
+        <v>7416</v>
+      </c>
+      <c r="Y310" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z310" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA310" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB310" s="2" t="inlineStr"/>
+      <c r="AC310" s="2" t="inlineStr"/>
+      <c r="AD310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>translationjob229</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:56.465</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:56.481</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:56.733</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:59.312</t>
+        </is>
+      </c>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:59.366</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>22:06:59.501</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="n">
+        <v>2847</v>
+      </c>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U311" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V311" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="W311" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X311" s="2" t="n">
+        <v>3036</v>
+      </c>
+      <c r="Y311" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z311" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA311" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB311" s="2" t="inlineStr"/>
+      <c r="AC311" s="2" t="inlineStr"/>
+      <c r="AD311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>translationjob230</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>22:06:59.996</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>22:07:00.032</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>22:07:00.397</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>22:07:03.163</t>
+        </is>
+      </c>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>22:07:03.226</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>22:07:03.371</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="n">
+        <v>3167</v>
+      </c>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U312" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V312" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="W312" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X312" s="2" t="n">
+        <v>3375</v>
+      </c>
+      <c r="Y312" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z312" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA312" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB312" s="2" t="inlineStr"/>
+      <c r="AC312" s="2" t="inlineStr"/>
+      <c r="AD312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>translationjob231</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:03.744</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:03.765</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:04.000</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:07.444</t>
+        </is>
+      </c>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:07.534</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>22:07:07.628</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="n">
+        <v>3700</v>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="U313" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V313" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="n">
+        <v>3884</v>
+      </c>
+      <c r="Y313" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z313" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA313" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB313" s="2" t="inlineStr"/>
+      <c r="AC313" s="2" t="inlineStr"/>
+      <c r="AD313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>translationjob232</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:07.947</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:07.962</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:08.195</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:11.193</t>
+        </is>
+      </c>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:11.279</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>22:07:11.341</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="n">
+        <v>3246</v>
+      </c>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="U314" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V314" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="n">
+        <v>3394</v>
+      </c>
+      <c r="Y314" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z314" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA314" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB314" s="2" t="inlineStr"/>
+      <c r="AC314" s="2" t="inlineStr"/>
+      <c r="AD314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>translationjob233</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:11.714</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:11.733</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:12.133</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:14.679</t>
+        </is>
+      </c>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:14.729</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>22:07:14.783</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="n">
+        <v>2965</v>
+      </c>
+      <c r="S315" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U315" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V315" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W315" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X315" s="2" t="n">
+        <v>3069</v>
+      </c>
+      <c r="Y315" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z315" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA315" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB315" s="2" t="inlineStr"/>
+      <c r="AC315" s="2" t="inlineStr"/>
+      <c r="AD315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>translationjob234</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:15.026</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:15.042</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:15.314</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:19.237</t>
+        </is>
+      </c>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:19.296</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>22:07:19.390</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="n">
+        <v>4211</v>
+      </c>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U316" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V316" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="n">
+        <v>4364</v>
+      </c>
+      <c r="Y316" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="Z316" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA316" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB316" s="2" t="inlineStr"/>
+      <c r="AC316" s="2" t="inlineStr"/>
+      <c r="AD316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>translationjob235</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>22:07:49.931</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>22:07:49.946</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>22:07:51.005</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>22:08:09.311</t>
+        </is>
+      </c>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>22:08:09.372</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr">
+        <is>
+          <t>22:08:09.802</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="n">
+        <v>19380</v>
+      </c>
+      <c r="S317" s="2" t="inlineStr">
+        <is>
+          <t>19.4s</t>
+        </is>
+      </c>
+      <c r="T317" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U317" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V317" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="n">
+        <v>19871</v>
+      </c>
+      <c r="Y317" s="2" t="inlineStr">
+        <is>
+          <t>19.9s</t>
+        </is>
+      </c>
+      <c r="Z317" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA317" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB317" s="2" t="inlineStr"/>
+      <c r="AC317" s="2" t="inlineStr"/>
+      <c r="AD317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>translationjob236</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:10.282</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:10.297</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:10.900</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:22.734</t>
+        </is>
+      </c>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:22.801</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>22:08:23.041</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="n">
+        <v>12452</v>
+      </c>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
+          <t>12.5s</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U318" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V318" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="n">
+        <v>12759</v>
+      </c>
+      <c r="Y318" s="2" t="inlineStr">
+        <is>
+          <t>12.8s</t>
+        </is>
+      </c>
+      <c r="Z318" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA318" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB318" s="2" t="inlineStr"/>
+      <c r="AC318" s="2" t="inlineStr"/>
+      <c r="AD318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>translationjob237</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:23.419</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:23.434</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:24.263</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:48.081</t>
+        </is>
+      </c>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:48.157</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>22:08:48.448</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="n">
+        <v>24662</v>
+      </c>
+      <c r="S319" s="2" t="inlineStr">
+        <is>
+          <t>24.7s</t>
+        </is>
+      </c>
+      <c r="T319" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U319" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V319" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="n">
+        <v>25029</v>
+      </c>
+      <c r="Y319" s="2" t="inlineStr">
+        <is>
+          <t>25.0s</t>
+        </is>
+      </c>
+      <c r="Z319" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA319" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB319" s="2" t="inlineStr"/>
+      <c r="AC319" s="2" t="inlineStr"/>
+      <c r="AD319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>translationjob238</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>22:08:48.855</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>22:08:48.873</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>22:08:49.791</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>22:09:11.710</t>
+        </is>
+      </c>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>22:09:11.766</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>22:09:12.328</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="n">
+        <v>22855</v>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>22.9s</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U320" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V320" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="n">
+        <v>23473</v>
+      </c>
+      <c r="Y320" s="2" t="inlineStr">
+        <is>
+          <t>23.5s</t>
+        </is>
+      </c>
+      <c r="Z320" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA320" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB320" s="2" t="inlineStr"/>
+      <c r="AC320" s="2" t="inlineStr"/>
+      <c r="AD320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>translationjob239</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:12.725</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:12.740</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:13.792</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:37.060</t>
+        </is>
+      </c>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:37.120</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>22:09:37.412</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="n">
+        <v>1052</v>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="n">
+        <v>24335</v>
+      </c>
+      <c r="S321" s="2" t="inlineStr">
+        <is>
+          <t>24.3s</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U321" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V321" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="n">
+        <v>24687</v>
+      </c>
+      <c r="Y321" s="2" t="inlineStr">
+        <is>
+          <t>24.7s</t>
+        </is>
+      </c>
+      <c r="Z321" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA321" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB321" s="2" t="inlineStr"/>
+      <c r="AC321" s="2" t="inlineStr"/>
+      <c r="AD321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>translationjob240</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>22:09:37.851</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>22:09:37.869</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>22:09:38.581</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>22:10:01.806</t>
+        </is>
+      </c>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>22:10:01.867</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>22:10:02.221</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="n">
+        <v>23955</v>
+      </c>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>24.0s</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U322" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V322" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="n">
+        <v>24370</v>
+      </c>
+      <c r="Y322" s="2" t="inlineStr">
+        <is>
+          <t>24.4s</t>
+        </is>
+      </c>
+      <c r="Z322" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA322" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB322" s="2" t="inlineStr"/>
+      <c r="AC322" s="2" t="inlineStr"/>
+      <c r="AD322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>translationjob241</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>22:34:54.102</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
+          <t>22:34:54.120</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>22:35:22.035</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t>22:35:58.188</t>
+        </is>
+      </c>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>22:35:58.360</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>22:36:01.819</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="n">
+        <v>27915</v>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>27.9s</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="n">
+        <v>64086</v>
+      </c>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>1m 4.1s</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="U323" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V323" s="2" t="n">
+        <v>3459</v>
+      </c>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="n">
+        <v>67717</v>
+      </c>
+      <c r="Y323" s="2" t="inlineStr">
+        <is>
+          <t>1m 7.7s</t>
+        </is>
+      </c>
+      <c r="Z323" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA323" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB323" s="2" t="inlineStr"/>
+      <c r="AC323" s="2" t="inlineStr"/>
+      <c r="AD323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>translationjob242</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>22:36:15.709</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>22:36:15.724</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>22:36:43.090</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t>22:37:09.858</t>
+        </is>
+      </c>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>22:37:09.912</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>22:37:13.026</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="n">
+        <v>27366</v>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>27.4s</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="n">
+        <v>54149</v>
+      </c>
+      <c r="S324" s="2" t="inlineStr">
+        <is>
+          <t>54.1s</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U324" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V324" s="2" t="n">
+        <v>3114</v>
+      </c>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="n">
+        <v>57317</v>
+      </c>
+      <c r="Y324" s="2" t="inlineStr">
+        <is>
+          <t>57.3s</t>
+        </is>
+      </c>
+      <c r="Z324" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:5, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA324" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB324" s="2" t="inlineStr"/>
+      <c r="AC324" s="2" t="inlineStr"/>
+      <c r="AD324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>translationjob243</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H325" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I325" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>22:37:27.239</t>
+        </is>
+      </c>
+      <c r="K325" s="4" t="inlineStr">
+        <is>
+          <t>22:37:27.253</t>
+        </is>
+      </c>
+      <c r="L325" s="4" t="inlineStr">
+        <is>
+          <t>22:37:38.797</t>
+        </is>
+      </c>
+      <c r="M325" s="4" t="inlineStr">
+        <is>
+          <t>22:38:44.895</t>
+        </is>
+      </c>
+      <c r="N325" s="4" t="inlineStr"/>
+      <c r="O325" s="4" t="inlineStr"/>
+      <c r="P325" s="4" t="n">
+        <v>11544</v>
+      </c>
+      <c r="Q325" s="4" t="inlineStr">
+        <is>
+          <t>11.5s</t>
+        </is>
+      </c>
+      <c r="R325" s="4" t="n">
+        <v>77656</v>
+      </c>
+      <c r="S325" s="4" t="inlineStr">
+        <is>
+          <t>1m 17.7s</t>
+        </is>
+      </c>
+      <c r="T325" s="4" t="inlineStr"/>
+      <c r="U325" s="4" t="inlineStr"/>
+      <c r="V325" s="4" t="inlineStr"/>
+      <c r="W325" s="4" t="inlineStr"/>
+      <c r="X325" s="4" t="inlineStr"/>
+      <c r="Y325" s="4" t="inlineStr"/>
+      <c r="Z325" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA325" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB325" s="4" t="inlineStr"/>
+      <c r="AC325" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD325" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>translationjob244</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>22:39:01.467</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>22:39:01.488</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>22:39:37.271</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>22:40:23.921</t>
+        </is>
+      </c>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>22:40:23.986</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>22:40:28.289</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>35783</v>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>35.8s</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>82454</v>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>1m 22.5s</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U326" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V326" s="2" t="n">
+        <v>4303</v>
+      </c>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="n">
+        <v>86822</v>
+      </c>
+      <c r="Y326" s="2" t="inlineStr">
+        <is>
+          <t>1m 26.8s</t>
+        </is>
+      </c>
+      <c r="Z326" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:6, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB326" s="2" t="inlineStr"/>
+      <c r="AC326" s="2" t="inlineStr"/>
+      <c r="AD326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>translationjob245</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>22:40:45.005</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>22:40:45.025</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>22:41:26.045</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>22:42:04.849</t>
+        </is>
+      </c>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>22:42:04.901</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>22:42:08.259</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>41020</v>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>41.0s</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="n">
+        <v>79844</v>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>1m 19.8s</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U327" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>3358</v>
+      </c>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="n">
+        <v>83254</v>
+      </c>
+      <c r="Y327" s="2" t="inlineStr">
+        <is>
+          <t>1m 23.3s</t>
+        </is>
+      </c>
+      <c r="Z327" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:6, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB327" s="2" t="inlineStr"/>
+      <c r="AC327" s="2" t="inlineStr"/>
+      <c r="AD327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>translationjob246</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>22:42:25.118</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>22:42:25.150</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>22:43:06.311</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>22:44:03.773</t>
+        </is>
+      </c>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>22:44:03.832</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>22:44:07.085</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>41161</v>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>41.2s</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="n">
+        <v>98655</v>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>1m 38.7s</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U328" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V328" s="2" t="n">
+        <v>3253</v>
+      </c>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="n">
+        <v>101967</v>
+      </c>
+      <c r="Y328" s="2" t="inlineStr">
+        <is>
+          <t>1m 42.0s</t>
+        </is>
+      </c>
+      <c r="Z328" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:6, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB328" s="2" t="inlineStr"/>
+      <c r="AC328" s="2" t="inlineStr"/>
+      <c r="AD328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>translationjob247</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:06.978</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:06.990</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:07.176</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.467</t>
+        </is>
+      </c>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.511</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.550</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="n">
+        <v>5489</v>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U329" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V329" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="n">
+        <v>5572</v>
+      </c>
+      <c r="Y329" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA329" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB329" s="2" t="inlineStr"/>
+      <c r="AC329" s="2" t="inlineStr"/>
+      <c r="AD329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>translationjob248</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.784</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.795</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:12.930</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.349</t>
+        </is>
+      </c>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.383</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.428</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="n">
+        <v>4565</v>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U330" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V330" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="n">
+        <v>4644</v>
+      </c>
+      <c r="Y330" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z330" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB330" s="2" t="inlineStr"/>
+      <c r="AC330" s="2" t="inlineStr"/>
+      <c r="AD330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>translationjob249</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.634</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.646</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:17.769</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:26.854</t>
+        </is>
+      </c>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:26.891</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>23:17:26.939</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="n">
+        <v>9220</v>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U331" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V331" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="n">
+        <v>9305</v>
+      </c>
+      <c r="Y331" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB331" s="2" t="inlineStr"/>
+      <c r="AC331" s="2" t="inlineStr"/>
+      <c r="AD331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>translationjob250</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:27.173</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:27.184</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:27.326</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.191</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.240</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.286</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>5018</v>
+      </c>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U332" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V332" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="n">
+        <v>5113</v>
+      </c>
+      <c r="Y332" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB332" s="2" t="inlineStr"/>
+      <c r="AC332" s="2" t="inlineStr"/>
+      <c r="AD332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>translationjob251</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.480</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.492</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:32.659</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.248</t>
+        </is>
+      </c>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.286</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.326</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>4768</v>
+      </c>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U333" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V333" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>4846</v>
+      </c>
+      <c r="Y333" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z333" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA333" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB333" s="2" t="inlineStr"/>
+      <c r="AC333" s="2" t="inlineStr"/>
+      <c r="AD333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>translationjob252</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.594</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.607</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:37.779</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:44.637</t>
+        </is>
+      </c>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:44.679</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>23:17:44.726</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="n">
+        <v>7043</v>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U334" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V334" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>7132</v>
+      </c>
+      <c r="Y334" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z334" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB334" s="2" t="inlineStr"/>
+      <c r="AC334" s="2" t="inlineStr"/>
+      <c r="AD334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>translationjob253</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>23:20:49.927</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>23:20:49.937</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>23:20:50.125</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>23:21:16.323</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>23:21:16.367</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>23:21:16.411</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>26396</v>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>26.4s</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U335" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V335" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="n">
+        <v>26484</v>
+      </c>
+      <c r="Y335" s="2" t="inlineStr">
+        <is>
+          <t>26.5s</t>
+        </is>
+      </c>
+      <c r="Z335" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA335" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB335" s="2" t="inlineStr"/>
+      <c r="AC335" s="2" t="inlineStr"/>
+      <c r="AD335" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD270"/>
+  <autoFilter ref="A1:AD335"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33448,7 +41518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33635,6 +41705,46 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>17.3s</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>1m 42.0s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33646,13 +41756,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33676,6 +41787,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -33692,6 +41808,9 @@
       <c r="D2" s="7" t="n">
         <v>234684</v>
       </c>
+      <c r="E2" s="7" t="n">
+        <v>126769</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -33708,6 +41827,9 @@
       <c r="D3" s="6" t="n">
         <v>90</v>
       </c>
+      <c r="E3" s="6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -33724,6 +41846,9 @@
       <c r="D4" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="E4" s="6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -33740,6 +41865,9 @@
       <c r="D5" s="7" t="n">
         <v>171</v>
       </c>
+      <c r="E5" s="7" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -33756,6 +41884,9 @@
       <c r="D6" s="6" t="n">
         <v>75</v>
       </c>
+      <c r="E6" s="6" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -33772,6 +41903,9 @@
       <c r="D7" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="E7" s="6" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -33788,6 +41922,9 @@
       <c r="D8" s="7" t="n">
         <v>77841</v>
       </c>
+      <c r="E8" s="7" t="n">
+        <v>90868</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -33804,6 +41941,9 @@
       <c r="D9" s="7" t="n">
         <v>40518</v>
       </c>
+      <c r="E9" s="7" t="n">
+        <v>14241</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -33820,6 +41960,9 @@
       <c r="D10" s="7" t="n">
         <v>19321</v>
       </c>
+      <c r="E10" s="7" t="n">
+        <v>13145</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -33836,6 +41979,9 @@
       <c r="D11" s="7" t="n">
         <v>1927</v>
       </c>
+      <c r="E11" s="7" t="n">
+        <v>1489</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -33852,6 +41998,9 @@
       <c r="D12" s="7" t="n">
         <v>2445</v>
       </c>
+      <c r="E12" s="7" t="n">
+        <v>2138</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -33868,6 +42017,9 @@
       <c r="D13" s="7" t="n">
         <v>1147</v>
       </c>
+      <c r="E13" s="7" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -33882,6 +42034,7 @@
       <c r="D14" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="E14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33894,7 +42047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -34018,6 +42171,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7584,8 +7584,5930 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:26.511</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:26.533</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:27.094</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:32.208</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:32.269</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>08:20:32.440</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>5697</v>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="n">
+        <v>5929</v>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:32.561</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:32.582</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:33.370</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:40.802</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:40.859</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>08:20:41.028</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>8241</v>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:41.139</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:41.160</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:41.748</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:51.907</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:51.975</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>08:20:52.125</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>10768</v>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>10.8s</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>10986</v>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:52.234</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:52.254</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:52.798</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:57.071</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:57.131</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>08:20:57.278</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>4837</v>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>5044</v>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>08:20:57.394</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>08:20:57.415</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>08:20:58.055</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>08:21:04.421</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:21:04.512</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>08:21:04.676</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>7027</v>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="n">
+        <v>7282</v>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:31.850</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:31.870</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:32.129</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:35.255</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:35.309</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>11:04:35.396</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>3405</v>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>3546</v>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:35.575</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:35.593</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:36.331</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.047</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.094</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.143</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>3472</v>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>3568</v>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.252</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.269</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:39.817</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.426</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.470</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.524</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>3174</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>3272</v>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.635</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.651</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:42.886</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:46.460</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:46.513</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>11:04:46.564</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="n">
+        <v>3929</v>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:46.684</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:46.701</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:47.689</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.438</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.484</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.539</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>988</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>3754</v>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="n">
+        <v>3855</v>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.656</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.674</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:50.881</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:54.671</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:54.727</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>11:04:54.778</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>4015</v>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>4122</v>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:39.299</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:39.317</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:39.636</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:42.549</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:42.621</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:30:42.683</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>3250</v>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="n">
+        <v>3384</v>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:42.871</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:42.890</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:43.321</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.068</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.124</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.192</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>3197</v>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="n">
+        <v>3321</v>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.335</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.368</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:46.595</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:50.095</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:50.163</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:30:50.222</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="n">
+        <v>3887</v>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:50.547</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:50.682</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:51.144</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:53.700</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:53.756</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:30:53.831</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>3153</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="n">
+        <v>3284</v>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:54.005</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:54.024</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:54.419</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:57.724</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:57.780</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:30:57.833</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>3719</v>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="n">
+        <v>3828</v>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>16:30:57.971</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>16:30:57.990</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>16:30:58.234</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>16:31:02.757</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>16:31:02.805</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:31:02.871</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>4786</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="n">
+        <v>4900</v>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:12.129</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:12.151</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:12.649</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:16.735</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:16.819</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:09:16.923</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>4606</v>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="n">
+        <v>4794</v>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:17.088</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:17.108</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:17.598</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:20.417</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:20.476</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:09:20.549</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>3329</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="n">
+        <v>3461</v>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:20.723</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:20.744</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:21.133</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:23.718</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:23.803</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18:09:23.890</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>2995</v>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="n">
+        <v>3167</v>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:24.252</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:24.272</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:24.627</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.153</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.232</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.301</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>3901</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="n">
+        <v>4049</v>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.486</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.509</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:28.788</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:31.635</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:31.699</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:09:31.781</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>3149</v>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="n">
+        <v>3295</v>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:31.945</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:31.968</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:32.292</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:36.142</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:36.214</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:09:36.297</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>4197</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="n">
+        <v>4352</v>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>translationjob23</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>21:36:57.340</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>21:36:57.364</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>21:36:57.667</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>21:37:00.690</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>21:37:00.771</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>21:37:00.964</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>3350</v>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="n">
+        <v>3624</v>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>translationjob24</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:01.139</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:01.163</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:01.575</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:04.551</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:04.628</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>21:37:04.709</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>3412</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="n">
+        <v>3570</v>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>translationjob25</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:04.875</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:04.904</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:06.432</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:08.852</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:08.928</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>21:37:08.998</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>3977</v>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="n">
+        <v>4123</v>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>translationjob26</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:09.173</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:09.195</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:09.445</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:12.577</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:12.648</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>21:37:12.734</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>3404</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="n">
+        <v>3561</v>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>translationjob27</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:13.074</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:13.096</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:13.368</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.105</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.194</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.326</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>3031</v>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="n">
+        <v>3252</v>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>translationjob28</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.495</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.522</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:16.764</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:19.562</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:19.655</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>21:37:19.730</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>3067</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="n">
+        <v>3235</v>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>translationjob29</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:07.828</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:07.846</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:08.552</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:13.510</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:13.563</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>21:53:13.828</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>5682</v>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>translationjob30</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:14.039</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:14.054</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:14.779</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:19.195</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:19.245</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>21:53:19.438</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>5156</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="n">
+        <v>5399</v>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>translationjob31</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:19.555</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:19.574</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:21.512</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:25.597</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:25.649</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>21:53:27.508</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>1938</v>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>6042</v>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>1859</v>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="n">
+        <v>7953</v>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>translationjob32</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:23.583</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:23.599</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:24.363</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:28.603</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:28.662</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>21:53:28.954</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>764</v>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>5020</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="n">
+        <v>5371</v>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>translationjob33</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:27.691</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:27.708</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:28.366</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:34.979</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:35.045</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>21:53:36.543</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>7288</v>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>1498</v>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="n">
+        <v>8852</v>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>translationjob34</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:29.132</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:29.148</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:29.883</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:34.904</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:34.967</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>21:53:36.554</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>5772</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>1587</v>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="n">
+        <v>7422</v>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>translationjob35</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:36.772</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:36.791</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:38.485</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:42.284</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:42.343</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>21:53:44.141</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>1694</v>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>1.7s</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>5512</v>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>1798</v>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="n">
+        <v>7369</v>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>translationjob36</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:44.331</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:44.348</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:45.839</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:50.858</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:50.918</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>21:53:51.318</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>1491</v>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>6527</v>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="n">
+        <v>6987</v>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>translationjob37</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:51.537</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:51.557</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:52.873</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:57.228</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:57.291</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>21:53:57.571</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>1316</v>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>5691</v>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="n">
+        <v>6034</v>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>translationjob38</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>21:53:57.767</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>21:53:57.785</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>21:53:58.733</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>21:54:04.841</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>21:54:05.052</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>21:54:05.423</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>7074</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="n">
+        <v>7656</v>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>translationjob39</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:00.168</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:00.185</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:01.867</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.205</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.265</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.510</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>1682</v>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>1.7s</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>8037</v>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="n">
+        <v>8342</v>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>translationjob40</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.737</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:08.754</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:09.821</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.042</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.104</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>22:00:16.322</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>1067</v>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>7305</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="n">
+        <v>7585</v>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>translationjob41</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>22:40:47.766</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>22:40:47.784</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>22:40:56.162</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>22:41:01.624</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>22:41:01.666</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>22:41:01.780</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>8378</v>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>13858</v>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>13.9s</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="n">
+        <v>14014</v>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>translationjob42</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:10.183</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:10.201</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:18.290</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:22.709</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:22.763</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>22:41:22.894</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>8089</v>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>12526</v>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>12.5s</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="n">
+        <v>12711</v>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>12.7s</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:31.418</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:31.434</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:39.651</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:45.050</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:45.111</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>22:41:45.265</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>8217</v>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>13632</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="n">
+        <v>13847</v>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>22:41:54.136</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>22:41:54.152</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>22:42:02.481</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>22:42:07.919</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>22:42:07.974</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>22:42:08.088</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>8329</v>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>13783</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:16.456</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:16.473</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:24.572</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:29.681</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:29.745</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>22:42:29.843</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>8099</v>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>13225</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>13.2s</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="n">
+        <v>13387</v>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:38.223</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:38.239</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:46.369</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:52.430</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:52.655</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>22:42:52.798</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>8130</v>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>14207</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>14.2s</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="n">
+        <v>14575</v>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD56"/>
+  <autoFilter ref="A1:AD103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7596,7 +13518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7703,6 +13625,46 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7714,11 +13676,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7732,6 +13695,11 @@
           <t>2026-03-28</t>
         </is>
       </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -7742,6 +13710,9 @@
       <c r="B2" s="5" t="n">
         <v>57696</v>
       </c>
+      <c r="C2" s="5" t="n">
+        <v>58379</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -7752,6 +13723,9 @@
       <c r="B3" s="5" t="n">
         <v>196</v>
       </c>
+      <c r="C3" s="5" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7762,6 +13736,7 @@
       <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="C4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7772,6 +13747,9 @@
       <c r="B5" s="4" t="n">
         <v>13</v>
       </c>
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7782,6 +13760,9 @@
       <c r="B6" s="5" t="n">
         <v>650</v>
       </c>
+      <c r="C6" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7792,6 +13773,9 @@
       <c r="B7" s="5" t="n">
         <v>110</v>
       </c>
+      <c r="C7" s="4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -7802,6 +13786,9 @@
       <c r="B8" s="4" t="n">
         <v>22</v>
       </c>
+      <c r="C8" s="4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7812,6 +13799,9 @@
       <c r="B9" s="4" t="n">
         <v>22</v>
       </c>
+      <c r="C9" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -7822,6 +13812,9 @@
       <c r="B10" s="5" t="n">
         <v>137387</v>
       </c>
+      <c r="C10" s="5" t="n">
+        <v>139498</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7832,6 +13825,9 @@
       <c r="B11" s="5" t="n">
         <v>84030</v>
       </c>
+      <c r="C11" s="5" t="n">
+        <v>83511</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -7842,6 +13838,9 @@
       <c r="B12" s="5" t="n">
         <v>13865</v>
       </c>
+      <c r="C12" s="5" t="n">
+        <v>13356</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -7852,6 +13851,9 @@
       <c r="B13" s="5" t="n">
         <v>1338</v>
       </c>
+      <c r="C13" s="5" t="n">
+        <v>1086</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7862,6 +13864,9 @@
       <c r="B14" s="5" t="n">
         <v>1026</v>
       </c>
+      <c r="C14" s="5" t="n">
+        <v>446</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -7871,6 +13876,9 @@
       </c>
       <c r="B15" s="5" t="n">
         <v>253</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -7884,7 +13892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7958,6 +13966,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>459</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
         <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,15 +99,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD103"/>
+  <dimension ref="A1:AD154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13506,8 +13513,6356 @@
       <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:50.492</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:50.516</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:50.798</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:53.345</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:53.412</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>10:29:53.491</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>2853</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="n">
+        <v>2999</v>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>11:30:48.140</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>11:30:48.161</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>11:30:48.392</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.481</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.554</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.628</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>20341</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>20.3s</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="n">
+        <v>20488</v>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>20.5s</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.766</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.785</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.973</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.255</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.314</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.377</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>14489</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>14.5s</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="n">
+        <v>14611</v>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.452</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.476</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.683</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.266</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.429</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.490</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>16814</v>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>16.8s</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="n">
+        <v>17038</v>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>17.0s</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.675</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.699</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:40.856</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.285</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.342</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.388</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>18610</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>18.6s</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="n">
+        <v>18713</v>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>18.7s</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.470</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.485</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>11:31:59.695</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.561</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.614</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.675</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>14091</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>14.1s</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="n">
+        <v>14205</v>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>14.2s</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.762</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.779</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:13.960</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:42.070</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:42.117</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>11:32:42.172</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>28308</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>28.3s</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="n">
+        <v>28410</v>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>28.4s</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:32.344</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:32.365</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:32.565</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:48.848</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:48.889</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>11:35:48.950</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>16504</v>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>16.5s</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="n">
+        <v>16606</v>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>16.6s</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>11:35:49.045</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>11:35:49.067</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>11:35:49.364</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.615</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.655</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.713</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>16570</v>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>16.6s</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="n">
+        <v>16668</v>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>16.7s</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.813</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.829</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:05.984</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.170</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.211</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.274</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>16357</v>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>16.4s</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="n">
+        <v>16461</v>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>16.5s</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.358</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.375</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:22.520</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:40.747</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:40.798</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>11:36:40.860</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>18389</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>18.4s</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="n">
+        <v>18502</v>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>18.5s</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:40.961</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:40.977</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:41.154</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:58.910</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:58.966</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>11:36:59.015</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>17949</v>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>17.9s</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="n">
+        <v>18054</v>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>18.1s</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>11:36:59.112</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>11:36:59.127</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>11:36:59.274</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>11:37:29.097</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>11:37:29.151</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>11:37:29.204</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>29985</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>30.0s</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="n">
+        <v>30092</v>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>30.1s</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>translationjob95</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:33.570</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:33.596</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:33.867</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.683</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.744</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.817</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>8113</v>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V117" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="n">
+        <v>8247</v>
+      </c>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>translationjob97</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:42.106</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:42.126</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:42.462</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.479</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:48.048</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>12:15:48.133</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>5373</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="n">
+        <v>6027</v>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>translationjob98</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:46.927</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.027</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:47.405</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:52.736</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:52.797</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>12:15:52.853</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>5809</v>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V119" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="n">
+        <v>5926</v>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>translationjob100</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:48.468</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:48.491</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:48.698</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:56.741</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:56.808</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>12:15:56.935</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>8273</v>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>translationjob101</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.167</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.192</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:53.429</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:59.838</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:59.906</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>12:15:59.973</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>6671</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="n">
+        <v>6806</v>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>translationjob103</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>12:15:57.280</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>12:15:57.303</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>12:15:57.575</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>12:16:09.126</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>12:16:09.203</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>12:16:09.263</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>11846</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>11.8s</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="n">
+        <v>11983</v>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>12.0s</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>translationjob104</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:25.914</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:25.933</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:26.248</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:28.571</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:28.629</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>14:38:28.696</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>2657</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="n">
+        <v>2782</v>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>translationjob106</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:28.881</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:28.896</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:29.075</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:30.953</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:31.006</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>14:38:31.055</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="n">
+        <v>2174</v>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>translationjob107</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:31.250</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:31.267</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:31.546</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.100</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.163</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.221</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>translationjob109</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.633</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.662</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:33.847</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:36.539</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:36.611</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>14:38:36.675</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>2906</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="n">
+        <v>3042</v>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>translationjob110</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:36.896</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:36.925</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:37.117</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.217</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.263</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.317</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>2321</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="n">
+        <v>2421</v>
+      </c>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z127" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>translationjob111</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.524</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.541</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:39.721</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:42.023</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:42.071</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>14:38:42.128</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>2499</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="n">
+        <v>2604</v>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>translationjob112</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>15:25:59.984</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>15:25:59.998</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>15:26:00.411</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>15:26:13.517</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>15:26:13.578</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>15:26:13.736</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>13533</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>13.5s</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="n">
+        <v>13752</v>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>translationjob113</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>15:26:06.731</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>15:26:06.748</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>15:26:07.166</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>15:26:07.479</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr"/>
+      <c r="P130" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>748</v>
+      </c>
+      <c r="S130" s="3" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="T130" s="3" t="inlineStr"/>
+      <c r="U130" s="3" t="inlineStr"/>
+      <c r="V130" s="3" t="inlineStr"/>
+      <c r="W130" s="3" t="inlineStr"/>
+      <c r="X130" s="3" t="inlineStr"/>
+      <c r="Y130" s="3" t="inlineStr"/>
+      <c r="Z130" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="3" t="inlineStr"/>
+      <c r="AC130" s="3" t="inlineStr"/>
+      <c r="AD130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>translationjob114</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:08.804</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:08.820</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:09.169</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:24.623</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:24.680</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>15:26:24.818</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>15819</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>15.8s</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="n">
+        <v>16014</v>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>16.0s</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>translationjob115</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>15:26:13.987</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>15:26:14.044</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>15:26:14.416</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>15:26:14.698</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr"/>
+      <c r="O132" s="3" t="inlineStr"/>
+      <c r="P132" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="n">
+        <v>711</v>
+      </c>
+      <c r="S132" s="3" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="T132" s="3" t="inlineStr"/>
+      <c r="U132" s="3" t="inlineStr"/>
+      <c r="V132" s="3" t="inlineStr"/>
+      <c r="W132" s="3" t="inlineStr"/>
+      <c r="X132" s="3" t="inlineStr"/>
+      <c r="Y132" s="3" t="inlineStr"/>
+      <c r="Z132" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="3" t="inlineStr"/>
+      <c r="AC132" s="3" t="inlineStr"/>
+      <c r="AD132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>translationjob116</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:14.937</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:14.966</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:15.281</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:25.941</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:26.038</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>15:26:26.280</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>11004</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>11343</v>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>11.3s</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>translationjob117</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>15:26:25.018</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>15:26:25.036</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>15:26:25.555</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>15:26:25.941</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr"/>
+      <c r="O134" s="3" t="inlineStr"/>
+      <c r="P134" s="3" t="n">
+        <v>519</v>
+      </c>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="n">
+        <v>923</v>
+      </c>
+      <c r="S134" s="3" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="T134" s="3" t="inlineStr"/>
+      <c r="U134" s="3" t="inlineStr"/>
+      <c r="V134" s="3" t="inlineStr"/>
+      <c r="W134" s="3" t="inlineStr"/>
+      <c r="X134" s="3" t="inlineStr"/>
+      <c r="Y134" s="3" t="inlineStr"/>
+      <c r="Z134" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="3" t="inlineStr"/>
+      <c r="AC134" s="3" t="inlineStr"/>
+      <c r="AD134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>translationjob118</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:26.351</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:26.369</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:26.838</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:35.324</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:35.377</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>15:26:35.534</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>8973</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="n">
+        <v>9183</v>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>translationjob119</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:35.790</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:35.808</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:36.264</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:53.930</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:53.990</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>15:26:54.252</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>18140</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>18.1s</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="n">
+        <v>18462</v>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>18.5s</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:01.291</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:01.305</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:01.503</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:04.954</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:04.997</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>21:21:05.048</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>3663</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="n">
+        <v>3757</v>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:05.110</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:05.123</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:05.256</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.357</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.396</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.431</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>2247</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="n">
+        <v>2321</v>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.491</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.504</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:07.616</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.596</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.639</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.686</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>2105</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="n">
+        <v>2195</v>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.790</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.806</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:09.919</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.090</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.128</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.180</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="n">
+        <v>2390</v>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.279</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.292</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:12.413</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:14.857</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:14.899</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>21:21:14.941</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>2578</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="n">
+        <v>2662</v>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:14.997</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:15.011</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:15.194</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:18.606</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:18.642</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>21:21:18.680</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>3609</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>3683</v>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:52.263</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:52.276</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:52.418</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.218</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.258</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.304</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>2955</v>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="n">
+        <v>3041</v>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.382</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.396</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:55.538</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.402</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.436</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.473</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>3020</v>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>3091</v>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z144" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.586</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.598</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>21:27:58.722</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.156</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.204</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.262</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>2570</v>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="n">
+        <v>2676</v>
+      </c>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z145" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.338</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.352</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:01.509</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.372</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.409</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.461</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>3034</v>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>3123</v>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z146" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.596</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.608</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:04.750</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.359</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.402</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.446</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>2763</v>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="Y147" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z147" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.551</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.563</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:07.750</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:11.041</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:11.079</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>21:28:11.122</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>3490</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>3571</v>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:07.963</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:07.983</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:08.818</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:14.406</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:14.459</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>21:58:14.882</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>6443</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="n">
+        <v>6919</v>
+      </c>
+      <c r="Y149" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="Z149" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:15.075</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:15.092</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:15.735</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:20.166</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:20.311</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>21:58:20.681</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>5091</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>5606</v>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z150" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:21.756</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:21.793</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:23.300</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:27.750</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:27.902</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>21:58:29.696</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>1507</v>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>5994</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>1794</v>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="n">
+        <v>7940</v>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:29.843</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:29.864</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:30.638</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:37.212</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:37.259</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>21:58:37.543</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>7369</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>7700</v>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:37.657</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:37.672</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:38.464</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:43.984</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:44.107</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>21:58:44.393</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>6327</v>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>6736</v>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="Z153" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:44.504</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:44.526</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:45.352</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:50.823</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:50.877</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>21:58:51.257</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>6319</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>6753</v>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD103"/>
+  <autoFilter ref="A1:AD154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13518,7 +19873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13534,134 +19889,174 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Stuck</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Retried</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Avg Duration</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Min Duration</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Max Duration</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>10.5s</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>2.0s</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>1m 14.9s</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>6.3s</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>3.2s</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>14.6s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>30.1s</t>
         </is>
       </c>
     </row>
@@ -13676,209 +20071,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Error Category</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Language copy not found</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>57696</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>58379</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>34530</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Content LC unknown state</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>196</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>110</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Failed to start translation</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Error processing Translation project</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TranslationCleanupJobConsumer</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>650</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="D6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ThumbnailServlet</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>40</v>
       </c>
+      <c r="D7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TicketAssemblyTranslationServiceImpl</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>12</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GCCScriptProcessor</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>9</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ReplicationSquadListener</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>137387</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>139498</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>135496</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ReplicationNewsAssemblyListener</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>84030</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>83511</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>28457</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ResourceUtils commit</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>13865</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>13356</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11684</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>LockUtil contention</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>1338</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>1086</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1016</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TranslateHrefAttributes</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>1026</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>446</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>818</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Error executing workflow</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>267</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -13892,7 +20329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13905,89 +20342,114 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Entries</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Obtained</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Expires</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Token Size Entries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>579</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>193</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>193</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>193</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>459</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>378</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD238"/>
+  <dimension ref="A1:AD300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30445,8 +30445,7820 @@
       <c r="AC238" s="2" t="inlineStr"/>
       <c r="AD238" s="2" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:47.649</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:47.669</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:47.938</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:52.937</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:52.983</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>06:35:53.090</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="n">
+        <v>5288</v>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U239" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V239" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="W239" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X239" s="2" t="n">
+        <v>5441</v>
+      </c>
+      <c r="Y239" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z239" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA239" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB239" s="2" t="inlineStr"/>
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:53.399</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:53.422</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:53.624</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:56.762</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:56.814</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>06:35:56.865</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="n">
+        <v>3363</v>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U240" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V240" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W240" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X240" s="2" t="n">
+        <v>3466</v>
+      </c>
+      <c r="Y240" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="Z240" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA240" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB240" s="2" t="inlineStr"/>
+      <c r="AC240" s="2" t="inlineStr"/>
+      <c r="AD240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>06:35:57.025</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>06:35:57.044</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>06:35:57.250</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>06:36:00.748</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>06:36:00.802</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>06:36:00.864</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="n">
+        <v>3723</v>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U241" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V241" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W241" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X241" s="2" t="n">
+        <v>3839</v>
+      </c>
+      <c r="Y241" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z241" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA241" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB241" s="2" t="inlineStr"/>
+      <c r="AC241" s="2" t="inlineStr"/>
+      <c r="AD241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:01.033</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:01.052</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:01.259</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.274</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.318</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.388</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="n">
+        <v>4241</v>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U242" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V242" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W242" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X242" s="2" t="n">
+        <v>4355</v>
+      </c>
+      <c r="Y242" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="Z242" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA242" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB242" s="2" t="inlineStr"/>
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.558</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.576</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:05.983</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:09.935</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:10.009</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>06:36:10.079</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="n">
+        <v>4377</v>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="U243" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V243" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W243" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X243" s="2" t="n">
+        <v>4521</v>
+      </c>
+      <c r="Y243" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="Z243" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA243" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB243" s="2" t="inlineStr"/>
+      <c r="AC243" s="2" t="inlineStr"/>
+      <c r="AD243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:10.254</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:10.272</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:10.469</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:15.950</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:16.012</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>06:36:16.065</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="n">
+        <v>5696</v>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U244" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V244" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W244" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X244" s="2" t="n">
+        <v>5811</v>
+      </c>
+      <c r="Y244" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z244" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA244" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB244" s="2" t="inlineStr"/>
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>translationjob47</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:36.961</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:36.989</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:37.308</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:43.195</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:43.482</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>09:19:43.547</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>6234</v>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="U245" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V245" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="n">
+        <v>6586</v>
+      </c>
+      <c r="Y245" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z245" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA245" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>translationjob48</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:26.227</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:26.247</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:26.987</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:35.602</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:35.658</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>11:20:35.827</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="n">
+        <v>9375</v>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U246" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V246" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W246" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X246" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="Y246" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="Z246" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB246" s="2" t="inlineStr"/>
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>translationjob49</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:36.057</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:36.076</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:36.494</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:42.340</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:42.406</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>11:20:42.528</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="n">
+        <v>6283</v>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U247" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V247" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="W247" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X247" s="2" t="n">
+        <v>6471</v>
+      </c>
+      <c r="Y247" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z247" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB247" s="2" t="inlineStr"/>
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>translationjob50</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:42.732</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:42.751</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:43.313</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.012</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.067</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.179</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="n">
+        <v>8280</v>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U248" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V248" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="W248" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X248" s="2" t="n">
+        <v>8447</v>
+      </c>
+      <c r="Y248" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z248" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA248" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB248" s="2" t="inlineStr"/>
+      <c r="AC248" s="2" t="inlineStr"/>
+      <c r="AD248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>translationjob51</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.389</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.407</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>11:20:51.845</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>11:21:03.335</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>11:21:03.393</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>11:21:03.505</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="n">
+        <v>11946</v>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>11.9s</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U249" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V249" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="W249" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X249" s="2" t="n">
+        <v>12116</v>
+      </c>
+      <c r="Y249" s="2" t="inlineStr">
+        <is>
+          <t>12.1s</t>
+        </is>
+      </c>
+      <c r="Z249" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB249" s="2" t="inlineStr"/>
+      <c r="AC249" s="2" t="inlineStr"/>
+      <c r="AD249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>translationjob52</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:03.775</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:03.801</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:04.613</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.079</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.144</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.248</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="n">
+        <v>8304</v>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U250" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V250" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W250" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X250" s="2" t="n">
+        <v>8473</v>
+      </c>
+      <c r="Y250" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z250" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA250" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB250" s="2" t="inlineStr"/>
+      <c r="AC250" s="2" t="inlineStr"/>
+      <c r="AD250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>translationjob53</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.498</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.518</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:12.969</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:25.724</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:25.790</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>11:21:25.921</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="n">
+        <v>13226</v>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>13.2s</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U251" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V251" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="W251" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X251" s="2" t="n">
+        <v>13423</v>
+      </c>
+      <c r="Y251" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="Z251" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA251" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB251" s="2" t="inlineStr"/>
+      <c r="AC251" s="2" t="inlineStr"/>
+      <c r="AD251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:21.595</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:21.615</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:21.808</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.360</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.396</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.446</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="n">
+        <v>11765</v>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>11.8s</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U252" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V252" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W252" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X252" s="2" t="n">
+        <v>11851</v>
+      </c>
+      <c r="Y252" s="2" t="inlineStr">
+        <is>
+          <t>11.9s</t>
+        </is>
+      </c>
+      <c r="Z252" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA252" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB252" s="2" t="inlineStr"/>
+      <c r="AC252" s="2" t="inlineStr"/>
+      <c r="AD252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.587</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.600</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:33.735</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.188</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.227</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.343</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="n">
+        <v>9601</v>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U253" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V253" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="W253" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X253" s="2" t="n">
+        <v>9756</v>
+      </c>
+      <c r="Y253" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="Z253" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA253" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB253" s="2" t="inlineStr"/>
+      <c r="AC253" s="2" t="inlineStr"/>
+      <c r="AD253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.456</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.469</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:43.608</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.344</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.387</t>
+        </is>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.432</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="n">
+        <v>10888</v>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>10.9s</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U254" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V254" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W254" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X254" s="2" t="n">
+        <v>10976</v>
+      </c>
+      <c r="Y254" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="Z254" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB254" s="2" t="inlineStr"/>
+      <c r="AC254" s="2" t="inlineStr"/>
+      <c r="AD254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.539</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.553</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>17:19:54.721</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.352</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.390</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.437</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="n">
+        <v>13813</v>
+      </c>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U255" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V255" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W255" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X255" s="2" t="n">
+        <v>13898</v>
+      </c>
+      <c r="Y255" s="2" t="inlineStr">
+        <is>
+          <t>13.9s</t>
+        </is>
+      </c>
+      <c r="Z255" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA255" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB255" s="2" t="inlineStr"/>
+      <c r="AC255" s="2" t="inlineStr"/>
+      <c r="AD255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>translationjob47</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.549</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.562</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:08.707</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.094</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.133</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.186</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="n">
+        <v>10545</v>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>10.5s</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U256" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V256" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W256" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X256" s="2" t="n">
+        <v>10637</v>
+      </c>
+      <c r="Y256" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="Z256" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA256" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB256" s="2" t="inlineStr"/>
+      <c r="AC256" s="2" t="inlineStr"/>
+      <c r="AD256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>translationjob48</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.319</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.332</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:19.459</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:37.252</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:37.293</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>17:20:37.333</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="n">
+        <v>17933</v>
+      </c>
+      <c r="S257" s="2" t="inlineStr">
+        <is>
+          <t>17.9s</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U257" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V257" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="W257" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X257" s="2" t="n">
+        <v>18014</v>
+      </c>
+      <c r="Y257" s="2" t="inlineStr">
+        <is>
+          <t>18.0s</t>
+        </is>
+      </c>
+      <c r="Z257" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA257" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB257" s="2" t="inlineStr"/>
+      <c r="AC257" s="2" t="inlineStr"/>
+      <c r="AD257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>translationjob49</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:42.222</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:42.238</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:42.719</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:46.594</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:46.647</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>17:50:47.080</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="n">
+        <v>4372</v>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U258" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V258" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="W258" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X258" s="2" t="n">
+        <v>4858</v>
+      </c>
+      <c r="Y258" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z258" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA258" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB258" s="2" t="inlineStr"/>
+      <c r="AC258" s="2" t="inlineStr"/>
+      <c r="AD258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>translationjob50</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:47.262</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:47.277</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:47.597</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:50.538</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:50.604</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>17:50:50.829</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="n">
+        <v>3276</v>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U259" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V259" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="W259" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X259" s="2" t="n">
+        <v>3567</v>
+      </c>
+      <c r="Y259" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z259" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB259" s="2" t="inlineStr"/>
+      <c r="AC259" s="2" t="inlineStr"/>
+      <c r="AD259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>translationjob51</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:51.104</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:51.124</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:51.489</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:54.724</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:54.786</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>17:50:54.946</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="n">
+        <v>3620</v>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U260" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V260" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X260" s="2" t="n">
+        <v>3842</v>
+      </c>
+      <c r="Y260" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z260" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB260" s="2" t="inlineStr"/>
+      <c r="AC260" s="2" t="inlineStr"/>
+      <c r="AD260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>translationjob52</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>17:50:55.170</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>17:50:55.193</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>17:50:55.758</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>17:51:00.903</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>17:51:00.965</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>17:51:01.148</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="n">
+        <v>5733</v>
+      </c>
+      <c r="S261" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U261" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V261" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="W261" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X261" s="2" t="n">
+        <v>5978</v>
+      </c>
+      <c r="Y261" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z261" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB261" s="2" t="inlineStr"/>
+      <c r="AC261" s="2" t="inlineStr"/>
+      <c r="AD261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>translationjob53</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:01.326</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:01.350</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:01.724</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:05.285</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:05.336</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>17:51:05.497</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="n">
+        <v>3959</v>
+      </c>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U262" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V262" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="W262" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X262" s="2" t="n">
+        <v>4171</v>
+      </c>
+      <c r="Y262" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z262" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB262" s="2" t="inlineStr"/>
+      <c r="AC262" s="2" t="inlineStr"/>
+      <c r="AD262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>translationjob54</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:05.765</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:05.783</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:06.132</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:16.070</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:16.153</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>17:51:16.315</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="n">
+        <v>10305</v>
+      </c>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>10.3s</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="U263" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V263" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X263" s="2" t="n">
+        <v>10550</v>
+      </c>
+      <c r="Y263" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="Z263" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB263" s="2" t="inlineStr"/>
+      <c r="AC263" s="2" t="inlineStr"/>
+      <c r="AD263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>translationjob56</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:40.495</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:40.519</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:41.660</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:48.771</t>
+        </is>
+      </c>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:48.831</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>17:55:49.244</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="n">
+        <v>1141</v>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="n">
+        <v>8276</v>
+      </c>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U264" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V264" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="W264" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X264" s="2" t="n">
+        <v>8749</v>
+      </c>
+      <c r="Y264" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="Z264" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB264" s="2" t="inlineStr"/>
+      <c r="AC264" s="2" t="inlineStr"/>
+      <c r="AD264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>translationjob57</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:49.398</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:49.421</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:50.030</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:56.349</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:56.414</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>17:55:56.983</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="n">
+        <v>6951</v>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U265" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V265" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="n">
+        <v>7585</v>
+      </c>
+      <c r="Y265" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z265" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA265" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB265" s="2" t="inlineStr"/>
+      <c r="AC265" s="2" t="inlineStr"/>
+      <c r="AD265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>translationjob58</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>17:55:57.269</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>17:55:57.286</t>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>17:55:58.771</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>17:56:07.903</t>
+        </is>
+      </c>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>17:56:07.962</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>17:56:09.978</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="n">
+        <v>10634</v>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U266" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V266" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="W266" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="X266" s="2" t="n">
+        <v>12709</v>
+      </c>
+      <c r="Y266" s="2" t="inlineStr">
+        <is>
+          <t>12.7s</t>
+        </is>
+      </c>
+      <c r="Z266" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA266" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB266" s="2" t="inlineStr"/>
+      <c r="AC266" s="2" t="inlineStr"/>
+      <c r="AD266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>translationjob62</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:10.121</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:10.138</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:10.961</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:21.575</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:21.641</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>17:56:21.930</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="n">
+        <v>11454</v>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>11.5s</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U267" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V267" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="n">
+        <v>11809</v>
+      </c>
+      <c r="Y267" s="2" t="inlineStr">
+        <is>
+          <t>11.8s</t>
+        </is>
+      </c>
+      <c r="Z267" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB267" s="2" t="inlineStr"/>
+      <c r="AC267" s="2" t="inlineStr"/>
+      <c r="AD267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>translationjob63</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:18.276</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:18.294</t>
+        </is>
+      </c>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:18.604</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:23.235</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:23.296</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>17:56:23.472</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="n">
+        <v>4959</v>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U268" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V268" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="n">
+        <v>5196</v>
+      </c>
+      <c r="Y268" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z268" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB268" s="2" t="inlineStr"/>
+      <c r="AC268" s="2" t="inlineStr"/>
+      <c r="AD268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>translationjob64</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:22.116</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:22.137</t>
+        </is>
+      </c>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:22.954</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:30.079</t>
+        </is>
+      </c>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:30.688</t>
+        </is>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>17:56:31.004</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="n">
+        <v>7963</v>
+      </c>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="U269" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="V269" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="W269" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X269" s="2" t="n">
+        <v>8888</v>
+      </c>
+      <c r="Y269" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z269" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB269" s="2" t="inlineStr"/>
+      <c r="AC269" s="2" t="inlineStr"/>
+      <c r="AD269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>translationjob65</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:23.719</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:23.737</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:24.106</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:29.096</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:29.153</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>17:56:29.358</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="n">
+        <v>5377</v>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U270" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V270" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="W270" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X270" s="2" t="n">
+        <v>5639</v>
+      </c>
+      <c r="Y270" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z270" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB270" s="2" t="inlineStr"/>
+      <c r="AC270" s="2" t="inlineStr"/>
+      <c r="AD270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>translationjob66</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:29.562</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:29.589</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:30.026</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.271</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.320</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.461</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="n">
+        <v>4709</v>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U271" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="n">
+        <v>4899</v>
+      </c>
+      <c r="Y271" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB271" s="2" t="inlineStr"/>
+      <c r="AC271" s="2" t="inlineStr"/>
+      <c r="AD271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>translationjob67</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:31.186</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:31.203</t>
+        </is>
+      </c>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:32.329</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:41.626</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:41.685</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>17:56:42.062</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="n">
+        <v>10440</v>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V272" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="n">
+        <v>10876</v>
+      </c>
+      <c r="Y272" s="2" t="inlineStr">
+        <is>
+          <t>10.9s</t>
+        </is>
+      </c>
+      <c r="Z272" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB272" s="2" t="inlineStr"/>
+      <c r="AC272" s="2" t="inlineStr"/>
+      <c r="AD272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>translationjob68</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.635</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.652</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:34.978</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:41.764</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:41.821</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>17:56:42.026</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="n">
+        <v>7129</v>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U273" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="n">
+        <v>7391</v>
+      </c>
+      <c r="Y273" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z273" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB273" s="2" t="inlineStr"/>
+      <c r="AC273" s="2" t="inlineStr"/>
+      <c r="AD273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>translationjob69</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:42.185</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:42.201</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:42.626</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.075</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.132</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.282</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="n">
+        <v>5890</v>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U274" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V274" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="n">
+        <v>6097</v>
+      </c>
+      <c r="Y274" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB274" s="2" t="inlineStr"/>
+      <c r="AC274" s="2" t="inlineStr"/>
+      <c r="AD274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>translationjob70</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:47.099</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:47.119</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:47.437</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.180</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.235</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.370</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="n">
+        <v>12081</v>
+      </c>
+      <c r="S275" s="2" t="inlineStr">
+        <is>
+          <t>12.1s</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U275" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V275" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="n">
+        <v>12271</v>
+      </c>
+      <c r="Y275" s="2" t="inlineStr">
+        <is>
+          <t>12.3s</t>
+        </is>
+      </c>
+      <c r="Z275" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB275" s="2" t="inlineStr"/>
+      <c r="AC275" s="2" t="inlineStr"/>
+      <c r="AD275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>translationjob71</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.437</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.455</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:48.888</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:54.857</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:54.914</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>17:56:55.066</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="n">
+        <v>6420</v>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V276" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X276" s="2" t="n">
+        <v>6629</v>
+      </c>
+      <c r="Y276" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z276" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB276" s="2" t="inlineStr"/>
+      <c r="AC276" s="2" t="inlineStr"/>
+      <c r="AD276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>translationjob72</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.592</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.613</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>17:56:59.951</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>17:57:05.335</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>17:57:05.393</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>17:57:05.560</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="n">
+        <v>5743</v>
+      </c>
+      <c r="S277" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U277" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V277" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="n">
+        <v>5968</v>
+      </c>
+      <c r="Y277" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z277" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB277" s="2" t="inlineStr"/>
+      <c r="AC277" s="2" t="inlineStr"/>
+      <c r="AD277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>translationjob73</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:05.772</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:05.789</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:06.362</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:11.339</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:11.402</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>17:57:11.623</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="n">
+        <v>573</v>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="n">
+        <v>5567</v>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U278" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V278" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="n">
+        <v>5851</v>
+      </c>
+      <c r="Y278" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA278" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB278" s="2" t="inlineStr"/>
+      <c r="AC278" s="2" t="inlineStr"/>
+      <c r="AD278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>translationjob74</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:11.847</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:11.868</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:12.277</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:20.255</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:20.316</t>
+        </is>
+      </c>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>17:57:20.461</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="n">
+        <v>8408</v>
+      </c>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U279" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V279" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="W279" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="n">
+        <v>8614</v>
+      </c>
+      <c r="Y279" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="Z279" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA279" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB279" s="2" t="inlineStr"/>
+      <c r="AC279" s="2" t="inlineStr"/>
+      <c r="AD279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>translationjob75</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:20.652</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:20.666</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:21.061</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:26.417</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:26.478</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>17:57:26.619</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="n">
+        <v>5765</v>
+      </c>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U280" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V280" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="n">
+        <v>5967</v>
+      </c>
+      <c r="Y280" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z280" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB280" s="2" t="inlineStr"/>
+      <c r="AC280" s="2" t="inlineStr"/>
+      <c r="AD280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>translationjob76</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:26.827</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:26.845</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:27.930</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:39.426</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:39.486</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>17:57:39.664</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="n">
+        <v>1085</v>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="n">
+        <v>12599</v>
+      </c>
+      <c r="S281" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U281" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V281" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="n">
+        <v>12837</v>
+      </c>
+      <c r="Y281" s="2" t="inlineStr">
+        <is>
+          <t>12.8s</t>
+        </is>
+      </c>
+      <c r="Z281" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB281" s="2" t="inlineStr"/>
+      <c r="AC281" s="2" t="inlineStr"/>
+      <c r="AD281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>translationjob77</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>18:37:58.092</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>18:37:58.106</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>18:37:58.494</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.269</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.313</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.409</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="n">
+        <v>5177</v>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U282" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V282" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X282" s="2" t="n">
+        <v>5317</v>
+      </c>
+      <c r="Y282" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="Z282" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB282" s="2" t="inlineStr"/>
+      <c r="AC282" s="2" t="inlineStr"/>
+      <c r="AD282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>translationjob78</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.530</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.545</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:03.936</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:07.927</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:07.970</t>
+        </is>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>18:38:08.089</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="n">
+        <v>4397</v>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U283" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V283" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="W283" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X283" s="2" t="n">
+        <v>4559</v>
+      </c>
+      <c r="Y283" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z283" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA283" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB283" s="2" t="inlineStr"/>
+      <c r="AC283" s="2" t="inlineStr"/>
+      <c r="AD283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>translationjob79</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:08.226</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:08.241</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:08.550</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:12.390</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:12.432</t>
+        </is>
+      </c>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>18:38:12.530</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="n">
+        <v>4164</v>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U284" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V284" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W284" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X284" s="2" t="n">
+        <v>4304</v>
+      </c>
+      <c r="Y284" s="2" t="inlineStr">
+        <is>
+          <t>4.3s</t>
+        </is>
+      </c>
+      <c r="Z284" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA284" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB284" s="2" t="inlineStr"/>
+      <c r="AC284" s="2" t="inlineStr"/>
+      <c r="AD284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>translationjob80</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:12.673</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:12.691</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:13.041</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:18.981</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:19.032</t>
+        </is>
+      </c>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>18:38:19.131</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="n">
+        <v>6308</v>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U285" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V285" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W285" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X285" s="2" t="n">
+        <v>6458</v>
+      </c>
+      <c r="Y285" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z285" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA285" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB285" s="2" t="inlineStr"/>
+      <c r="AC285" s="2" t="inlineStr"/>
+      <c r="AD285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>translationjob81</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:19.261</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:19.275</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:19.586</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:23.790</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:23.837</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>18:38:23.939</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="n">
+        <v>4529</v>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U286" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V286" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="W286" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X286" s="2" t="n">
+        <v>4678</v>
+      </c>
+      <c r="Y286" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z286" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA286" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB286" s="2" t="inlineStr"/>
+      <c r="AC286" s="2" t="inlineStr"/>
+      <c r="AD286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>translationjob82</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:24.081</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:24.096</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:24.381</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:28.638</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:28.681</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>18:38:28.795</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="n">
+        <v>4557</v>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U287" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V287" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W287" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X287" s="2" t="n">
+        <v>4714</v>
+      </c>
+      <c r="Y287" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z287" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA287" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB287" s="2" t="inlineStr"/>
+      <c r="AC287" s="2" t="inlineStr"/>
+      <c r="AD287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>translationjob83</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:31.862</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:31.875</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:32.068</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.489</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.531</t>
+        </is>
+      </c>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.595</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="n">
+        <v>10627</v>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V288" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W288" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X288" s="2" t="n">
+        <v>10733</v>
+      </c>
+      <c r="Y288" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="Z288" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA288" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB288" s="2" t="inlineStr"/>
+      <c r="AC288" s="2" t="inlineStr"/>
+      <c r="AD288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>translationjob84</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.742</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.758</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:42.906</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:52.634</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:52.684</t>
+        </is>
+      </c>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>21:46:52.743</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="n">
+        <v>9892</v>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U289" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V289" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W289" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X289" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="Y289" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB289" s="2" t="inlineStr"/>
+      <c r="AC289" s="2" t="inlineStr"/>
+      <c r="AD289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>translationjob85</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>21:46:52.876</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>21:46:52.892</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>21:46:53.047</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>21:47:07.729</t>
+        </is>
+      </c>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>21:47:07.781</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>21:47:07.827</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="n">
+        <v>14853</v>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>14.9s</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V290" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="W290" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X290" s="2" t="n">
+        <v>14951</v>
+      </c>
+      <c r="Y290" s="2" t="inlineStr">
+        <is>
+          <t>15.0s</t>
+        </is>
+      </c>
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA290" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB290" s="2" t="inlineStr"/>
+      <c r="AC290" s="2" t="inlineStr"/>
+      <c r="AD290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>translationjob86</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:07.955</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:07.971</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:08.116</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.267</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.306</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.362</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="n">
+        <v>13312</v>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V291" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W291" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X291" s="2" t="n">
+        <v>13407</v>
+      </c>
+      <c r="Y291" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="Z291" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB291" s="2" t="inlineStr"/>
+      <c r="AC291" s="2" t="inlineStr"/>
+      <c r="AD291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>translationjob87</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.516</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.534</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:21.707</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.244</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.289</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.341</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="n">
+        <v>15728</v>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>15.7s</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V292" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="n">
+        <v>15825</v>
+      </c>
+      <c r="Y292" s="2" t="inlineStr">
+        <is>
+          <t>15.8s</t>
+        </is>
+      </c>
+      <c r="Z292" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB292" s="2" t="inlineStr"/>
+      <c r="AC292" s="2" t="inlineStr"/>
+      <c r="AD292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>translationjob88</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.495</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.512</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:37.661</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:55.575</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:55.620</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>21:47:55.675</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="n">
+        <v>18080</v>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>18.1s</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V293" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="n">
+        <v>18180</v>
+      </c>
+      <c r="Y293" s="2" t="inlineStr">
+        <is>
+          <t>18.2s</t>
+        </is>
+      </c>
+      <c r="Z293" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB293" s="2" t="inlineStr"/>
+      <c r="AC293" s="2" t="inlineStr"/>
+      <c r="AD293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>translationjob89</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:41.230</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:41.248</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:41.471</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:43.840</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:43.893</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>22:17:43.957</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="n">
+        <v>2610</v>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U294" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V294" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="n">
+        <v>2727</v>
+      </c>
+      <c r="Y294" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA294" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB294" s="2" t="inlineStr"/>
+      <c r="AC294" s="2" t="inlineStr"/>
+      <c r="AD294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>translationjob90</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:44.120</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:44.138</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:44.301</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.188</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.245</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.300</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="n">
+        <v>2068</v>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U295" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V295" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="n">
+        <v>2180</v>
+      </c>
+      <c r="Y295" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA295" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB295" s="2" t="inlineStr"/>
+      <c r="AC295" s="2" t="inlineStr"/>
+      <c r="AD295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>translationjob91</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.522</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.540</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:46.726</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:48.805</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:48.868</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>22:17:48.924</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="n">
+        <v>2283</v>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V296" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="n">
+        <v>2402</v>
+      </c>
+      <c r="Y296" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB296" s="2" t="inlineStr"/>
+      <c r="AC296" s="2" t="inlineStr"/>
+      <c r="AD296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>translationjob92</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:49.091</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:49.110</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:49.364</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:51.939</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:51.996</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>22:17:52.062</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="n">
+        <v>2848</v>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V297" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="n">
+        <v>2971</v>
+      </c>
+      <c r="Y297" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z297" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA297" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB297" s="2" t="inlineStr"/>
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>translationjob93</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:52.256</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:52.277</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:52.443</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.287</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.342</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.391</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V298" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="n">
+        <v>2135</v>
+      </c>
+      <c r="Y298" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="Z298" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA298" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB298" s="2" t="inlineStr"/>
+      <c r="AC298" s="2" t="inlineStr"/>
+      <c r="AD298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>translationjob94</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.529</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.547</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:54.734</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:57.522</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:57.664</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>22:17:57.733</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="n">
+        <v>2993</v>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V299" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="n">
+        <v>3204</v>
+      </c>
+      <c r="Y299" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB299" s="2" t="inlineStr"/>
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>translationjob95</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:23.407</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:23.420</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:23.596</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:32.148</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:32.189</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>22:36:32.288</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="n">
+        <v>8741</v>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V300" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W300" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X300" s="2" t="n">
+        <v>8881</v>
+      </c>
+      <c r="Y300" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z300" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB300" s="2" t="inlineStr"/>
+      <c r="AC300" s="2" t="inlineStr"/>
+      <c r="AD300" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD238"/>
+  <autoFilter ref="A1:AD300"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30457,7 +38269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30684,6 +38496,46 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>18.2s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30695,7 +38547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30703,6 +38555,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30731,6 +38584,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -30750,6 +38608,9 @@
       <c r="E2" s="6" t="n">
         <v>269</v>
       </c>
+      <c r="F2" s="6" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -30767,6 +38628,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -30780,6 +38642,7 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -30799,6 +38662,7 @@
       <c r="E5" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -30814,6 +38678,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -30829,6 +38694,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -30846,6 +38712,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -30863,6 +38730,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -30882,6 +38750,9 @@
       <c r="E10" s="6" t="n">
         <v>124868</v>
       </c>
+      <c r="F10" s="6" t="n">
+        <v>126932</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -30899,6 +38770,7 @@
         <v>28457</v>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -30918,6 +38790,9 @@
       <c r="E12" s="6" t="n">
         <v>10478</v>
       </c>
+      <c r="F12" s="6" t="n">
+        <v>10480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -30937,6 +38812,9 @@
       <c r="E13" s="6" t="n">
         <v>1182</v>
       </c>
+      <c r="F13" s="6" t="n">
+        <v>1376</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -30956,6 +38834,9 @@
       <c r="E14" s="6" t="n">
         <v>974</v>
       </c>
+      <c r="F14" s="6" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -30974,6 +38855,9 @@
       </c>
       <c r="E15" s="5" t="n">
         <v>11</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -30987,7 +38871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31136,6 +39020,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$344</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$381</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
         <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFFAFE"/>
+        <bgColor rgb="00CFFAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,15 +99,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD344"/>
+  <dimension ref="A1:AD381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43872,8 +43879,4676 @@
       <c r="AC344" s="2" t="inlineStr"/>
       <c r="AD344" s="2" t="inlineStr"/>
     </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>translationjob165</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>03:39:47.232</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>03:39:47.250</t>
+        </is>
+      </c>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>03:40:59.414</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>03:41:18.794</t>
+        </is>
+      </c>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>03:41:18.844</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>03:41:20.772</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>72164</v>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>1m 12.2s</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="n">
+        <v>91562</v>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>1m 31.6s</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U345" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V345" s="2" t="n">
+        <v>1928</v>
+      </c>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="n">
+        <v>93540</v>
+      </c>
+      <c r="Y345" s="2" t="inlineStr">
+        <is>
+          <t>1m 33.5s</t>
+        </is>
+      </c>
+      <c r="Z345" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB345" s="2" t="inlineStr"/>
+      <c r="AC345" s="2" t="inlineStr"/>
+      <c r="AD345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>translationjob166</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>03:41:51.205</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>03:41:51.221</t>
+        </is>
+      </c>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>03:43:03.282</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>03:43:24.400</t>
+        </is>
+      </c>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>03:43:24.450</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>03:43:25.908</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>72061</v>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>1m 12.1s</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="n">
+        <v>93195</v>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>1m 33.2s</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U346" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V346" s="2" t="n">
+        <v>1458</v>
+      </c>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="n">
+        <v>94703</v>
+      </c>
+      <c r="Y346" s="2" t="inlineStr">
+        <is>
+          <t>1m 34.7s</t>
+        </is>
+      </c>
+      <c r="Z346" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB346" s="2" t="inlineStr"/>
+      <c r="AC346" s="2" t="inlineStr"/>
+      <c r="AD346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>translationjob167</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>03:43:57.197</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>03:43:57.212</t>
+        </is>
+      </c>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>03:46:04.297</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>03:46:28.562</t>
+        </is>
+      </c>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>03:46:28.609</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>03:46:29.992</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>127085</v>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>2m 7.1s</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="n">
+        <v>151365</v>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>2m 31.4s</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U347" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V347" s="2" t="n">
+        <v>1383</v>
+      </c>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="n">
+        <v>152795</v>
+      </c>
+      <c r="Y347" s="2" t="inlineStr">
+        <is>
+          <t>2m 32.8s</t>
+        </is>
+      </c>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB347" s="2" t="inlineStr"/>
+      <c r="AC347" s="2" t="inlineStr"/>
+      <c r="AD347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>translationjob168</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>03:47:00.940</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>03:47:00.956</t>
+        </is>
+      </c>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>03:48:11.901</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>03:48:34.485</t>
+        </is>
+      </c>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>03:48:34.538</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>03:48:35.954</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>70945</v>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>1m 10.9s</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="n">
+        <v>93545</v>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>1m 33.5s</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U348" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="n">
+        <v>95014</v>
+      </c>
+      <c r="Y348" s="2" t="inlineStr">
+        <is>
+          <t>1m 35.0s</t>
+        </is>
+      </c>
+      <c r="Z348" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:4, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB348" s="2" t="inlineStr"/>
+      <c r="AC348" s="2" t="inlineStr"/>
+      <c r="AD348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>translationjob169</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>03:49:06.685</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>03:49:06.701</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>03:50:23.273</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>03:50:55.252</t>
+        </is>
+      </c>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>03:50:55.303</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>03:50:56.599</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>76572</v>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>1m 16.6s</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="n">
+        <v>108567</v>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>1m 48.6s</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U349" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V349" s="2" t="n">
+        <v>1296</v>
+      </c>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="n">
+        <v>109914</v>
+      </c>
+      <c r="Y349" s="2" t="inlineStr">
+        <is>
+          <t>1m 49.9s</t>
+        </is>
+      </c>
+      <c r="Z349" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB349" s="2" t="inlineStr"/>
+      <c r="AC349" s="2" t="inlineStr"/>
+      <c r="AD349" s="2" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>translationjob170</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>03:51:28.895</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>03:51:28.915</t>
+        </is>
+      </c>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>03:52:39.679</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>03:53:05.553</t>
+        </is>
+      </c>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>03:53:05.594</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>03:53:06.947</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>70764</v>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>1m 10.8s</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="n">
+        <v>96658</v>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>1m 36.7s</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U350" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V350" s="2" t="n">
+        <v>1353</v>
+      </c>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="n">
+        <v>98052</v>
+      </c>
+      <c r="Y350" s="2" t="inlineStr">
+        <is>
+          <t>1m 38.1s</t>
+        </is>
+      </c>
+      <c r="Z350" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:3, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA350" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB350" s="2" t="inlineStr"/>
+      <c r="AC350" s="2" t="inlineStr"/>
+      <c r="AD350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>translationjob96</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:49.874</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:49.895</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:50.185</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:54.445</t>
+        </is>
+      </c>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:54.497</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>08:24:54.573</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>4571</v>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U351" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V351" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="n">
+        <v>4699</v>
+      </c>
+      <c r="Y351" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z351" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB351" s="2" t="inlineStr"/>
+      <c r="AC351" s="2" t="inlineStr"/>
+      <c r="AD351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>translationjob97</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F352" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I352" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J352" s="3" t="inlineStr">
+        <is>
+          <t>11:40:44.038</t>
+        </is>
+      </c>
+      <c r="K352" s="3" t="inlineStr">
+        <is>
+          <t>11:40:44.067</t>
+        </is>
+      </c>
+      <c r="L352" s="3" t="inlineStr">
+        <is>
+          <t>11:40:45.115</t>
+        </is>
+      </c>
+      <c r="M352" s="3" t="inlineStr">
+        <is>
+          <t>11:41:21.217</t>
+        </is>
+      </c>
+      <c r="N352" s="3" t="inlineStr">
+        <is>
+          <t>11:41:21.266</t>
+        </is>
+      </c>
+      <c r="O352" s="3" t="inlineStr">
+        <is>
+          <t>11:41:21.490</t>
+        </is>
+      </c>
+      <c r="P352" s="3" t="n">
+        <v>1048</v>
+      </c>
+      <c r="Q352" s="3" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R352" s="3" t="n">
+        <v>37179</v>
+      </c>
+      <c r="S352" s="3" t="inlineStr">
+        <is>
+          <t>37.2s</t>
+        </is>
+      </c>
+      <c r="T352" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="U352" s="3" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V352" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="W352" s="3" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X352" s="3" t="n">
+        <v>37452</v>
+      </c>
+      <c r="Y352" s="3" t="inlineStr">
+        <is>
+          <t>37.5s</t>
+        </is>
+      </c>
+      <c r="Z352" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA352" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB352" s="3" t="inlineStr"/>
+      <c r="AC352" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD352" s="3" t="inlineStr">
+        <is>
+          <t>API call failed (token_request_error) → retried → APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>translationjob98</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:21.822</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:21.846</t>
+        </is>
+      </c>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:22.666</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:27.872</t>
+        </is>
+      </c>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:27.935</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>11:41:28.149</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="n">
+        <v>6050</v>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U353" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="W353" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X353" s="2" t="n">
+        <v>6327</v>
+      </c>
+      <c r="Y353" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z353" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB353" s="2" t="inlineStr"/>
+      <c r="AC353" s="2" t="inlineStr"/>
+      <c r="AD353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>translationjob99</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:28.581</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:28.602</t>
+        </is>
+      </c>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:29.436</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:35.865</t>
+        </is>
+      </c>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:35.918</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>11:41:36.342</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>7284</v>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U354" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V354" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="W354" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X354" s="2" t="n">
+        <v>7761</v>
+      </c>
+      <c r="Y354" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z354" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA354" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB354" s="2" t="inlineStr"/>
+      <c r="AC354" s="2" t="inlineStr"/>
+      <c r="AD354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>translationjob100</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:36.771</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:36.795</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:37.578</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:43.798</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:43.868</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>11:41:44.077</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="n">
+        <v>7027</v>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U355" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V355" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="n">
+        <v>7306</v>
+      </c>
+      <c r="Y355" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z355" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB355" s="2" t="inlineStr"/>
+      <c r="AC355" s="2" t="inlineStr"/>
+      <c r="AD355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>translationjob101</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:44.435</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:44.457</t>
+        </is>
+      </c>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:45.591</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:52.682</t>
+        </is>
+      </c>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:52.738</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>11:41:53.142</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>1134</v>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>8247</v>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U356" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V356" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="n">
+        <v>8707</v>
+      </c>
+      <c r="Y356" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="Z356" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB356" s="2" t="inlineStr"/>
+      <c r="AC356" s="2" t="inlineStr"/>
+      <c r="AD356" s="2" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>translationjob102</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>11:41:53.565</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>11:41:53.590</t>
+        </is>
+      </c>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>11:41:54.344</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>11:42:03.323</t>
+        </is>
+      </c>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>11:42:03.617</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>11:42:03.837</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>9758</v>
+      </c>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="U357" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V357" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="n">
+        <v>10272</v>
+      </c>
+      <c r="Y357" s="2" t="inlineStr">
+        <is>
+          <t>10.3s</t>
+        </is>
+      </c>
+      <c r="Z357" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA357" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB357" s="2" t="inlineStr"/>
+      <c r="AC357" s="2" t="inlineStr"/>
+      <c r="AD357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>translationjob23</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:26.485</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:26.512</t>
+        </is>
+      </c>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:26.873</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:32.876</t>
+        </is>
+      </c>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:32.954</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>18:32:33.064</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="n">
+        <v>6391</v>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U358" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V358" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="n">
+        <v>6579</v>
+      </c>
+      <c r="Y358" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z358" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA358" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB358" s="2" t="inlineStr"/>
+      <c r="AC358" s="2" t="inlineStr"/>
+      <c r="AD358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>translationjob24</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:33.331</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:33.357</t>
+        </is>
+      </c>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:33.966</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:40.798</t>
+        </is>
+      </c>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:40.868</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>18:32:40.988</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U359" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V359" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="n">
+        <v>7657</v>
+      </c>
+      <c r="Y359" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z359" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB359" s="2" t="inlineStr"/>
+      <c r="AC359" s="2" t="inlineStr"/>
+      <c r="AD359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>translationjob25</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:41.126</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:41.149</t>
+        </is>
+      </c>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:41.449</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:45.706</t>
+        </is>
+      </c>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:45.781</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>18:32:45.906</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="n">
+        <v>4580</v>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U360" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V360" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="n">
+        <v>4780</v>
+      </c>
+      <c r="Y360" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z360" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB360" s="2" t="inlineStr"/>
+      <c r="AC360" s="2" t="inlineStr"/>
+      <c r="AD360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>translationjob26</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:46.046</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:46.066</t>
+        </is>
+      </c>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:46.328</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:52.647</t>
+        </is>
+      </c>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:52.727</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>18:32:52.826</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="n">
+        <v>6601</v>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U361" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V361" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>6780</v>
+      </c>
+      <c r="Y361" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z361" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB361" s="2" t="inlineStr"/>
+      <c r="AC361" s="2" t="inlineStr"/>
+      <c r="AD361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>translationjob27</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:52.980</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:53.013</t>
+        </is>
+      </c>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:53.503</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.194</t>
+        </is>
+      </c>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.272</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.362</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V362" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="Y362" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="Z362" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB362" s="2" t="inlineStr"/>
+      <c r="AC362" s="2" t="inlineStr"/>
+      <c r="AD362" s="2" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>translationjob28</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.533</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.558</t>
+        </is>
+      </c>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>18:32:59.999</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>18:33:09.616</t>
+        </is>
+      </c>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>18:33:09.680</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>18:33:09.778</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="n">
+        <v>10083</v>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>10.1s</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U363" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V363" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>10245</v>
+      </c>
+      <c r="Y363" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="Z363" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB363" s="2" t="inlineStr"/>
+      <c r="AC363" s="2" t="inlineStr"/>
+      <c r="AD363" s="2" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>translationjob29</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:06.821</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:06.842</t>
+        </is>
+      </c>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:07.157</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.588</t>
+        </is>
+      </c>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.654</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.767</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="n">
+        <v>7767</v>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U364" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="n">
+        <v>7946</v>
+      </c>
+      <c r="Y364" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z364" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB364" s="2" t="inlineStr"/>
+      <c r="AC364" s="2" t="inlineStr"/>
+      <c r="AD364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>translationjob30</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:15.029</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:15.053</t>
+        </is>
+      </c>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:15.341</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.020</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.098</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.266</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>4991</v>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U365" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V365" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="n">
+        <v>5237</v>
+      </c>
+      <c r="Y365" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z365" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB365" s="2" t="inlineStr"/>
+      <c r="AC365" s="2" t="inlineStr"/>
+      <c r="AD365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>translationjob31</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.383</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.403</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.772</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.149</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.213</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.461</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>10766</v>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>10.8s</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U366" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V366" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>11078</v>
+      </c>
+      <c r="Y366" s="2" t="inlineStr">
+        <is>
+          <t>11.1s</t>
+        </is>
+      </c>
+      <c r="Z366" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB366" s="2" t="inlineStr"/>
+      <c r="AC366" s="2" t="inlineStr"/>
+      <c r="AD366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>translationjob32</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.614</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.634</t>
+        </is>
+      </c>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.929</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:40.448</t>
+        </is>
+      </c>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:40.518</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>19:02:40.622</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>8834</v>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U367" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V367" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="n">
+        <v>9008</v>
+      </c>
+      <c r="Y367" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="Z367" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB367" s="2" t="inlineStr"/>
+      <c r="AC367" s="2" t="inlineStr"/>
+      <c r="AD367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>translationjob33</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:40.756</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:40.778</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:41.053</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:47.671</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:47.741</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>19:02:47.847</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>6915</v>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U368" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V368" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="n">
+        <v>7091</v>
+      </c>
+      <c r="Y368" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z368" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB368" s="2" t="inlineStr"/>
+      <c r="AC368" s="2" t="inlineStr"/>
+      <c r="AD368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>translationjob34</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>19:02:47.958</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
+          <t>19:02:47.984</t>
+        </is>
+      </c>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>19:02:48.268</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr">
+        <is>
+          <t>19:03:01.733</t>
+        </is>
+      </c>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>19:03:01.806</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>19:03:01.921</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="n">
+        <v>13775</v>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="U369" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V369" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>13963</v>
+      </c>
+      <c r="Y369" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z369" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB369" s="2" t="inlineStr"/>
+      <c r="AC369" s="2" t="inlineStr"/>
+      <c r="AD369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>translationjob35</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>20:59:57.331</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>20:59:57.360</t>
+        </is>
+      </c>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>20:59:58.522</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr">
+        <is>
+          <t>21:00:08.301</t>
+        </is>
+      </c>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>21:00:08.388</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>21:00:08.745</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>1.2s</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>10970</v>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="U370" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V370" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="W370" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>11414</v>
+      </c>
+      <c r="Y370" s="2" t="inlineStr">
+        <is>
+          <t>11.4s</t>
+        </is>
+      </c>
+      <c r="Z370" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB370" s="2" t="inlineStr"/>
+      <c r="AC370" s="2" t="inlineStr"/>
+      <c r="AD370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>translationjob36</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:09.108</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:09.133</t>
+        </is>
+      </c>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:09.988</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:16.835</t>
+        </is>
+      </c>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:16.983</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>21:00:17.463</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="n">
+        <v>7727</v>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="U371" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V371" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="n">
+        <v>8355</v>
+      </c>
+      <c r="Y371" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z371" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB371" s="2" t="inlineStr"/>
+      <c r="AC371" s="2" t="inlineStr"/>
+      <c r="AD371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>translationjob37</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:17.706</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:17.738</t>
+        </is>
+      </c>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:19.011</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:31.258</t>
+        </is>
+      </c>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:31.355</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>21:00:31.717</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="n">
+        <v>13552</v>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U372" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V372" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="n">
+        <v>14011</v>
+      </c>
+      <c r="Y372" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z372" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA372" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB372" s="2" t="inlineStr"/>
+      <c r="AC372" s="2" t="inlineStr"/>
+      <c r="AD372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>translationjob38</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:32.198</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:32.223</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:33.530</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:43.339</t>
+        </is>
+      </c>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:43.439</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>21:00:43.695</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="n">
+        <v>11141</v>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>11.1s</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U373" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V373" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="n">
+        <v>11497</v>
+      </c>
+      <c r="Y373" s="2" t="inlineStr">
+        <is>
+          <t>11.5s</t>
+        </is>
+      </c>
+      <c r="Z373" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB373" s="2" t="inlineStr"/>
+      <c r="AC373" s="2" t="inlineStr"/>
+      <c r="AD373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>translationjob39</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:32.259</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:32.284</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:34.064</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:40.843</t>
+        </is>
+      </c>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:40.924</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>21:00:41.375</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="n">
+        <v>1780</v>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="n">
+        <v>8584</v>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="U374" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V374" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="n">
+        <v>9116</v>
+      </c>
+      <c r="Y374" s="2" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="Z374" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB374" s="2" t="inlineStr"/>
+      <c r="AC374" s="2" t="inlineStr"/>
+      <c r="AD374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>translationjob40</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:41.626</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:41.652</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:42.877</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:48.704</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:48.812</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>21:00:49.684</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>1.2s</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="n">
+        <v>7078</v>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="U375" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V375" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="n">
+        <v>8058</v>
+      </c>
+      <c r="Y375" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z375" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB375" s="2" t="inlineStr"/>
+      <c r="AC375" s="2" t="inlineStr"/>
+      <c r="AD375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>translationjob41</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:43.946</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:43.973</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:44.851</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:51.379</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:51.482</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>21:00:51.831</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="n">
+        <v>7433</v>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="U376" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V376" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="n">
+        <v>7885</v>
+      </c>
+      <c r="Y376" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z376" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB376" s="2" t="inlineStr"/>
+      <c r="AC376" s="2" t="inlineStr"/>
+      <c r="AD376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>translationjob42</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>21:00:49.962</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>21:00:49.994</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>21:00:51.955</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>21:01:00.133</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>21:01:00.455</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>21:01:04.812</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>10171</v>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="U377" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>4357</v>
+      </c>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>14850</v>
+      </c>
+      <c r="Y377" s="2" t="inlineStr">
+        <is>
+          <t>14.8s</t>
+        </is>
+      </c>
+      <c r="Z377" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA377" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB377" s="2" t="inlineStr"/>
+      <c r="AC377" s="2" t="inlineStr"/>
+      <c r="AD377" s="2" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>21:00:52.360</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>21:00:52.388</t>
+        </is>
+      </c>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>21:00:53.685</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>21:01:05.867</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>21:01:06.185</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>21:01:06.946</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>1297</v>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>13507</v>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>13.5s</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="U378" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V378" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="W378" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>14586</v>
+      </c>
+      <c r="Y378" s="2" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+      <c r="Z378" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB378" s="2" t="inlineStr"/>
+      <c r="AC378" s="2" t="inlineStr"/>
+      <c r="AD378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:05.148</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:05.176</t>
+        </is>
+      </c>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:07.041</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:13.709</t>
+        </is>
+      </c>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:13.815</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>21:01:14.365</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>8561</v>
+      </c>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="U379" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V379" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="n">
+        <v>9217</v>
+      </c>
+      <c r="Y379" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z379" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA379" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB379" s="2" t="inlineStr"/>
+      <c r="AC379" s="2" t="inlineStr"/>
+      <c r="AD379" s="2" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:14.671</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:14.701</t>
+        </is>
+      </c>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:16.094</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:23.765</t>
+        </is>
+      </c>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:24.042</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>21:01:24.585</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="n">
+        <v>1393</v>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>9094</v>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="U380" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="W380" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>9914</v>
+      </c>
+      <c r="Y380" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="Z380" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB380" s="2" t="inlineStr"/>
+      <c r="AC380" s="2" t="inlineStr"/>
+      <c r="AD380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:24.788</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:24.818</t>
+        </is>
+      </c>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:26.127</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:33.530</t>
+        </is>
+      </c>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:33.595</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>21:01:33.970</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>8742</v>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U381" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="W381" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>9182</v>
+      </c>
+      <c r="Y381" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z381" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB381" s="2" t="inlineStr"/>
+      <c r="AC381" s="2" t="inlineStr"/>
+      <c r="AD381" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD344"/>
+  <autoFilter ref="A1:AD381"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43884,7 +48559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -43900,214 +48575,254 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Stuck</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Retried</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Avg Duration</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Min Duration</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Max Duration</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>16.0s</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>1.6s</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>2m 29.9s</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>10.6s</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>1.9s</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>1m 40.2s</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>9.8s</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>1.9s</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>35.3s</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>12.1s</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>2.7s</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>2m 29.6s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>25.7s</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>2m 32.8s</t>
         </is>
       </c>
     </row>
@@ -44122,7 +48837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -44130,272 +48845,315 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Error Category</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Language copy not found</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>233312</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>268729</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>60159</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>253573</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>253314</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Content LC unknown state</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TranslationCleanupJobConsumer</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>540</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ThumbnailServlet</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>69</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TicketAssemblyTranslationServiceImpl</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>36</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ReplicationSquadListener</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>166502</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>174817</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>139752</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>173166</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>172505</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ResourceUtils commit</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>19640</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>21848</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>13502</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>20714</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>20964</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>LockUtil contention</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>1575</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>1523</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>1782</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>2013</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1462</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TranslateHrefAttributes</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>778</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>1054</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>1282</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>626</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Error executing workflow</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>742</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>932</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>287</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>812</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>810</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Error processing Translation project</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>GCCScriptProcessor</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>10</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>ReplicationNewsAssemblyListener</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>55349</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="6" t="n">
         <v>92531</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>69944</v>
       </c>
     </row>
   </sheetData>
@@ -44409,7 +49167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -44422,139 +49180,164 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Total Entries</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Obtained</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Expires</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Token Size Entries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>252</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>648</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>777</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>882</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>635</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD129"/>
+  <dimension ref="A1:AD175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16685,8 +16685,5804 @@
       <c r="AC129" s="2" t="inlineStr"/>
       <c r="AD129" s="2" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>translationjob41</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:32.240</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:32.260</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:32.803</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:45.495</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:45.546</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>08:25:45.633</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>13255</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="n">
+        <v>13393</v>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>translationjob42</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:45.863</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:45.885</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:46.125</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.110</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.164</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.238</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>5247</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="n">
+        <v>5375</v>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>translationjob43</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.447</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.468</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:51.710</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:56.877</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:56.926</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>08:25:57.008</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>5430</v>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="n">
+        <v>5561</v>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>translationjob44</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>08:25:57.159</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>08:25:57.175</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>08:25:57.407</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>08:26:01.855</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>08:26:01.903</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>08:26:02.040</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>4696</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>4881</v>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>translationjob45</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:02.201</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:02.221</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:02.558</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.291</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.334</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.419</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>4090</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="n">
+        <v>4218</v>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="Z134" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>translationjob46</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.564</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.578</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:06.818</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:16.146</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:16.202</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>08:26:16.283</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>9582</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="n">
+        <v>9719</v>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:08.273</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:08.293</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:08.609</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:15.807</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:15.855</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>09:51:15.939</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>7534</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="n">
+        <v>7666</v>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:16.032</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:16.054</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:16.404</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.129</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.179</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.353</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>7097</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="n">
+        <v>7321</v>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.525</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.542</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:23.795</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.259</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.303</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.396</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>8734</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="n">
+        <v>8871</v>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.515</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.532</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:32.762</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.093</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.144</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.243</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>14578</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="n">
+        <v>14728</v>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>14.7s</t>
+        </is>
+      </c>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.356</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.376</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:47.656</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:59.791</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:59.842</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>09:51:59.927</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>12435</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>12.4s</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="n">
+        <v>12571</v>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>translationjob0</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:00.019</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:00.041</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:00.677</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:10.435</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:10.665</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>11:16:10.851</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>636</v>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>10416</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="n">
+        <v>10832</v>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>10.8s</t>
+        </is>
+      </c>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:10.965</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:10.984</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:11.899</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:19.127</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:19.180</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>11:16:19.377</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>8162</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>8412</v>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:19.574</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:19.601</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:20.336</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:28.100</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:28.222</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>11:16:28.422</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>8526</v>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="n">
+        <v>8848</v>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>translationjob3</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:28.593</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:28.617</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:29.395</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:35.155</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:35.226</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>11:16:35.432</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>6562</v>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>6839</v>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z144" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>translationjob4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:35.734</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:35.772</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:36.732</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:44.141</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:44.203</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>11:16:44.439</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>8407</v>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="n">
+        <v>8705</v>
+      </c>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="Z145" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>translationjob48</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:15.734</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:15.752</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:16.027</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:23.775</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:23.828</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>14:19:23.901</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>8041</v>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>8167</v>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z146" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>translationjob49</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:24.047</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:24.063</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:24.230</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.301</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.342</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.433</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>5254</v>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="n">
+        <v>5386</v>
+      </c>
+      <c r="Y147" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z147" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>translationjob50</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.569</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.584</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:29.891</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.122</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.172</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.243</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>9553</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>9674</v>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>translationjob51</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.374</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.390</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:39.566</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:47.644</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:47.695</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>14:19:47.771</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>8270</v>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="n">
+        <v>8397</v>
+      </c>
+      <c r="Y149" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z149" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>translationjob52</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:47.917</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:47.932</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:48.139</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:54.472</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:54.530</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>14:19:54.631</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>6555</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>6714</v>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="Z150" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>translationjob53</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>14:19:54.810</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>14:19:54.830</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>14:19:55.061</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>14:20:05.959</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>14:20:06.016</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>14:20:06.110</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>11149</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>11.1s</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="n">
+        <v>11300</v>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>11.3s</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:43.714</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:43.741</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:44.633</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:57.502</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:57.741</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>15:35:57.957</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>13788</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>14243</v>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>14.2s</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>15:35:58.068</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>15:35:58.088</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>15:35:58.757</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>15:36:18.445</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>15:36:18.504</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>15:36:18.722</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>20377</v>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>20.4s</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>20654</v>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>20.7s</t>
+        </is>
+      </c>
+      <c r="Z153" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:18.894</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:18.918</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:19.679</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:44.512</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:44.583</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>15:36:44.814</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>25618</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>25.6s</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>25920</v>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>25.9s</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:45.452</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:45.471</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:46.363</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:58.446</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:58.499</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>15:36:58.683</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>12994</v>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>13.0s</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="n">
+        <v>13231</v>
+      </c>
+      <c r="Y155" s="2" t="inlineStr">
+        <is>
+          <t>13.2s</t>
+        </is>
+      </c>
+      <c r="Z155" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>15:36:58.879</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>15:36:58.898</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>15:36:59.798</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>15:37:09.452</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>15:37:09.540</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>15:37:09.806</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="n">
+        <v>10573</v>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="n">
+        <v>10927</v>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>10.9s</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:10.106</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:10.129</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:10.667</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:32.165</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:32.232</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>15:37:32.464</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="n">
+        <v>22059</v>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>22.1s</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="n">
+        <v>22358</v>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>22.4s</t>
+        </is>
+      </c>
+      <c r="Z157" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>translationjob81</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>19:01:59.120</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>19:01:59.135</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>19:01:59.312</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>19:02:08.805</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>19:02:08.839</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>19:02:08.900</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="n">
+        <v>9685</v>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="n">
+        <v>9780</v>
+      </c>
+      <c r="Y158" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>translationjob82</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:09.052</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:09.064</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:09.208</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.584</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.651</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.721</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="n">
+        <v>5532</v>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="n">
+        <v>5669</v>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>translationjob83</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.959</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:14.972</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:15.118</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.233</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.265</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.330</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>5274</v>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="n">
+        <v>5371</v>
+      </c>
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z160" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>translationjob84</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.446</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.457</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:20.651</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.382</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.412</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.467</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>5936</v>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="n">
+        <v>6021</v>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>translationjob85</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.594</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.607</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:26.759</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.353</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.384</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.436</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>4759</v>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="n">
+        <v>4842</v>
+      </c>
+      <c r="Y162" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z162" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>translationjob86</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.559</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.569</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:31.719</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:38.599</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:38.633</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>19:02:38.685</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>7040</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z163" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>translationjob87</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:10.635</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:10.653</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:11.035</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:15.508</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:15.560</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>21:50:15.647</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>4873</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="n">
+        <v>5012</v>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>translationjob88</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:15.860</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:15.880</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:16.149</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:19.717</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:19.763</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>21:50:19.904</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>3857</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>4044</v>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>translationjob89</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:20.108</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:20.126</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:20.503</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:24.987</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:25.042</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>21:50:25.127</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>4879</v>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="n">
+        <v>5019</v>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>translationjob90</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:25.340</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:25.358</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:25.622</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:29.848</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:30.832</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>21:50:30.996</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>4508</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>984</v>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="n">
+        <v>5656</v>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>translationjob91</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:30.995</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:31.017</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:31.661</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.247</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.326</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.588</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="n">
+        <v>6252</v>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>6593</v>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>translationjob92</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:31.374</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:31.401</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:31.741</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:36.647</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:36.699</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>21:50:36.809</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>5273</v>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>5435</v>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>translationjob93</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.036</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.054</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.346</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:42.598</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:42.647</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>21:50:42.727</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>5562</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="n">
+        <v>5691</v>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>translationjob94</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.787</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:37.807</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:38.423</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:43.547</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:43.598</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>21:50:43.792</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>5760</v>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="n">
+        <v>6005</v>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>translationjob95</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:43.996</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:44.015</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:44.984</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:49.749</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:49.856</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>21:50:51.308</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="n">
+        <v>969</v>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="n">
+        <v>5753</v>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z172" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>translationjob96</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>21:50:51.540</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>21:50:51.560</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>21:50:52.190</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>21:51:00.305</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>21:51:00.344</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>21:51:00.652</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>8765</v>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="n">
+        <v>9112</v>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>translationjob97</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:00.839</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:00.858</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:01.336</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:14.849</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:14.891</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>21:51:15.192</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>478</v>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>14010</v>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="n">
+        <v>14353</v>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>14.4s</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>translationjob98</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:15.385</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:15.405</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:16.148</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:25.600</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:25.817</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>21:51:25.975</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>743</v>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>10215</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="n">
+        <v>10590</v>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD129"/>
+  <autoFilter ref="A1:AD175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16697,7 +22493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16844,6 +22640,46 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25.9s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16855,12 +22691,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16879,6 +22716,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -16892,6 +22734,9 @@
       <c r="C2" s="6" t="n">
         <v>78904</v>
       </c>
+      <c r="D2" s="6" t="n">
+        <v>24586</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -16903,6 +22748,7 @@
         <v>636</v>
       </c>
       <c r="C3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -16916,6 +22762,9 @@
       <c r="C4" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="D4" s="6" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -16929,6 +22778,7 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -16942,6 +22792,7 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -16955,6 +22806,9 @@
       <c r="C7" s="6" t="n">
         <v>139911</v>
       </c>
+      <c r="D7" s="6" t="n">
+        <v>135602</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -16968,6 +22822,9 @@
       <c r="C8" s="6" t="n">
         <v>85748</v>
       </c>
+      <c r="D8" s="6" t="n">
+        <v>21928</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -16981,6 +22838,9 @@
       <c r="C9" s="6" t="n">
         <v>12330</v>
       </c>
+      <c r="D9" s="6" t="n">
+        <v>12256</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -16994,6 +22854,9 @@
       <c r="C10" s="6" t="n">
         <v>1856</v>
       </c>
+      <c r="D10" s="6" t="n">
+        <v>1648</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -17007,6 +22870,9 @@
       <c r="C11" s="6" t="n">
         <v>768</v>
       </c>
+      <c r="D11" s="6" t="n">
+        <v>1128</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -17020,6 +22886,9 @@
       <c r="C12" s="6" t="n">
         <v>162</v>
       </c>
+      <c r="D12" s="6" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -17031,6 +22900,9 @@
       <c r="C13" s="5" t="n">
         <v>89</v>
       </c>
+      <c r="D13" s="5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -17040,6 +22912,9 @@
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17054,7 +22929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17153,6 +23028,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>693</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
         <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFFAFE"/>
+        <bgColor rgb="00CFFAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,16 +105,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD175"/>
+  <dimension ref="A1:AD245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22481,8 +22488,8840 @@
       <c r="AC175" s="2" t="inlineStr"/>
       <c r="AD175" s="2" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:03.938</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:03.956</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:04.190</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.227</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.309</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.396</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>5289</v>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="n">
+        <v>5458</v>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.514</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.531</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:09.834</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:13.942</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:13.986</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>07:32:14.070</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>4428</v>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="n">
+        <v>4556</v>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:14.157</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:14.172</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:14.447</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:21.885</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:21.924</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>07:32:21.998</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>7728</v>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="n">
+        <v>7841</v>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:22.101</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:22.115</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:22.323</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.302</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.346</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.437</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="n">
+        <v>6336</v>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.534</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.554</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:28.758</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.313</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.360</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.443</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>4779</v>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="n">
+        <v>4909</v>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.626</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.641</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:33.845</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:41.328</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:41.375</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>07:32:41.463</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>7702</v>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="n">
+        <v>7837</v>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:15.156</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:15.180</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:15.833</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:28.548</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:28.611</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>09:36:28.896</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>13392</v>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>13.4s</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="n">
+        <v>13740</v>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>13.7s</t>
+        </is>
+      </c>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:29.000</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:29.021</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:29.475</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:35.165</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:35.217</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>09:36:35.408</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>6165</v>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="n">
+        <v>6408</v>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:35.524</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:35.542</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:36.029</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:44.190</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:44.250</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>09:36:44.425</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>8666</v>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="n">
+        <v>8901</v>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB184" s="2" t="inlineStr"/>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:44.543</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:44.559</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:45.212</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:51.975</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:52.020</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>09:36:52.191</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>7432</v>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V185" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="n">
+        <v>7648</v>
+      </c>
+      <c r="Y185" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z185" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:52.330</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:52.352</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:52.826</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:59.545</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:59.607</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>09:36:59.786</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="n">
+        <v>7456</v>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="Z186" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB186" s="2" t="inlineStr"/>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:00.083</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:00.103</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:00.589</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:08.698</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:08.749</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>09:37:08.984</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>8615</v>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U187" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V187" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="W187" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X187" s="2" t="n">
+        <v>8901</v>
+      </c>
+      <c r="Y187" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z187" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB187" s="2" t="inlineStr"/>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>translationjob5</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:24.655</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:24.678</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:24.900</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:49.881</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:49.933</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>09:48:50.019</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>25226</v>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>25.2s</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V188" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W188" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X188" s="2" t="n">
+        <v>25364</v>
+      </c>
+      <c r="Y188" s="2" t="inlineStr">
+        <is>
+          <t>25.4s</t>
+        </is>
+      </c>
+      <c r="Z188" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB188" s="2" t="inlineStr"/>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>translationjob6</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>09:48:50.128</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>09:48:50.150</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>09:48:50.474</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.237</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.295</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.385</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="n">
+        <v>17109</v>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>17.1s</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V189" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="W189" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X189" s="2" t="n">
+        <v>17257</v>
+      </c>
+      <c r="Y189" s="2" t="inlineStr">
+        <is>
+          <t>17.3s</t>
+        </is>
+      </c>
+      <c r="Z189" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>translationjob7</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.446</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.465</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:07.748</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:25.579</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:25.636</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>09:49:25.716</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>18133</v>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>18.1s</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W190" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X190" s="2" t="n">
+        <v>18270</v>
+      </c>
+      <c r="Y190" s="2" t="inlineStr">
+        <is>
+          <t>18.3s</t>
+        </is>
+      </c>
+      <c r="Z190" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>translationjob8</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:25.818</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:25.837</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:26.156</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:45.580</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:45.639</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>09:49:45.737</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>19762</v>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>19.8s</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="n">
+        <v>19919</v>
+      </c>
+      <c r="Y191" s="2" t="inlineStr">
+        <is>
+          <t>19.9s</t>
+        </is>
+      </c>
+      <c r="Z191" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB191" s="2" t="inlineStr"/>
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>translationjob9</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:45.843</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:45.861</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:46.212</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.402</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.450</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.530</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>12559</v>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="n">
+        <v>12687</v>
+      </c>
+      <c r="Y192" s="2" t="inlineStr">
+        <is>
+          <t>12.7s</t>
+        </is>
+      </c>
+      <c r="Z192" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>translationjob10</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.603</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.625</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>09:49:58.825</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>09:50:15.930</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>09:50:15.981</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>09:50:16.064</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>17327</v>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>17.3s</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U193" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V193" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="n">
+        <v>17461</v>
+      </c>
+      <c r="Y193" s="2" t="inlineStr">
+        <is>
+          <t>17.5s</t>
+        </is>
+      </c>
+      <c r="Z193" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>translationjob17</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.263</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.277</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:46.480</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.210</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.250</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.316</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>5947</v>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V194" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="n">
+        <v>6053</v>
+      </c>
+      <c r="Y194" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z194" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>translationjob18</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.402</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.420</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:52.600</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.240</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.282</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.344</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>5838</v>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V195" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="n">
+        <v>5942</v>
+      </c>
+      <c r="Y195" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z195" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>translationjob19</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.422</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.436</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>10:33:58.593</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.162</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.199</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.254</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>5740</v>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V196" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="n">
+        <v>5832</v>
+      </c>
+      <c r="Y196" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z196" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>translationjob20</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.356</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.371</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:04.520</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.413</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.452</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.523</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>8057</v>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V197" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="n">
+        <v>8167</v>
+      </c>
+      <c r="Y197" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z197" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>translationjob21</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.599</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.613</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:12.779</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:18.588</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:18.629</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>10:34:18.704</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="n">
+        <v>5989</v>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V198" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="n">
+        <v>6105</v>
+      </c>
+      <c r="Y198" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z198" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>translationjob22</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:18.805</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:18.820</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:19.080</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:28.396</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:28.439</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>10:34:28.489</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="n">
+        <v>9591</v>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V199" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="n">
+        <v>9684</v>
+      </c>
+      <c r="Y199" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="Z199" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>translationjob11</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>13:57:42.816</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>13:57:42.835</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>13:57:43.133</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>13:58:00.077</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>13:58:00.120</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>13:58:00.187</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="n">
+        <v>17261</v>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>17.3s</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V200" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W200" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X200" s="2" t="n">
+        <v>17371</v>
+      </c>
+      <c r="Y200" s="2" t="inlineStr">
+        <is>
+          <t>17.4s</t>
+        </is>
+      </c>
+      <c r="Z200" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB200" s="2" t="inlineStr"/>
+      <c r="AC200" s="2" t="inlineStr"/>
+      <c r="AD200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>translationjob12</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:00.291</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:00.306</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:00.507</t>
+        </is>
+      </c>
+      <c r="M201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:49.905</t>
+        </is>
+      </c>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:49.943</t>
+        </is>
+      </c>
+      <c r="O201" s="4" t="inlineStr">
+        <is>
+          <t>13:58:50.001</t>
+        </is>
+      </c>
+      <c r="P201" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q201" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R201" s="4" t="n">
+        <v>49614</v>
+      </c>
+      <c r="S201" s="4" t="inlineStr">
+        <is>
+          <t>49.6s</t>
+        </is>
+      </c>
+      <c r="T201" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U201" s="4" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V201" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="W201" s="4" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X201" s="4" t="n">
+        <v>49710</v>
+      </c>
+      <c r="Y201" s="4" t="inlineStr">
+        <is>
+          <t>49.7s</t>
+        </is>
+      </c>
+      <c r="Z201" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB201" s="4" t="inlineStr"/>
+      <c r="AC201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD201" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (api_payload_dump) → retried → APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>translationjob13</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>13:58:50.073</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>13:58:50.086</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>13:58:50.290</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>13:59:13.679</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>13:59:13.718</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>13:59:13.773</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="n">
+        <v>23606</v>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>23.6s</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V202" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X202" s="2" t="n">
+        <v>23700</v>
+      </c>
+      <c r="Y202" s="2" t="inlineStr">
+        <is>
+          <t>23.7s</t>
+        </is>
+      </c>
+      <c r="Z202" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB202" s="2" t="inlineStr"/>
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>translationjob14</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:13.875</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:13.889</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:14.063</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.266</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.308</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.368</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="n">
+        <v>20391</v>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>20.4s</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U203" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V203" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="n">
+        <v>20493</v>
+      </c>
+      <c r="Y203" s="2" t="inlineStr">
+        <is>
+          <t>20.5s</t>
+        </is>
+      </c>
+      <c r="Z203" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>translationjob15</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.449</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.463</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:34.627</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:51.445</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:51.485</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>13:59:51.534</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="n">
+        <v>16996</v>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>17.0s</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V204" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="n">
+        <v>17085</v>
+      </c>
+      <c r="Y204" s="2" t="inlineStr">
+        <is>
+          <t>17.1s</t>
+        </is>
+      </c>
+      <c r="Z204" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>translationjob16</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>13:59:51.601</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>13:59:51.614</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>13:59:51.824</t>
+        </is>
+      </c>
+      <c r="M205" s="4" t="inlineStr">
+        <is>
+          <t>14:00:43.947</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>14:00:44.011</t>
+        </is>
+      </c>
+      <c r="O205" s="4" t="inlineStr">
+        <is>
+          <t>14:00:44.087</t>
+        </is>
+      </c>
+      <c r="P205" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q205" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R205" s="4" t="n">
+        <v>52346</v>
+      </c>
+      <c r="S205" s="4" t="inlineStr">
+        <is>
+          <t>52.3s</t>
+        </is>
+      </c>
+      <c r="T205" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U205" s="4" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V205" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="W205" s="4" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X205" s="4" t="n">
+        <v>52486</v>
+      </c>
+      <c r="Y205" s="4" t="inlineStr">
+        <is>
+          <t>52.5s</t>
+        </is>
+      </c>
+      <c r="Z205" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA205" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB205" s="4" t="inlineStr"/>
+      <c r="AC205" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" s="4" t="inlineStr">
+        <is>
+          <t>API call failed (api_payload_dump) → retried → APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>translationjob54</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:44.637</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:44.652</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:44.829</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.574</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.609</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.663</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="n">
+        <v>9937</v>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>9.9s</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V206" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="n">
+        <v>10026</v>
+      </c>
+      <c r="Y206" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="Z206" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>translationjob55</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.730</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.743</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>16:44:54.897</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.037</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.071</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.133</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="n">
+        <v>7307</v>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V207" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="n">
+        <v>7403</v>
+      </c>
+      <c r="Y207" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z207" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>translationjob56</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.204</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.216</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:02.417</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:16.904</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:16.939</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>16:45:16.986</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="n">
+        <v>14700</v>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>14.7s</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V208" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X208" s="2" t="n">
+        <v>14782</v>
+      </c>
+      <c r="Y208" s="2" t="inlineStr">
+        <is>
+          <t>14.8s</t>
+        </is>
+      </c>
+      <c r="Z208" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA208" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>translationjob57</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:17.130</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:17.143</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:17.299</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.241</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.269</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.325</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="n">
+        <v>13111</v>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>13.1s</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V209" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="n">
+        <v>13195</v>
+      </c>
+      <c r="Y209" s="2" t="inlineStr">
+        <is>
+          <t>13.2s</t>
+        </is>
+      </c>
+      <c r="Z209" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>translationjob58</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.445</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.457</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:30.660</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:39.720</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:39.767</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>16:45:39.818</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="n">
+        <v>9275</v>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V210" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="n">
+        <v>9373</v>
+      </c>
+      <c r="Y210" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="Z210" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA210" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB210" s="2" t="inlineStr"/>
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>translationjob59</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:39.949</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:39.961</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:40.147</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:55.774</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:55.816</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>16:45:55.887</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="n">
+        <v>15825</v>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>15.8s</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U211" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V211" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W211" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X211" s="2" t="n">
+        <v>15938</v>
+      </c>
+      <c r="Y211" s="2" t="inlineStr">
+        <is>
+          <t>15.9s</t>
+        </is>
+      </c>
+      <c r="Z211" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA211" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB211" s="2" t="inlineStr"/>
+      <c r="AC211" s="2" t="inlineStr"/>
+      <c r="AD211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>translationjob60</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:03.714</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:03.726</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:03.911</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:13.963</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:14.004</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>16:53:14.068</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="n">
+        <v>10249</v>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U212" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V212" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="W212" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X212" s="2" t="n">
+        <v>10354</v>
+      </c>
+      <c r="Y212" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="Z212" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB212" s="2" t="inlineStr"/>
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>translationjob62</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:14.278</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:14.292</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:14.480</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:22.556</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:22.591</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>16:53:22.646</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="n">
+        <v>8278</v>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V213" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W213" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X213" s="2" t="n">
+        <v>8368</v>
+      </c>
+      <c r="Y213" s="2" t="inlineStr">
+        <is>
+          <t>8.4s</t>
+        </is>
+      </c>
+      <c r="Z213" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA213" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB213" s="2" t="inlineStr"/>
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>translationjob64</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:22.769</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:22.790</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:23.008</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:38.698</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:38.730</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>16:53:38.790</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="n">
+        <v>15929</v>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>15.9s</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V214" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="n">
+        <v>16021</v>
+      </c>
+      <c r="Y214" s="2" t="inlineStr">
+        <is>
+          <t>16.0s</t>
+        </is>
+      </c>
+      <c r="Z214" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA214" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB214" s="2" t="inlineStr"/>
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>translationjob66</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:38.921</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:38.933</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:39.085</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:54.533</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:54.563</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>16:53:54.611</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="n">
+        <v>15612</v>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>15.6s</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V215" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="n">
+        <v>15690</v>
+      </c>
+      <c r="Y215" s="2" t="inlineStr">
+        <is>
+          <t>15.7s</t>
+        </is>
+      </c>
+      <c r="Z215" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA215" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB215" s="2" t="inlineStr"/>
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>translationjob67</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>16:53:54.826</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>16:53:54.841</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>16:53:55.044</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>16:54:07.940</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>16:54:08.039</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>16:54:08.114</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="n">
+        <v>13114</v>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>13.1s</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V216" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="n">
+        <v>13288</v>
+      </c>
+      <c r="Y216" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="Z216" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA216" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB216" s="2" t="inlineStr"/>
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>translationjob69</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:08.263</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:08.276</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:08.431</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:25.825</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:25.860</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>16:54:25.913</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>17562</v>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>17.6s</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V217" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W217" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X217" s="2" t="n">
+        <v>17650</v>
+      </c>
+      <c r="Y217" s="2" t="inlineStr">
+        <is>
+          <t>17.6s</t>
+        </is>
+      </c>
+      <c r="Z217" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB217" s="2" t="inlineStr"/>
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>translationjob70</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:09.197</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:09.213</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:12.189</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:28.976</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:29.026</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>17:28:29.657</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="n">
+        <v>2976</v>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="n">
+        <v>19779</v>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>19.8s</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U218" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V218" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="W218" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X218" s="2" t="n">
+        <v>20460</v>
+      </c>
+      <c r="Y218" s="2" t="inlineStr">
+        <is>
+          <t>20.5s</t>
+        </is>
+      </c>
+      <c r="Z218" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA218" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB218" s="2" t="inlineStr"/>
+      <c r="AC218" s="2" t="inlineStr"/>
+      <c r="AD218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>translationjob71</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:30.068</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:30.082</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:32.530</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:42.692</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:42.789</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>17:28:43.642</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="n">
+        <v>2448</v>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="n">
+        <v>12624</v>
+      </c>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U219" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V219" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="W219" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="X219" s="2" t="n">
+        <v>13574</v>
+      </c>
+      <c r="Y219" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="Z219" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB219" s="2" t="inlineStr"/>
+      <c r="AC219" s="2" t="inlineStr"/>
+      <c r="AD219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>translationjob72</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:44.815</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:44.832</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:48.538</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:58.410</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:58.607</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>17:28:59.411</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="n">
+        <v>3706</v>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="n">
+        <v>13595</v>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="U220" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V220" s="2" t="n">
+        <v>804</v>
+      </c>
+      <c r="W220" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="X220" s="2" t="n">
+        <v>14596</v>
+      </c>
+      <c r="Y220" s="2" t="inlineStr">
+        <is>
+          <t>14.6s</t>
+        </is>
+      </c>
+      <c r="Z220" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB220" s="2" t="inlineStr"/>
+      <c r="AC220" s="2" t="inlineStr"/>
+      <c r="AD220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>translationjob74</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:00.385</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:00.402</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:04.185</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:20.551</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:20.614</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>17:29:21.346</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="n">
+        <v>3783</v>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="n">
+        <v>20166</v>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>20.2s</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U221" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V221" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="W221" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="X221" s="2" t="n">
+        <v>20961</v>
+      </c>
+      <c r="Y221" s="2" t="inlineStr">
+        <is>
+          <t>21.0s</t>
+        </is>
+      </c>
+      <c r="Z221" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB221" s="2" t="inlineStr"/>
+      <c r="AC221" s="2" t="inlineStr"/>
+      <c r="AD221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>translationjob75</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:22.342</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:22.363</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:26.249</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:43.045</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:43.110</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>17:29:43.879</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="n">
+        <v>3886</v>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="n">
+        <v>20703</v>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>20.7s</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U222" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V222" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="W222" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="X222" s="2" t="n">
+        <v>21537</v>
+      </c>
+      <c r="Y222" s="2" t="inlineStr">
+        <is>
+          <t>21.5s</t>
+        </is>
+      </c>
+      <c r="Z222" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB222" s="2" t="inlineStr"/>
+      <c r="AC222" s="2" t="inlineStr"/>
+      <c r="AD222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>translationjob76</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>17:29:44.956</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>17:29:44.975</t>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>17:29:48.936</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>17:30:07.059</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>17:30:07.130</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>17:30:08.149</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="n">
+        <v>3961</v>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>4.0s</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="n">
+        <v>22103</v>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>22.1s</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U223" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V223" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="n">
+        <v>23193</v>
+      </c>
+      <c r="Y223" s="2" t="inlineStr">
+        <is>
+          <t>23.2s</t>
+        </is>
+      </c>
+      <c r="Z223" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB223" s="2" t="inlineStr"/>
+      <c r="AC223" s="2" t="inlineStr"/>
+      <c r="AD223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>translationjob77</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>18:57:54.231</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>18:57:54.250</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>18:57:55.120</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>18:58:01.628</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>18:58:01.674</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>18:58:01.964</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="n">
+        <v>7397</v>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U224" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V224" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="n">
+        <v>7733</v>
+      </c>
+      <c r="Y224" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB224" s="2" t="inlineStr"/>
+      <c r="AC224" s="2" t="inlineStr"/>
+      <c r="AD224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>translationjob78</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:02.135</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:02.148</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:02.936</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:07.418</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:07.449</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>18:58:07.655</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="n">
+        <v>5283</v>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U225" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V225" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="W225" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X225" s="2" t="n">
+        <v>5520</v>
+      </c>
+      <c r="Y225" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z225" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB225" s="2" t="inlineStr"/>
+      <c r="AC225" s="2" t="inlineStr"/>
+      <c r="AD225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>translationjob80</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:07.845</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:07.874</t>
+        </is>
+      </c>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:08.429</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:14.273</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:14.313</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>18:58:14.491</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="n">
+        <v>6428</v>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U226" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V226" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W226" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X226" s="2" t="n">
+        <v>6646</v>
+      </c>
+      <c r="Y226" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z226" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA226" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB226" s="2" t="inlineStr"/>
+      <c r="AC226" s="2" t="inlineStr"/>
+      <c r="AD226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>translationjob82</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:14.752</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:14.767</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:15.301</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:20.353</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:20.385</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>18:58:20.604</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="n">
+        <v>5601</v>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U227" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V227" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="W227" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X227" s="2" t="n">
+        <v>5852</v>
+      </c>
+      <c r="Y227" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z227" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA227" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB227" s="2" t="inlineStr"/>
+      <c r="AC227" s="2" t="inlineStr"/>
+      <c r="AD227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>translationjob84</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:20.829</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:20.845</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:21.443</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:27.350</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:27.385</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>18:58:27.558</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="n">
+        <v>598</v>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="n">
+        <v>6521</v>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U228" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V228" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="W228" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X228" s="2" t="n">
+        <v>6729</v>
+      </c>
+      <c r="Y228" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="Z228" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA228" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB228" s="2" t="inlineStr"/>
+      <c r="AC228" s="2" t="inlineStr"/>
+      <c r="AD228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>translationjob85</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:27.839</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:27.851</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:28.301</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:35.133</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:35.166</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>18:58:35.390</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="n">
+        <v>7294</v>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U229" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V229" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="n">
+        <v>7551</v>
+      </c>
+      <c r="Y229" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z229" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB229" s="2" t="inlineStr"/>
+      <c r="AC229" s="2" t="inlineStr"/>
+      <c r="AD229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>translationjob86</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:01.580</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:01.594</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:02.286</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:10.992</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:11.033</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>21:55:11.274</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="n">
+        <v>692</v>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="n">
+        <v>9412</v>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U230" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V230" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="W230" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X230" s="2" t="n">
+        <v>9694</v>
+      </c>
+      <c r="Y230" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="Z230" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB230" s="2" t="inlineStr"/>
+      <c r="AC230" s="2" t="inlineStr"/>
+      <c r="AD230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>translationjob87</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:11.449</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:11.465</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:12.070</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:24.550</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:24.595</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>21:55:24.791</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="n">
+        <v>13101</v>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>13.1s</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U231" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V231" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="W231" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X231" s="2" t="n">
+        <v>13342</v>
+      </c>
+      <c r="Y231" s="2" t="inlineStr">
+        <is>
+          <t>13.3s</t>
+        </is>
+      </c>
+      <c r="Z231" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB231" s="2" t="inlineStr"/>
+      <c r="AC231" s="2" t="inlineStr"/>
+      <c r="AD231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>translationjob88</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:20.520</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:20.535</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:21.215</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:27.135</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:27.182</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>21:55:27.400</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="n">
+        <v>6615</v>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U232" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V232" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="W232" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X232" s="2" t="n">
+        <v>6880</v>
+      </c>
+      <c r="Y232" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="Z232" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB232" s="2" t="inlineStr"/>
+      <c r="AC232" s="2" t="inlineStr"/>
+      <c r="AD232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>translationjob89</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:25.013</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:25.032</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:26.405</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:34.287</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:34.432</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>21:55:36.537</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>1.4s</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="n">
+        <v>9274</v>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="U233" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V233" s="2" t="n">
+        <v>2105</v>
+      </c>
+      <c r="W233" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="X233" s="2" t="n">
+        <v>11524</v>
+      </c>
+      <c r="Y233" s="2" t="inlineStr">
+        <is>
+          <t>11.5s</t>
+        </is>
+      </c>
+      <c r="Z233" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA233" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB233" s="2" t="inlineStr"/>
+      <c r="AC233" s="2" t="inlineStr"/>
+      <c r="AD233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>translationjob90</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:27.583</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:27.598</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:28.292</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:33.624</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:33.665</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>21:55:34.064</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="n">
+        <v>6041</v>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U234" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V234" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="W234" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X234" s="2" t="n">
+        <v>6481</v>
+      </c>
+      <c r="Y234" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z234" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA234" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB234" s="2" t="inlineStr"/>
+      <c r="AC234" s="2" t="inlineStr"/>
+      <c r="AD234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>translationjob92</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:34.267</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:34.282</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:36.377</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:42.938</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:43.057</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.686</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="n">
+        <v>2095</v>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="n">
+        <v>8671</v>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="U235" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V235" s="2" t="n">
+        <v>1629</v>
+      </c>
+      <c r="W235" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="X235" s="2" t="n">
+        <v>10419</v>
+      </c>
+      <c r="Y235" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="Z235" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA235" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB235" s="2" t="inlineStr"/>
+      <c r="AC235" s="2" t="inlineStr"/>
+      <c r="AD235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>translationjob93</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:36.774</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:36.795</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:37.385</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.174</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.541</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.849</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="n">
+        <v>590</v>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="n">
+        <v>7400</v>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="U236" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="V236" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="W236" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X236" s="2" t="n">
+        <v>8075</v>
+      </c>
+      <c r="Y236" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z236" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA236" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB236" s="2" t="inlineStr"/>
+      <c r="AC236" s="2" t="inlineStr"/>
+      <c r="AD236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>translationjob94</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.942</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:44.958</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:45.607</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:52.316</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:52.368</t>
+        </is>
+      </c>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>21:55:52.624</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="n">
+        <v>649</v>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="n">
+        <v>7374</v>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U237" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V237" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="W237" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X237" s="2" t="n">
+        <v>7682</v>
+      </c>
+      <c r="Y237" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z237" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA237" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB237" s="2" t="inlineStr"/>
+      <c r="AC237" s="2" t="inlineStr"/>
+      <c r="AD237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>translationjob95</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>21:55:52.832</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>21:55:52.851</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>21:55:53.596</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>21:56:00.286</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>21:56:00.341</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>21:56:00.606</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U238" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V238" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="W238" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X238" s="2" t="n">
+        <v>7774</v>
+      </c>
+      <c r="Y238" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="Z238" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA238" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB238" s="2" t="inlineStr"/>
+      <c r="AC238" s="2" t="inlineStr"/>
+      <c r="AD238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>translationjob97</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:00.840</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:00.858</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:01.687</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:08.691</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:08.733</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>21:56:09.027</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="n">
+        <v>7851</v>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U239" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V239" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="W239" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X239" s="2" t="n">
+        <v>8187</v>
+      </c>
+      <c r="Y239" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z239" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA239" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB239" s="2" t="inlineStr"/>
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>translationjob98</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:01.355</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:01.371</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:01.926</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:09.653</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:09.695</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>21:56:09.896</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="n">
+        <v>8298</v>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U240" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V240" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="W240" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X240" s="2" t="n">
+        <v>8541</v>
+      </c>
+      <c r="Y240" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z240" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA240" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB240" s="2" t="inlineStr"/>
+      <c r="AC240" s="2" t="inlineStr"/>
+      <c r="AD240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>translationjob100</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:10.126</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:10.144</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:10.693</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:17.856</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:17.935</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>21:56:18.086</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="n">
+        <v>549</v>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="n">
+        <v>7730</v>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U241" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V241" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="W241" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X241" s="2" t="n">
+        <v>7960</v>
+      </c>
+      <c r="Y241" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="Z241" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA241" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB241" s="2" t="inlineStr"/>
+      <c r="AC241" s="2" t="inlineStr"/>
+      <c r="AD241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>translationjob101</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:18.279</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:18.294</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:18.770</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.111</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.160</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.313</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="n">
+        <v>6832</v>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U242" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V242" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="W242" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X242" s="2" t="n">
+        <v>7034</v>
+      </c>
+      <c r="Y242" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z242" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA242" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB242" s="2" t="inlineStr"/>
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>translationjob103</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.552</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.571</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.926</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.125</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.180</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.319</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="n">
+        <v>8573</v>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U243" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V243" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="W243" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X243" s="2" t="n">
+        <v>8767</v>
+      </c>
+      <c r="Y243" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z243" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA243" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB243" s="2" t="inlineStr"/>
+      <c r="AC243" s="2" t="inlineStr"/>
+      <c r="AD243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>translationjob104</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.513</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.528</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.915</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:41.571</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:41.618</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>21:56:41.767</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="n">
+        <v>7058</v>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U244" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V244" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="W244" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X244" s="2" t="n">
+        <v>7254</v>
+      </c>
+      <c r="Y244" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z244" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA244" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB244" s="2" t="inlineStr"/>
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>translationjob106</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:41.975</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:41.992</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:42.467</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:51.398</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:51.455</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>21:56:51.604</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>9423</v>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>9.4s</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U245" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V245" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="n">
+        <v>9629</v>
+      </c>
+      <c r="Y245" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="Z245" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA245" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD175"/>
+  <autoFilter ref="A1:AD245"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22493,7 +31332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22509,174 +31348,214 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Stuck</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Retried</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Avg Duration</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Min Duration</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Max Duration</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>10.3s</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>2.8s</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>42.5s</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>12.0s</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>1.7s</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>1m 28.9s</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>9.1s</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>4.0s</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>25.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>12.4s</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>52.5s</t>
         </is>
       </c>
     </row>
@@ -22691,231 +31570,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Error Category</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Language copy not found</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>250401</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>78904</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>24586</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1498</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>TranslationCleanupJobConsumer</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>636</v>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ThumbnailServlet</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>137</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>TicketAssemblyTranslationServiceImpl</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>GCCScriptProcessor</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ReplicationSquadListener</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>169398</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>139911</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>135602</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>132428</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ReplicationNewsAssemblyListener</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>139851</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>85748</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>21928</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3641</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>ResourceUtils commit</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>18708</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>12330</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>12256</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>10513</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>LockUtil contention</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>1252</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>1856</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>1648</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1144</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>TranslateHrefAttributes</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>768</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>1128</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Error executing workflow</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>761</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>154</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Content LC unknown state</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n">
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>89</v>
       </c>
+      <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Error processing Translation project</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n">
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>6</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -22929,7 +31851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22942,114 +31864,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Total Entries</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Init</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Obtained</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Expires</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Token Size Entries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>216</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>744</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>248</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>248</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>248</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>693</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/translation_jobs_all_days.xlsx
+++ b/reports/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AD$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD245"/>
+  <dimension ref="A1:AI245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,11 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,6 +672,31 @@
           <t>Retry Detail</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>API Requests</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Tokens</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Completion Tokens</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Total Tokens</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Latency (ms)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -793,6 +823,11 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -919,6 +954,11 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1045,6 +1085,11 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1171,6 +1216,11 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1297,6 +1347,11 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1423,6 +1478,11 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1549,6 +1609,11 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1675,6 +1740,11 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1801,6 +1871,11 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1927,6 +2002,11 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2053,6 +2133,11 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2179,6 +2264,11 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2305,6 +2395,11 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2431,6 +2526,11 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2557,6 +2657,11 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2683,6 +2788,11 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2809,6 +2919,11 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2935,6 +3050,11 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3061,6 +3181,11 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3187,6 +3312,11 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3313,6 +3443,11 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3439,6 +3574,11 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3565,6 +3705,11 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3691,6 +3836,11 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3817,6 +3967,11 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3943,6 +4098,11 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4069,6 +4229,11 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4195,6 +4360,11 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4321,6 +4491,11 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4447,6 +4622,11 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4573,6 +4753,11 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4699,6 +4884,11 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4825,6 +5015,11 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4951,6 +5146,11 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5077,6 +5277,11 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5203,6 +5408,11 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -5329,6 +5539,11 @@
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5455,6 +5670,11 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5581,6 +5801,11 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5707,6 +5932,11 @@
       <c r="AB41" s="2" t="inlineStr"/>
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5833,6 +6063,11 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5959,6 +6194,11 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6085,6 +6325,11 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -6211,6 +6456,11 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6337,6 +6587,11 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -6463,6 +6718,11 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6589,6 +6849,11 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -6715,6 +6980,11 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6841,6 +7111,11 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -6967,6 +7242,11 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7093,6 +7373,11 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7219,6 +7504,11 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7345,6 +7635,11 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -7471,6 +7766,11 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7597,6 +7897,11 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7723,6 +8028,11 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7849,6 +8159,11 @@
       <c r="AB58" s="2" t="inlineStr"/>
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -7975,6 +8290,11 @@
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -8101,6 +8421,11 @@
       <c r="AB60" s="2" t="inlineStr"/>
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -8227,6 +8552,11 @@
       <c r="AB61" s="2" t="inlineStr"/>
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8353,6 +8683,11 @@
       <c r="AB62" s="2" t="inlineStr"/>
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -8479,6 +8814,11 @@
       <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8605,6 +8945,11 @@
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -8731,6 +9076,11 @@
       <c r="AB65" s="2" t="inlineStr"/>
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8857,6 +9207,11 @@
       <c r="AB66" s="2" t="inlineStr"/>
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8983,6 +9338,11 @@
       <c r="AB67" s="2" t="inlineStr"/>
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -9109,6 +9469,11 @@
       <c r="AB68" s="2" t="inlineStr"/>
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -9235,6 +9600,11 @@
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -9361,6 +9731,11 @@
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -9487,6 +9862,11 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -9613,6 +9993,11 @@
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -9739,6 +10124,11 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -9865,6 +10255,11 @@
       <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -9991,6 +10386,11 @@
       <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -10117,6 +10517,11 @@
       <c r="AB76" s="2" t="inlineStr"/>
       <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -10243,6 +10648,11 @@
       <c r="AB77" s="2" t="inlineStr"/>
       <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -10369,6 +10779,11 @@
       <c r="AB78" s="2" t="inlineStr"/>
       <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -10495,6 +10910,11 @@
       <c r="AB79" s="2" t="inlineStr"/>
       <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -10621,6 +11041,11 @@
       <c r="AB80" s="2" t="inlineStr"/>
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -10747,6 +11172,11 @@
       <c r="AB81" s="2" t="inlineStr"/>
       <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -10873,6 +11303,11 @@
       <c r="AB82" s="2" t="inlineStr"/>
       <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -10999,6 +11434,11 @@
       <c r="AB83" s="2" t="inlineStr"/>
       <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -11125,6 +11565,11 @@
       <c r="AB84" s="2" t="inlineStr"/>
       <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -11251,6 +11696,11 @@
       <c r="AB85" s="2" t="inlineStr"/>
       <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -11377,6 +11827,11 @@
       <c r="AB86" s="2" t="inlineStr"/>
       <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -11503,6 +11958,11 @@
       <c r="AB87" s="2" t="inlineStr"/>
       <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -11629,6 +12089,11 @@
       <c r="AB88" s="2" t="inlineStr"/>
       <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -11755,6 +12220,11 @@
       <c r="AB89" s="2" t="inlineStr"/>
       <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -11881,6 +12351,11 @@
       <c r="AB90" s="2" t="inlineStr"/>
       <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -12007,6 +12482,11 @@
       <c r="AB91" s="2" t="inlineStr"/>
       <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -12133,6 +12613,11 @@
       <c r="AB92" s="2" t="inlineStr"/>
       <c r="AC92" s="2" t="inlineStr"/>
       <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -12259,6 +12744,11 @@
       <c r="AB93" s="2" t="inlineStr"/>
       <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -12385,6 +12875,11 @@
       <c r="AB94" s="2" t="inlineStr"/>
       <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -12511,6 +13006,11 @@
       <c r="AB95" s="2" t="inlineStr"/>
       <c r="AC95" s="2" t="inlineStr"/>
       <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -12637,6 +13137,11 @@
       <c r="AB96" s="2" t="inlineStr"/>
       <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -12763,6 +13268,11 @@
       <c r="AB97" s="2" t="inlineStr"/>
       <c r="AC97" s="2" t="inlineStr"/>
       <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -12889,6 +13399,11 @@
       <c r="AB98" s="2" t="inlineStr"/>
       <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -13015,6 +13530,11 @@
       <c r="AB99" s="2" t="inlineStr"/>
       <c r="AC99" s="2" t="inlineStr"/>
       <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -13141,6 +13661,11 @@
       <c r="AB100" s="2" t="inlineStr"/>
       <c r="AC100" s="2" t="inlineStr"/>
       <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -13267,6 +13792,11 @@
       <c r="AB101" s="2" t="inlineStr"/>
       <c r="AC101" s="2" t="inlineStr"/>
       <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -13393,6 +13923,11 @@
       <c r="AB102" s="2" t="inlineStr"/>
       <c r="AC102" s="2" t="inlineStr"/>
       <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -13519,6 +14054,11 @@
       <c r="AB103" s="2" t="inlineStr"/>
       <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -13645,6 +14185,11 @@
       <c r="AB104" s="2" t="inlineStr"/>
       <c r="AC104" s="2" t="inlineStr"/>
       <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -13771,6 +14316,11 @@
       <c r="AB105" s="2" t="inlineStr"/>
       <c r="AC105" s="2" t="inlineStr"/>
       <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -13897,6 +14447,11 @@
       <c r="AB106" s="2" t="inlineStr"/>
       <c r="AC106" s="2" t="inlineStr"/>
       <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -14023,6 +14578,11 @@
       <c r="AB107" s="2" t="inlineStr"/>
       <c r="AC107" s="2" t="inlineStr"/>
       <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -14123,6 +14683,11 @@
       <c r="AB108" s="3" t="inlineStr"/>
       <c r="AC108" s="3" t="inlineStr"/>
       <c r="AD108" s="3" t="inlineStr"/>
+      <c r="AE108" s="3" t="inlineStr"/>
+      <c r="AF108" s="3" t="inlineStr"/>
+      <c r="AG108" s="3" t="inlineStr"/>
+      <c r="AH108" s="3" t="inlineStr"/>
+      <c r="AI108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -14249,6 +14814,11 @@
       <c r="AB109" s="2" t="inlineStr"/>
       <c r="AC109" s="2" t="inlineStr"/>
       <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -14375,6 +14945,11 @@
       <c r="AB110" s="2" t="inlineStr"/>
       <c r="AC110" s="2" t="inlineStr"/>
       <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -14475,6 +15050,11 @@
       <c r="AB111" s="3" t="inlineStr"/>
       <c r="AC111" s="3" t="inlineStr"/>
       <c r="AD111" s="3" t="inlineStr"/>
+      <c r="AE111" s="3" t="inlineStr"/>
+      <c r="AF111" s="3" t="inlineStr"/>
+      <c r="AG111" s="3" t="inlineStr"/>
+      <c r="AH111" s="3" t="inlineStr"/>
+      <c r="AI111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -14601,6 +15181,11 @@
       <c r="AB112" s="2" t="inlineStr"/>
       <c r="AC112" s="2" t="inlineStr"/>
       <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -14727,6 +15312,11 @@
       <c r="AB113" s="2" t="inlineStr"/>
       <c r="AC113" s="2" t="inlineStr"/>
       <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -14853,6 +15443,11 @@
       <c r="AB114" s="2" t="inlineStr"/>
       <c r="AC114" s="2" t="inlineStr"/>
       <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -14953,6 +15548,11 @@
       <c r="AB115" s="3" t="inlineStr"/>
       <c r="AC115" s="3" t="inlineStr"/>
       <c r="AD115" s="3" t="inlineStr"/>
+      <c r="AE115" s="3" t="inlineStr"/>
+      <c r="AF115" s="3" t="inlineStr"/>
+      <c r="AG115" s="3" t="inlineStr"/>
+      <c r="AH115" s="3" t="inlineStr"/>
+      <c r="AI115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -15079,6 +15679,11 @@
       <c r="AB116" s="2" t="inlineStr"/>
       <c r="AC116" s="2" t="inlineStr"/>
       <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -15205,6 +15810,11 @@
       <c r="AB117" s="2" t="inlineStr"/>
       <c r="AC117" s="2" t="inlineStr"/>
       <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -15331,6 +15941,11 @@
       <c r="AB118" s="2" t="inlineStr"/>
       <c r="AC118" s="2" t="inlineStr"/>
       <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -15457,6 +16072,11 @@
       <c r="AB119" s="2" t="inlineStr"/>
       <c r="AC119" s="2" t="inlineStr"/>
       <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -15583,6 +16203,11 @@
       <c r="AB120" s="2" t="inlineStr"/>
       <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -15709,6 +16334,11 @@
       <c r="AB121" s="2" t="inlineStr"/>
       <c r="AC121" s="2" t="inlineStr"/>
       <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -15835,6 +16465,11 @@
       <c r="AB122" s="2" t="inlineStr"/>
       <c r="AC122" s="2" t="inlineStr"/>
       <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -15961,6 +16596,11 @@
       <c r="AB123" s="2" t="inlineStr"/>
       <c r="AC123" s="2" t="inlineStr"/>
       <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -16087,6 +16727,11 @@
       <c r="AB124" s="2" t="inlineStr"/>
       <c r="AC124" s="2" t="inlineStr"/>
       <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -16213,6 +16858,11 @@
       <c r="AB125" s="2" t="inlineStr"/>
       <c r="AC125" s="2" t="inlineStr"/>
       <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -16313,6 +16963,11 @@
       <c r="AB126" s="3" t="inlineStr"/>
       <c r="AC126" s="3" t="inlineStr"/>
       <c r="AD126" s="3" t="inlineStr"/>
+      <c r="AE126" s="3" t="inlineStr"/>
+      <c r="AF126" s="3" t="inlineStr"/>
+      <c r="AG126" s="3" t="inlineStr"/>
+      <c r="AH126" s="3" t="inlineStr"/>
+      <c r="AI126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -16439,6 +17094,11 @@
       <c r="AB127" s="2" t="inlineStr"/>
       <c r="AC127" s="2" t="inlineStr"/>
       <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -16565,6 +17225,11 @@
       <c r="AB128" s="2" t="inlineStr"/>
       <c r="AC128" s="2" t="inlineStr"/>
       <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -16691,6 +17356,11 @@
       <c r="AB129" s="2" t="inlineStr"/>
       <c r="AC129" s="2" t="inlineStr"/>
       <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -16817,6 +17487,11 @@
       <c r="AB130" s="2" t="inlineStr"/>
       <c r="AC130" s="2" t="inlineStr"/>
       <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -16943,6 +17618,11 @@
       <c r="AB131" s="2" t="inlineStr"/>
       <c r="AC131" s="2" t="inlineStr"/>
       <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -17069,6 +17749,11 @@
       <c r="AB132" s="2" t="inlineStr"/>
       <c r="AC132" s="2" t="inlineStr"/>
       <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -17195,6 +17880,11 @@
       <c r="AB133" s="2" t="inlineStr"/>
       <c r="AC133" s="2" t="inlineStr"/>
       <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -17321,6 +18011,11 @@
       <c r="AB134" s="2" t="inlineStr"/>
       <c r="AC134" s="2" t="inlineStr"/>
       <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -17447,6 +18142,11 @@
       <c r="AB135" s="2" t="inlineStr"/>
       <c r="AC135" s="2" t="inlineStr"/>
       <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -17573,6 +18273,11 @@
       <c r="AB136" s="2" t="inlineStr"/>
       <c r="AC136" s="2" t="inlineStr"/>
       <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -17699,6 +18404,11 @@
       <c r="AB137" s="2" t="inlineStr"/>
       <c r="AC137" s="2" t="inlineStr"/>
       <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -17825,6 +18535,11 @@
       <c r="AB138" s="2" t="inlineStr"/>
       <c r="AC138" s="2" t="inlineStr"/>
       <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -17951,6 +18666,11 @@
       <c r="AB139" s="2" t="inlineStr"/>
       <c r="AC139" s="2" t="inlineStr"/>
       <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -18077,6 +18797,11 @@
       <c r="AB140" s="2" t="inlineStr"/>
       <c r="AC140" s="2" t="inlineStr"/>
       <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -18203,6 +18928,11 @@
       <c r="AB141" s="2" t="inlineStr"/>
       <c r="AC141" s="2" t="inlineStr"/>
       <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -18329,6 +19059,11 @@
       <c r="AB142" s="2" t="inlineStr"/>
       <c r="AC142" s=